--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -22,11 +22,11 @@
     <definedName name="변수H">변수!$C$1:$W$1</definedName>
     <definedName name="환율">변수!$C$6:$W$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$W$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$W$86</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$W$95</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$W$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$W$83</definedName>
     <definedName name="SUBQH">subQ!$A$1:$W$1</definedName>
-    <definedName name="subQ">subQ!$A$5:$W$42</definedName>
+    <definedName name="subQ">subQ!$A$5:$W$44</definedName>
     <definedName name="SLS_H">SLS!$A$1:$AA$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -770,121 +770,121 @@
     <comment ref="K23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)</t>
       </text>
     </comment>
     <comment ref="L23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)</t>
       </text>
     </comment>
     <comment ref="N23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)</t>
       </text>
     </comment>
     <comment ref="O23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)</t>
       </text>
     </comment>
     <comment ref="P23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)</t>
       </text>
     </comment>
     <comment ref="Q23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)</t>
       </text>
     </comment>
     <comment ref="S23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)</t>
       </text>
     </comment>
     <comment ref="T23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)</t>
       </text>
     </comment>
     <comment ref="U23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 5.0% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)</t>
       </text>
     </comment>
     <comment ref="V23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 5.0% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)</t>
       </text>
     </comment>
     <comment ref="K24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟</t>
       </text>
     </comment>
     <comment ref="L24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟</t>
       </text>
     </comment>
     <comment ref="N24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟</t>
       </text>
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟</t>
       </text>
     </comment>
     <comment ref="P24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟</t>
       </text>
     </comment>
     <comment ref="Q24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟</t>
       </text>
     </comment>
     <comment ref="S24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟</t>
       </text>
     </comment>
     <comment ref="T24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟</t>
       </text>
     </comment>
     <comment ref="U24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 5.0% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟</t>
       </text>
     </comment>
     <comment ref="V24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 5.0% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟</t>
       </text>
     </comment>
     <comment ref="K25" authorId="0" shapeId="0">
@@ -896,55 +896,55 @@
     <comment ref="L25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 6498억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 6405억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="N25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 7194억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 7026억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 7877억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 7683억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="P25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 8476억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 8323억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 9142억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 9124억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="S25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 9727억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 9956억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="T25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 10267억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 10855억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="U25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 10714억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 11765억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="V25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 11211억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 12819억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="K26" authorId="0" shapeId="0">
@@ -1616,238 +1616,352 @@
     <comment ref="K43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 3206억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)</t>
+SLS 해양 원화 2776억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)</t>
       </text>
     </comment>
     <comment ref="L43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 3211억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)</t>
+SLS 해양 원화 2786억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)</t>
       </text>
     </comment>
     <comment ref="N43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 3141억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)</t>
+SLS 해양 원화 2726억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)</t>
       </text>
     </comment>
     <comment ref="O43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 3176억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)</t>
+SLS 해양 원화 2756억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)</t>
       </text>
     </comment>
     <comment ref="P43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 3036억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)</t>
+SLS 해양 원화 2636억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)</t>
       </text>
     </comment>
     <comment ref="Q43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 2647억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)</t>
+SLS 해양 원화 2302억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)</t>
       </text>
     </comment>
     <comment ref="S43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 2424억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)</t>
+SLS 해양 원화 2110억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)</t>
       </text>
     </comment>
     <comment ref="T43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 2424억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)</t>
+SLS 해양 원화 2110억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)</t>
       </text>
     </comment>
     <comment ref="U43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 2150억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)</t>
+SLS 해양 원화 1875억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)</t>
       </text>
     </comment>
     <comment ref="V43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 1686억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)</t>
+SLS 해양 원화 1476억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)</t>
       </text>
     </comment>
     <comment ref="K44" authorId="0" shapeId="0">
       <text>
+        <t>모델값 역산(implied): v / 매출액
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+      </text>
+    </comment>
+    <comment ref="L44" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출액
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+      </text>
+    </comment>
+    <comment ref="N44" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출액
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+      </text>
+    </comment>
+    <comment ref="O44" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출액
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+      </text>
+    </comment>
+    <comment ref="P44" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출액
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+      </text>
+    </comment>
+    <comment ref="Q44" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출액
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+      </text>
+    </comment>
+    <comment ref="S44" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출액
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+      </text>
+    </comment>
+    <comment ref="T44" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출액
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+      </text>
+    </comment>
+    <comment ref="U44" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출액
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+      </text>
+    </comment>
+    <comment ref="V44" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출액
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+      </text>
+    </comment>
+    <comment ref="K45" authorId="0" shapeId="0">
+      <text>
         <t>모델값 역산(implied): v / 매출조선
-매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)</t>
-      </text>
-    </comment>
-    <comment ref="L44" authorId="0" shapeId="0">
+매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)</t>
+      </text>
+    </comment>
+    <comment ref="L45" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출조선
-매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)</t>
-      </text>
-    </comment>
-    <comment ref="N44" authorId="0" shapeId="0">
+매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)</t>
+      </text>
+    </comment>
+    <comment ref="N45" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출조선
-매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)</t>
-      </text>
-    </comment>
-    <comment ref="O44" authorId="0" shapeId="0">
+매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)</t>
+      </text>
+    </comment>
+    <comment ref="O45" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출조선
-매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)</t>
-      </text>
-    </comment>
-    <comment ref="P44" authorId="0" shapeId="0">
+매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)</t>
+      </text>
+    </comment>
+    <comment ref="P45" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출조선
-매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)</t>
-      </text>
-    </comment>
-    <comment ref="Q44" authorId="0" shapeId="0">
+매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)</t>
+      </text>
+    </comment>
+    <comment ref="Q45" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출조선
-매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)</t>
-      </text>
-    </comment>
-    <comment ref="S44" authorId="0" shapeId="0">
+매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)</t>
+      </text>
+    </comment>
+    <comment ref="S45" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출조선
-매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)</t>
-      </text>
-    </comment>
-    <comment ref="T44" authorId="0" shapeId="0">
+매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)</t>
+      </text>
+    </comment>
+    <comment ref="T45" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출조선
-매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)</t>
-      </text>
-    </comment>
-    <comment ref="U44" authorId="0" shapeId="0">
+매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)</t>
+      </text>
+    </comment>
+    <comment ref="U45" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출조선
-매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)</t>
-      </text>
-    </comment>
-    <comment ref="V44" authorId="0" shapeId="0">
+매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)</t>
+      </text>
+    </comment>
+    <comment ref="V45" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출조선
-매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)</t>
-      </text>
-    </comment>
-    <comment ref="K45" authorId="0" shapeId="0">
+매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)</t>
+      </text>
+    </comment>
+    <comment ref="L46" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출조선신규
+매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함</t>
+      </text>
+    </comment>
+    <comment ref="N46" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출조선신규
+매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함</t>
+      </text>
+    </comment>
+    <comment ref="O46" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출조선신규
+매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함</t>
+      </text>
+    </comment>
+    <comment ref="P46" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출조선신규
+매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함</t>
+      </text>
+    </comment>
+    <comment ref="Q46" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출조선신규
+매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함</t>
+      </text>
+    </comment>
+    <comment ref="S46" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출조선신규
+매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함</t>
+      </text>
+    </comment>
+    <comment ref="T46" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출조선신규
+매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함</t>
+      </text>
+    </comment>
+    <comment ref="U46" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출조선신규
+매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함</t>
+      </text>
+    </comment>
+    <comment ref="V46" authorId="0" shapeId="0">
+      <text>
+        <t>모델값 역산(implied): v / 매출조선신규
+매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함</t>
+      </text>
+    </comment>
+    <comment ref="K47" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지</t>
       </text>
     </comment>
-    <comment ref="L45" authorId="0" shapeId="0">
+    <comment ref="L47" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지</t>
       </text>
     </comment>
-    <comment ref="N45" authorId="0" shapeId="0">
+    <comment ref="N47" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지</t>
       </text>
     </comment>
-    <comment ref="O45" authorId="0" shapeId="0">
+    <comment ref="O47" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지</t>
       </text>
     </comment>
-    <comment ref="P45" authorId="0" shapeId="0">
+    <comment ref="P47" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지</t>
       </text>
     </comment>
-    <comment ref="Q45" authorId="0" shapeId="0">
+    <comment ref="Q47" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지</t>
       </text>
     </comment>
-    <comment ref="S45" authorId="0" shapeId="0">
+    <comment ref="S47" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지</t>
       </text>
     </comment>
-    <comment ref="T45" authorId="0" shapeId="0">
+    <comment ref="T47" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지</t>
       </text>
     </comment>
-    <comment ref="U45" authorId="0" shapeId="0">
+    <comment ref="U47" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지</t>
       </text>
     </comment>
-    <comment ref="V45" authorId="0" shapeId="0">
+    <comment ref="V47" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지</t>
       </text>
     </comment>
-    <comment ref="K46" authorId="0" shapeId="0">
+    <comment ref="K48" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출기타
 매출기타 × 회사 OPM(부문 OP 미공시)</t>
       </text>
     </comment>
-    <comment ref="L46" authorId="0" shapeId="0">
+    <comment ref="L48" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출기타
 매출기타 × 회사 OPM(부문 OP 미공시)</t>
       </text>
     </comment>
-    <comment ref="N46" authorId="0" shapeId="0">
+    <comment ref="N48" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출기타
 매출기타 × 회사 OPM(부문 OP 미공시)</t>
       </text>
     </comment>
-    <comment ref="O46" authorId="0" shapeId="0">
+    <comment ref="O48" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출기타
 매출기타 × 회사 OPM(부문 OP 미공시)</t>
       </text>
     </comment>
-    <comment ref="P46" authorId="0" shapeId="0">
+    <comment ref="P48" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출기타
 매출기타 × 회사 OPM(부문 OP 미공시)</t>
       </text>
     </comment>
-    <comment ref="Q46" authorId="0" shapeId="0">
+    <comment ref="Q48" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출기타
 매출기타 × 회사 OPM(부문 OP 미공시)</t>
       </text>
     </comment>
-    <comment ref="S46" authorId="0" shapeId="0">
+    <comment ref="S48" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출기타
 매출기타 × 회사 OPM(부문 OP 미공시)</t>
       </text>
     </comment>
-    <comment ref="T46" authorId="0" shapeId="0">
+    <comment ref="T48" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출기타
 매출기타 × 회사 OPM(부문 OP 미공시)</t>
       </text>
     </comment>
-    <comment ref="U46" authorId="0" shapeId="0">
+    <comment ref="U48" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출기타
 매출기타 × 회사 OPM(부문 OP 미공시)</t>
       </text>
     </comment>
-    <comment ref="V46" authorId="0" shapeId="0">
+    <comment ref="V48" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출기타
 매출기타 × 회사 OPM(부문 OP 미공시)</t>
@@ -2105,61 +2219,61 @@
     </comment>
     <comment ref="K9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="L9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="N9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="O9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="P9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="Q9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="S9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="T9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="U9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 5.0% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="V9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 5.0% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟)
 [ratio]</t>
       </text>
     </comment>
@@ -2190,61 +2304,61 @@
     </comment>
     <comment ref="K10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟
 [yoy]</t>
       </text>
     </comment>
     <comment ref="L10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟
 [yoy]</t>
       </text>
     </comment>
     <comment ref="N10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟
 [yoy]</t>
       </text>
     </comment>
     <comment ref="O10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟
 [yoy]</t>
       </text>
     </comment>
     <comment ref="P10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.5% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Q10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟
 [yoy]</t>
       </text>
     </comment>
     <comment ref="S10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟
 [yoy]</t>
       </text>
     </comment>
     <comment ref="T10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 4.4% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟
 [yoy]</t>
       </text>
     </comment>
     <comment ref="U10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 5.0% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 5.0% + 회사 캘리브레이션 +22.5%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟
 [yoy]</t>
       </text>
     </comment>
@@ -2256,55 +2370,55 @@
     </comment>
     <comment ref="L11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 6498억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 6405억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="N11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 7194억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 7026억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 7877억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 7683억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="P11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 8476억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 8323억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 9142억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 9124억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 9727억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 9956억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 10267억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 10855억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 10714억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 11765억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 11211억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 12819억 × 1.76% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -3401,259 +3515,398 @@
     </comment>
     <comment ref="K34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 3206억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 2776억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="L34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 3211억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 2786억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="N34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 3141억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 2726억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="O34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 3176억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 2756억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="P34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 3036억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 2636억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="Q34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2647억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 2302억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="S34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2424억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 2110억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="T34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2424억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 2110억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="U34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2150억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1875억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="V34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1686억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억)
+        <t>추정: SLS 해양 원화 1476억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy)
 [ratio]</t>
       </text>
     </comment>
+    <comment ref="I35" authorId="0" shapeId="0">
+      <text>
+        <t>실측(계정 매핑 없음 — 모델값 직접) — origin 2026Q2 이전 실적 분기 — origin 이후 신규수주 매출은 정의상 0</t>
+      </text>
+    </comment>
+    <comment ref="J35" authorId="0" shapeId="0">
+      <text>
+        <t>실측(계정 매핑 없음 — 모델값 직접) — origin 2026Q2 이전 실적 분기 — origin 이후 신규수주 매출은 정의상 0</t>
+      </text>
+    </comment>
     <comment ref="K35" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="L35" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="N35" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="O35" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="P35" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="Q35" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="S35" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="T35" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="U35" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="V35" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="F36" authorId="0" shapeId="0">
+    <comment ref="K36" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="L36" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="N36" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="O36" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="P36" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="Q36" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="S36" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="T36" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="U36" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="V36" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선 × 타겟 OPM(부문 OP 미공시 → 회사 OPM 적용; 신규수주분 포함)
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="I37" authorId="0" shapeId="0">
+      <text>
+        <t>실측(계정 매핑 없음 — 모델값 직접) — origin 2026Q2 이전 실적 분기 — 정의상 0</t>
+      </text>
+    </comment>
+    <comment ref="J37" authorId="0" shapeId="0">
+      <text>
+        <t>실측(계정 매핑 없음 — 모델값 직접) — origin 2026Q2 이전 실적 분기 — 정의상 0</t>
+      </text>
+    </comment>
+    <comment ref="K37" authorId="0" shapeId="0">
+      <text>
+        <t>추정(가정 셀 참조 불가 — 기준값 없음, 모델값 직접): 매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함</t>
+      </text>
+    </comment>
+    <comment ref="L37" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="N37" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="O37" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="P37" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="Q37" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="S37" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="T37" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="U37" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="V37" authorId="0" shapeId="0">
+      <text>
+        <t>추정: 매출조선신규 × 타겟 OPM(신규분에도 같은 타겟) — OP조선에 포함
+[ratio]</t>
+      </text>
+    </comment>
+    <comment ref="F38" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — 연결 매출 − 조선 부문(파생)</t>
       </text>
     </comment>
-    <comment ref="G36" authorId="0" shapeId="0">
+    <comment ref="G38" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — 연결 매출 − 조선 부문(파생)</t>
       </text>
     </comment>
-    <comment ref="I36" authorId="0" shapeId="0">
+    <comment ref="I38" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — 연결 매출 − 조선 부문(파생)</t>
       </text>
     </comment>
-    <comment ref="J36" authorId="0" shapeId="0">
+    <comment ref="J38" authorId="0" shapeId="0">
       <text>
         <t>실측(계정 매핑 없음 — 모델값 직접) — 연결 매출 − 조선 부문(파생)</t>
       </text>
     </comment>
-    <comment ref="K36" authorId="0" shapeId="0">
+    <comment ref="K38" authorId="0" shapeId="0">
       <text>
         <t>추정: 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="L36" authorId="0" shapeId="0">
+    <comment ref="L38" authorId="0" shapeId="0">
       <text>
         <t>추정: 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="N36" authorId="0" shapeId="0">
+    <comment ref="N38" authorId="0" shapeId="0">
       <text>
         <t>추정: 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="O36" authorId="0" shapeId="0">
+    <comment ref="O38" authorId="0" shapeId="0">
       <text>
         <t>추정: 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="P36" authorId="0" shapeId="0">
+    <comment ref="P38" authorId="0" shapeId="0">
       <text>
         <t>추정: 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="Q36" authorId="0" shapeId="0">
+    <comment ref="Q38" authorId="0" shapeId="0">
       <text>
         <t>추정: 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="S36" authorId="0" shapeId="0">
+    <comment ref="S38" authorId="0" shapeId="0">
       <text>
         <t>추정: 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="T36" authorId="0" shapeId="0">
+    <comment ref="T38" authorId="0" shapeId="0">
       <text>
         <t>추정: 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="U36" authorId="0" shapeId="0">
+    <comment ref="U38" authorId="0" shapeId="0">
       <text>
         <t>추정: 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="V36" authorId="0" shapeId="0">
+    <comment ref="V38" authorId="0" shapeId="0">
       <text>
         <t>추정: 기타 부문(연결 − 조선 부문) 최근 4분기 중위 22억 유지
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="K37" authorId="0" shapeId="0">
+    <comment ref="K39" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출기타 × 회사 OPM(부문 OP 미공시)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="L37" authorId="0" shapeId="0">
+    <comment ref="L39" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출기타 × 회사 OPM(부문 OP 미공시)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="N37" authorId="0" shapeId="0">
+    <comment ref="N39" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출기타 × 회사 OPM(부문 OP 미공시)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="O37" authorId="0" shapeId="0">
+    <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출기타 × 회사 OPM(부문 OP 미공시)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="P37" authorId="0" shapeId="0">
+    <comment ref="P39" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출기타 × 회사 OPM(부문 OP 미공시)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="Q37" authorId="0" shapeId="0">
+    <comment ref="Q39" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출기타 × 회사 OPM(부문 OP 미공시)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="S37" authorId="0" shapeId="0">
+    <comment ref="S39" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출기타 × 회사 OPM(부문 OP 미공시)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="T37" authorId="0" shapeId="0">
+    <comment ref="T39" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출기타 × 회사 OPM(부문 OP 미공시)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="U37" authorId="0" shapeId="0">
+    <comment ref="U39" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출기타 × 회사 OPM(부문 OP 미공시)
 [ratio]</t>
       </text>
     </comment>
-    <comment ref="V37" authorId="0" shapeId="0">
+    <comment ref="V39" authorId="0" shapeId="0">
       <text>
         <t>추정: 매출기타 × 회사 OPM(부문 OP 미공시)
 [ratio]</t>
@@ -3968,7 +4221,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4089,14 +4342,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / 추정 매출은 2026Q2 기준 잔고 소진분만 — 이후 신규 수주 매출 미포함(2028 감소는 이 한계). forecast_panel 모듈 참고 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
+          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 14,599억) — 보수/낙관은 scenarios 블록(합산 안 함) / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.4, "op_wape_pct": 26.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 2960.48, "rev_act": 2739.73, "op_pred": 624.67, "op_act": 664.89}, {"q": "2025Q4", "rev_pred": 2960.48, "rev_act": 3504.05, "op_pred": 624.67, "op_act": 953.29}, {"q": "2026Q1", "rev_pred": 2960.48, "rev_act": 3082.71, "op_pred": 624.67, "op_act": 826.39}, {"q": "2026Q2", "rev_pred": 2960.48, "rev_act": 3544.35, "op_pred": 624.67, "op_act": 952.49}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.4, "op_wape_pct": 26.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 2960.48, "rev_act": 2739.73, "op_pred": 624.67, "op_act": 664.89}, {"q": "2025Q4", "rev_pred": 2960.48, "rev_act": 3504.05, "op_pred": 624.67, "op_act": 953.29}, {"q": "2026Q1", "rev_pred": 2960.48, "rev_act": 3082.71, "op_pred": 624.67, "op_act": 826.39}, {"q": "2026Q2", "rev_pred": 2960.48, "rev_act": 3544.35, "op_pred": 624.67, "op_act": 952.49}]}</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5268,7 @@
         </is>
       </c>
       <c r="D16" s="26">
-        <f>변수!D59</f>
+        <f>변수!D61</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -5172,7 +5425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W59"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6257,36 +6510,36 @@
         <v/>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.178126</v>
+        <v>0.021092</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>-0.07758900000000001</v>
+        <v>-0.175375</v>
       </c>
       <c r="M21" s="25" t="n"/>
       <c r="N21" s="24" t="n">
-        <v>0.025843</v>
+        <v>-0.009350000000000001</v>
       </c>
       <c r="O21" s="24" t="n">
-        <v>-0.097922</v>
+        <v>-0.034365</v>
       </c>
       <c r="P21" s="24" t="n">
-        <v>-0.052699</v>
+        <v>0.331479</v>
       </c>
       <c r="Q21" s="24" t="n">
-        <v>-0.174511</v>
+        <v>0.337868</v>
       </c>
       <c r="R21" s="25" t="n"/>
       <c r="S21" s="24" t="n">
-        <v>-0.22681</v>
+        <v>0.366595</v>
       </c>
       <c r="T21" s="24" t="n">
-        <v>-0.23525</v>
+        <v>0.363591</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>-0.289765</v>
+        <v>0.312789</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>-0.360057</v>
+        <v>0.263117</v>
       </c>
       <c r="W21" s="25" t="n"/>
     </row>
@@ -6331,23 +6584,23 @@
         <v/>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.024438</v>
+        <v>0.024436</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>0.024436</v>
+        <v>0.024437</v>
       </c>
       <c r="M22" s="25">
         <f>IFERROR(subQ!M8/subQ!M5,"")</f>
         <v/>
       </c>
       <c r="N22" s="24" t="n">
-        <v>0.024437</v>
+        <v>0.024438</v>
       </c>
       <c r="O22" s="24" t="n">
+        <v>0.024438</v>
+      </c>
+      <c r="P22" s="24" t="n">
         <v>0.024436</v>
-      </c>
-      <c r="P22" s="24" t="n">
-        <v>0.024437</v>
       </c>
       <c r="Q22" s="24" t="n">
         <v>0.024437</v>
@@ -6357,16 +6610,16 @@
         <v/>
       </c>
       <c r="S22" s="24" t="n">
+        <v>0.024438</v>
+      </c>
+      <c r="T22" s="24" t="n">
+        <v>0.024438</v>
+      </c>
+      <c r="U22" s="24" t="n">
         <v>0.024436</v>
       </c>
-      <c r="T22" s="24" t="n">
+      <c r="V22" s="24" t="n">
         <v>0.024436</v>
-      </c>
-      <c r="U22" s="24" t="n">
-        <v>0.024438</v>
-      </c>
-      <c r="V22" s="24" t="n">
-        <v>0.024434</v>
       </c>
       <c r="W22" s="25">
         <f>IFERROR(subQ!W8/subQ!W5,"")</f>
@@ -6414,42 +6667,42 @@
         <v/>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.269903</v>
+        <v>0.268402</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>0.269905</v>
+        <v>0.268404</v>
       </c>
       <c r="M23" s="25">
         <f>IFERROR(subQ!M9/subQ!M5,"")</f>
         <v/>
       </c>
       <c r="N23" s="24" t="n">
-        <v>0.269904</v>
+        <v>0.268402</v>
       </c>
       <c r="O23" s="24" t="n">
-        <v>0.269904</v>
+        <v>0.268402</v>
       </c>
       <c r="P23" s="24" t="n">
-        <v>0.269704</v>
+        <v>0.268403</v>
       </c>
       <c r="Q23" s="24" t="n">
-        <v>0.268904</v>
+        <v>0.268404</v>
       </c>
       <c r="R23" s="25">
         <f>IFERROR(subQ!R9/subQ!R5,"")</f>
         <v/>
       </c>
       <c r="S23" s="24" t="n">
-        <v>0.268502</v>
+        <v>0.268403</v>
       </c>
       <c r="T23" s="24" t="n">
-        <v>0.268502</v>
+        <v>0.268404</v>
       </c>
       <c r="U23" s="24" t="n">
-        <v>0.274602</v>
+        <v>0.268403</v>
       </c>
       <c r="V23" s="24" t="n">
-        <v>0.274602</v>
+        <v>0.268404</v>
       </c>
       <c r="W23" s="25">
         <f>IFERROR(subQ!W9/subQ!W5,"")</f>
@@ -6478,40 +6731,40 @@
       <c r="H24" s="22" t="n"/>
       <c r="I24" s="21" t="n"/>
       <c r="J24" s="23">
-        <f>IFERROR(subQ!J39/subQ!E39-1,"")</f>
+        <f>IFERROR(subQ!J41/subQ!E41-1,"")</f>
         <v/>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.112073</v>
+        <v>0.105892</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>-0.008085</v>
+        <v>-0.013598</v>
       </c>
       <c r="M24" s="25" t="n"/>
       <c r="N24" s="24" t="n">
-        <v>0.006714</v>
+        <v>0.001119</v>
       </c>
       <c r="O24" s="24" t="n">
-        <v>0.004466</v>
+        <v>-0.001116</v>
       </c>
       <c r="P24" s="24" t="n">
-        <v>-0.000741</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="24" t="n">
-        <v>-0.003705</v>
+        <v>0</v>
       </c>
       <c r="R24" s="25" t="n"/>
       <c r="S24" s="24" t="n">
-        <v>-0.005187</v>
+        <v>0</v>
       </c>
       <c r="T24" s="24" t="n">
-        <v>-0.005187</v>
+        <v>0</v>
       </c>
       <c r="U24" s="24" t="n">
-        <v>0.018168</v>
+        <v>0</v>
       </c>
       <c r="V24" s="24" t="n">
-        <v>0.021197</v>
+        <v>0</v>
       </c>
       <c r="W24" s="25" t="n"/>
     </row>
@@ -6559,39 +6812,39 @@
         <v>25.59</v>
       </c>
       <c r="L25" s="29" t="n">
-        <v>28.66</v>
+        <v>28.25</v>
       </c>
       <c r="M25" s="30">
         <f>subQ!M11</f>
         <v/>
       </c>
       <c r="N25" s="29" t="n">
-        <v>31.73</v>
+        <v>30.99</v>
       </c>
       <c r="O25" s="29" t="n">
-        <v>34.74</v>
+        <v>33.88</v>
       </c>
       <c r="P25" s="29" t="n">
-        <v>37.38</v>
+        <v>36.71</v>
       </c>
       <c r="Q25" s="29" t="n">
-        <v>40.32</v>
+        <v>40.24</v>
       </c>
       <c r="R25" s="30">
         <f>subQ!R11</f>
         <v/>
       </c>
       <c r="S25" s="29" t="n">
-        <v>42.9</v>
+        <v>43.91</v>
       </c>
       <c r="T25" s="29" t="n">
-        <v>45.28</v>
+        <v>47.88</v>
       </c>
       <c r="U25" s="29" t="n">
-        <v>47.25</v>
+        <v>51.89</v>
       </c>
       <c r="V25" s="29" t="n">
-        <v>49.44</v>
+        <v>56.54</v>
       </c>
       <c r="W25" s="30">
         <f>subQ!W11</f>
@@ -6805,42 +7058,42 @@
         <v/>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.227596</v>
+        <v>0.227589</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>0.227595</v>
+        <v>0.227591</v>
       </c>
       <c r="M28" s="25">
         <f>IFERROR(subQ!M15/subQ!M14,"")</f>
         <v/>
       </c>
       <c r="N28" s="24" t="n">
+        <v>0.2276</v>
+      </c>
+      <c r="O28" s="24" t="n">
+        <v>0.227599</v>
+      </c>
+      <c r="P28" s="24" t="n">
+        <v>0.22759</v>
+      </c>
+      <c r="Q28" s="24" t="n">
         <v>0.227594</v>
-      </c>
-      <c r="O28" s="24" t="n">
-        <v>0.227593</v>
-      </c>
-      <c r="P28" s="24" t="n">
-        <v>0.2276</v>
-      </c>
-      <c r="Q28" s="24" t="n">
-        <v>0.227596</v>
       </c>
       <c r="R28" s="25">
         <f>IFERROR(subQ!R15/subQ!R14,"")</f>
         <v/>
       </c>
       <c r="S28" s="24" t="n">
-        <v>0.227589</v>
+        <v>0.227598</v>
       </c>
       <c r="T28" s="24" t="n">
-        <v>0.2276</v>
+        <v>0.227597</v>
       </c>
       <c r="U28" s="24" t="n">
-        <v>0.227595</v>
+        <v>0.227594</v>
       </c>
       <c r="V28" s="24" t="n">
-        <v>0.227601</v>
+        <v>0.227592</v>
       </c>
       <c r="W28" s="25">
         <f>IFERROR(subQ!W15/subQ!W14,"")</f>
@@ -7036,17 +7289,17 @@
         <v>0.0016</v>
       </c>
       <c r="L31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="M31" s="30" t="n"/>
       <c r="N31" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O31" s="29" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="P31" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="O31" s="29" t="n">
-        <v>95.23</v>
-      </c>
-      <c r="P31" s="29" t="n">
-        <v>-0.01</v>
       </c>
       <c r="Q31" s="29" t="n">
         <v>0</v>
@@ -7059,7 +7312,7 @@
         <v>95.22</v>
       </c>
       <c r="U31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="V31" s="29" t="n">
         <v>0</v>
@@ -7104,17 +7357,17 @@
         <v>0.0016</v>
       </c>
       <c r="L32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="M32" s="30" t="n"/>
       <c r="N32" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="O32" s="29" t="n">
+        <v>95.22</v>
+      </c>
+      <c r="P32" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="O32" s="29" t="n">
-        <v>95.23</v>
-      </c>
-      <c r="P32" s="29" t="n">
-        <v>-0.01</v>
       </c>
       <c r="Q32" s="29" t="n">
         <v>0</v>
@@ -7127,7 +7380,7 @@
         <v>95.22</v>
       </c>
       <c r="U32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="V32" s="29" t="n">
         <v>0</v>
@@ -7265,36 +7518,36 @@
         <v/>
       </c>
       <c r="K35" s="24" t="n">
-        <v>0.119994</v>
+        <v>0.103976</v>
       </c>
       <c r="L35" s="24" t="n">
-        <v>0.107109</v>
+        <v>0.09693599999999999</v>
       </c>
       <c r="M35" s="25" t="n"/>
       <c r="N35" s="24" t="n">
-        <v>0.095052</v>
+        <v>0.093523</v>
       </c>
       <c r="O35" s="24" t="n">
-        <v>0.075933</v>
+        <v>0.083369</v>
       </c>
       <c r="P35" s="24" t="n">
-        <v>0.07856</v>
+        <v>0.09618500000000001</v>
       </c>
       <c r="Q35" s="24" t="n">
-        <v>0.064029</v>
+        <v>0.091248</v>
       </c>
       <c r="R35" s="25" t="n"/>
       <c r="S35" s="24" t="n">
-        <v>0.05554</v>
+        <v>0.090307</v>
       </c>
       <c r="T35" s="24" t="n">
-        <v>0.043524</v>
+        <v>0.08376400000000001</v>
       </c>
       <c r="U35" s="24" t="n">
-        <v>0.046399</v>
+        <v>0.089576</v>
       </c>
       <c r="V35" s="24" t="n">
-        <v>0.03571</v>
+        <v>0.08237899999999999</v>
       </c>
       <c r="W35" s="25" t="n"/>
     </row>
@@ -7566,29 +7819,29 @@
       <c r="L41" s="31" t="n"/>
       <c r="M41" s="25" t="n"/>
       <c r="N41" s="24" t="n">
-        <v>-0.470848</v>
+        <v>-0.431979</v>
       </c>
       <c r="O41" s="24" t="n">
-        <v>-0.352142</v>
+        <v>-0.314525</v>
       </c>
       <c r="P41" s="24" t="n">
-        <v>0.104056</v>
+        <v>0.042735</v>
       </c>
       <c r="Q41" s="24" t="n">
-        <v>0.120069</v>
+        <v>-0.082524</v>
       </c>
       <c r="R41" s="25" t="n"/>
       <c r="S41" s="24" t="n">
-        <v>0.153589</v>
+        <v>-0.183515</v>
       </c>
       <c r="T41" s="24" t="n">
-        <v>0.185484</v>
+        <v>-0.260671</v>
       </c>
       <c r="U41" s="24" t="n">
-        <v>0.266773</v>
+        <v>-0.257377</v>
       </c>
       <c r="V41" s="24" t="n">
-        <v>0.327718</v>
+        <v>-0.24515</v>
       </c>
       <c r="W41" s="25" t="n"/>
     </row>
@@ -7618,36 +7871,36 @@
         <v/>
       </c>
       <c r="K42" s="24" t="n">
-        <v>-0.587156</v>
+        <v>-0.584098</v>
       </c>
       <c r="L42" s="24" t="n">
-        <v>-0.492063</v>
+        <v>-0.484127</v>
       </c>
       <c r="M42" s="25" t="n"/>
       <c r="N42" s="24" t="n">
-        <v>-0.559567</v>
+        <v>-0.552347</v>
       </c>
       <c r="O42" s="24" t="n">
-        <v>-0.508403</v>
+        <v>-0.504202</v>
       </c>
       <c r="P42" s="24" t="n">
-        <v>-0.17037</v>
+        <v>-0.176471</v>
       </c>
       <c r="Q42" s="24" t="n">
-        <v>-0.15625</v>
+        <v>-0.184615</v>
       </c>
       <c r="R42" s="25" t="n"/>
       <c r="S42" s="24" t="n">
-        <v>-0.147541</v>
+        <v>-0.185484</v>
       </c>
       <c r="T42" s="24" t="n">
-        <v>-0.128205</v>
+        <v>-0.186441</v>
       </c>
       <c r="U42" s="24" t="n">
-        <v>-0.116071</v>
+        <v>-0.196429</v>
       </c>
       <c r="V42" s="24" t="n">
-        <v>-0.111111</v>
+        <v>-0.188679</v>
       </c>
       <c r="W42" s="25" t="n"/>
     </row>
@@ -7692,42 +7945,42 @@
         <v/>
       </c>
       <c r="K43" s="24" t="n">
-        <v>0.993324</v>
+        <v>0.992293</v>
       </c>
       <c r="L43" s="24" t="n">
-        <v>0.99333</v>
+        <v>0.9925389999999999</v>
       </c>
       <c r="M43" s="25">
         <f>IFERROR(subQ!M34/subQ!M5,"")</f>
         <v/>
       </c>
       <c r="N43" s="24" t="n">
-        <v>0.993182</v>
+        <v>0.99294</v>
       </c>
       <c r="O43" s="24" t="n">
-        <v>0.9932569999999999</v>
+        <v>0.9937009999999999</v>
       </c>
       <c r="P43" s="24" t="n">
-        <v>0.992949</v>
+        <v>0.994212</v>
       </c>
       <c r="Q43" s="24" t="n">
-        <v>0.991919</v>
+        <v>0.9944229999999999</v>
       </c>
       <c r="R43" s="25">
         <f>IFERROR(subQ!R34/subQ!R5,"")</f>
         <v/>
       </c>
       <c r="S43" s="24" t="n">
-        <v>0.991182</v>
+        <v>0.994834</v>
       </c>
       <c r="T43" s="24" t="n">
-        <v>0.991182</v>
+        <v>0.99538</v>
       </c>
       <c r="U43" s="24" t="n">
-        <v>0.990072</v>
+        <v>0.995593</v>
       </c>
       <c r="V43" s="24" t="n">
-        <v>0.9873729999999999</v>
+        <v>0.9955850000000001</v>
       </c>
       <c r="W43" s="25">
         <f>IFERROR(subQ!W34/subQ!W5,"")</f>
@@ -7737,7 +7990,7 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>drv:OP조선</t>
+          <t>drv:매출조선신규</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -7747,80 +8000,80 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OP조선 마진(/매출조선)</t>
+          <t>매출조선신규 비중(/매출액)</t>
         </is>
       </c>
       <c r="E44" s="21">
-        <f>IFERROR(subQ!E35/subQ!E34,"")</f>
+        <f>IFERROR(subQ!E35/subQ!E5,"")</f>
         <v/>
       </c>
       <c r="F44" s="21">
-        <f>IFERROR(subQ!F35/subQ!F34,"")</f>
+        <f>IFERROR(subQ!F35/subQ!F5,"")</f>
         <v/>
       </c>
       <c r="G44" s="21">
-        <f>IFERROR(subQ!G35/subQ!G34,"")</f>
+        <f>IFERROR(subQ!G35/subQ!G5,"")</f>
         <v/>
       </c>
       <c r="H44" s="22">
-        <f>IFERROR(subQ!H35/subQ!H34,"")</f>
+        <f>IFERROR(subQ!H35/subQ!H5,"")</f>
         <v/>
       </c>
       <c r="I44" s="21">
-        <f>IFERROR(subQ!I35/subQ!I34,"")</f>
+        <f>IFERROR(subQ!I35/subQ!I5,"")</f>
         <v/>
       </c>
       <c r="J44" s="23">
-        <f>IFERROR(subQ!J35/subQ!J34,"")</f>
+        <f>IFERROR(subQ!J35/subQ!J5,"")</f>
         <v/>
       </c>
       <c r="K44" s="24" t="n">
-        <v>0.269902</v>
+        <v>0</v>
       </c>
       <c r="L44" s="24" t="n">
-        <v>0.269904</v>
+        <v>0.028243</v>
       </c>
       <c r="M44" s="25">
-        <f>IFERROR(subQ!M35/subQ!M34,"")</f>
+        <f>IFERROR(subQ!M35/subQ!M5,"")</f>
         <v/>
       </c>
       <c r="N44" s="24" t="n">
-        <v>0.269904</v>
+        <v>0.100377</v>
       </c>
       <c r="O44" s="24" t="n">
-        <v>0.269904</v>
+        <v>0.188433</v>
       </c>
       <c r="P44" s="24" t="n">
-        <v>0.269702</v>
+        <v>0.286426</v>
       </c>
       <c r="Q44" s="24" t="n">
-        <v>0.268903</v>
+        <v>0.399029</v>
       </c>
       <c r="R44" s="25">
-        <f>IFERROR(subQ!R35/subQ!R34,"")</f>
+        <f>IFERROR(subQ!R35/subQ!R5,"")</f>
         <v/>
       </c>
       <c r="S44" s="24" t="n">
-        <v>0.268502</v>
+        <v>0.489312</v>
       </c>
       <c r="T44" s="24" t="n">
-        <v>0.268502</v>
+        <v>0.543319</v>
       </c>
       <c r="U44" s="24" t="n">
-        <v>0.274602</v>
+        <v>0.612136</v>
       </c>
       <c r="V44" s="24" t="n">
-        <v>0.274603</v>
+        <v>0.693271</v>
       </c>
       <c r="W44" s="25">
-        <f>IFERROR(subQ!W35/subQ!W34,"")</f>
+        <f>IFERROR(subQ!W35/subQ!W5,"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>drv:매출기타</t>
+          <t>drv:OP조선</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -7830,217 +8083,324 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>매출기타 비중(/매출액)</t>
+          <t>OP조선 마진(/매출조선)</t>
         </is>
       </c>
       <c r="E45" s="21">
-        <f>IFERROR(subQ!E36/subQ!E5,"")</f>
+        <f>IFERROR(subQ!E36/subQ!E34,"")</f>
         <v/>
       </c>
       <c r="F45" s="21">
-        <f>IFERROR(subQ!F36/subQ!F5,"")</f>
+        <f>IFERROR(subQ!F36/subQ!F34,"")</f>
         <v/>
       </c>
       <c r="G45" s="21">
-        <f>IFERROR(subQ!G36/subQ!G5,"")</f>
+        <f>IFERROR(subQ!G36/subQ!G34,"")</f>
         <v/>
       </c>
       <c r="H45" s="22">
-        <f>IFERROR(subQ!H36/subQ!H5,"")</f>
+        <f>IFERROR(subQ!H36/subQ!H34,"")</f>
         <v/>
       </c>
       <c r="I45" s="21">
-        <f>IFERROR(subQ!I36/subQ!I5,"")</f>
+        <f>IFERROR(subQ!I36/subQ!I34,"")</f>
         <v/>
       </c>
       <c r="J45" s="23">
-        <f>IFERROR(subQ!J36/subQ!J5,"")</f>
+        <f>IFERROR(subQ!J36/subQ!J34,"")</f>
         <v/>
       </c>
       <c r="K45" s="24" t="n">
-        <v>0.00668</v>
+        <v>0.268404</v>
       </c>
       <c r="L45" s="24" t="n">
-        <v>0.00667</v>
+        <v>0.268402</v>
       </c>
       <c r="M45" s="25">
-        <f>IFERROR(subQ!M36/subQ!M5,"")</f>
+        <f>IFERROR(subQ!M36/subQ!M34,"")</f>
         <v/>
       </c>
       <c r="N45" s="24" t="n">
-        <v>0.006818</v>
+        <v>0.268404</v>
       </c>
       <c r="O45" s="24" t="n">
-        <v>0.006743</v>
+        <v>0.268404</v>
       </c>
       <c r="P45" s="24" t="n">
-        <v>0.007051</v>
+        <v>0.268403</v>
       </c>
       <c r="Q45" s="24" t="n">
-        <v>0.008081</v>
+        <v>0.268403</v>
       </c>
       <c r="R45" s="25">
-        <f>IFERROR(subQ!R36/subQ!R5,"")</f>
+        <f>IFERROR(subQ!R36/subQ!R34,"")</f>
         <v/>
       </c>
       <c r="S45" s="24" t="n">
-        <v>0.008817999999999999</v>
+        <v>0.268402</v>
       </c>
       <c r="T45" s="24" t="n">
-        <v>0.008817999999999999</v>
+        <v>0.268403</v>
       </c>
       <c r="U45" s="24" t="n">
-        <v>0.009927999999999999</v>
+        <v>0.268403</v>
       </c>
       <c r="V45" s="24" t="n">
-        <v>0.012627</v>
+        <v>0.268404</v>
       </c>
       <c r="W45" s="25">
-        <f>IFERROR(subQ!W36/subQ!W5,"")</f>
+        <f>IFERROR(subQ!W36/subQ!W34,"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
+          <t>drv:OP조선신규</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OP조선신규 마진(/매출조선신규)</t>
+        </is>
+      </c>
+      <c r="E46" s="21">
+        <f>IFERROR(subQ!E37/subQ!E35,"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="21">
+        <f>IFERROR(subQ!F37/subQ!F35,"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="21">
+        <f>IFERROR(subQ!G37/subQ!G35,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="22">
+        <f>IFERROR(subQ!H37/subQ!H35,"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="21">
+        <f>IFERROR(subQ!I37/subQ!I35,"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="23">
+        <f>IFERROR(subQ!J37/subQ!J35,"")</f>
+        <v/>
+      </c>
+      <c r="K46" s="31" t="n"/>
+      <c r="L46" s="24" t="n">
+        <v>0.268472</v>
+      </c>
+      <c r="M46" s="25">
+        <f>IFERROR(subQ!M37/subQ!M35,"")</f>
+        <v/>
+      </c>
+      <c r="N46" s="24" t="n">
+        <v>0.268415</v>
+      </c>
+      <c r="O46" s="24" t="n">
+        <v>0.268405</v>
+      </c>
+      <c r="P46" s="24" t="n">
+        <v>0.268406</v>
+      </c>
+      <c r="Q46" s="24" t="n">
+        <v>0.268403</v>
+      </c>
+      <c r="R46" s="25">
+        <f>IFERROR(subQ!R37/subQ!R35,"")</f>
+        <v/>
+      </c>
+      <c r="S46" s="24" t="n">
+        <v>0.268404</v>
+      </c>
+      <c r="T46" s="24" t="n">
+        <v>0.268405</v>
+      </c>
+      <c r="U46" s="24" t="n">
+        <v>0.268403</v>
+      </c>
+      <c r="V46" s="24" t="n">
+        <v>0.268402</v>
+      </c>
+      <c r="W46" s="25">
+        <f>IFERROR(subQ!W37/subQ!W35,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>drv:매출기타</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>매출기타 비중(/매출액)</t>
+        </is>
+      </c>
+      <c r="E47" s="21">
+        <f>IFERROR(subQ!E38/subQ!E5,"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="21">
+        <f>IFERROR(subQ!F38/subQ!F5,"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="21">
+        <f>IFERROR(subQ!G38/subQ!G5,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="22">
+        <f>IFERROR(subQ!H38/subQ!H5,"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="21">
+        <f>IFERROR(subQ!I38/subQ!I5,"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="23">
+        <f>IFERROR(subQ!J38/subQ!J5,"")</f>
+        <v/>
+      </c>
+      <c r="K47" s="24" t="n">
+        <v>0.007707</v>
+      </c>
+      <c r="L47" s="24" t="n">
+        <v>0.007461</v>
+      </c>
+      <c r="M47" s="25">
+        <f>IFERROR(subQ!M38/subQ!M5,"")</f>
+        <v/>
+      </c>
+      <c r="N47" s="24" t="n">
+        <v>0.00706</v>
+      </c>
+      <c r="O47" s="24" t="n">
+        <v>0.006299</v>
+      </c>
+      <c r="P47" s="24" t="n">
+        <v>0.005788</v>
+      </c>
+      <c r="Q47" s="24" t="n">
+        <v>0.005577</v>
+      </c>
+      <c r="R47" s="25">
+        <f>IFERROR(subQ!R38/subQ!R5,"")</f>
+        <v/>
+      </c>
+      <c r="S47" s="24" t="n">
+        <v>0.005166</v>
+      </c>
+      <c r="T47" s="24" t="n">
+        <v>0.00462</v>
+      </c>
+      <c r="U47" s="24" t="n">
+        <v>0.004409</v>
+      </c>
+      <c r="V47" s="24" t="n">
+        <v>0.004415</v>
+      </c>
+      <c r="W47" s="25">
+        <f>IFERROR(subQ!W38/subQ!W5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
           <t>drv:OP기타</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>OP기타 마진(/매출기타)</t>
         </is>
       </c>
-      <c r="E46" s="21">
-        <f>IFERROR(subQ!E37/subQ!E36,"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="21">
-        <f>IFERROR(subQ!F37/subQ!F36,"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="21">
-        <f>IFERROR(subQ!G37/subQ!G36,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="22">
-        <f>IFERROR(subQ!H37/subQ!H36,"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="21">
-        <f>IFERROR(subQ!I37/subQ!I36,"")</f>
-        <v/>
-      </c>
-      <c r="J46" s="23">
-        <f>IFERROR(subQ!J37/subQ!J36,"")</f>
-        <v/>
-      </c>
-      <c r="K46" s="24" t="n">
-        <v>0.269944</v>
-      </c>
-      <c r="L46" s="24" t="n">
-        <v>0.269944</v>
-      </c>
-      <c r="M46" s="25">
-        <f>IFERROR(subQ!M37/subQ!M36,"")</f>
-        <v/>
-      </c>
-      <c r="N46" s="24" t="n">
-        <v>0.269944</v>
-      </c>
-      <c r="O46" s="24" t="n">
-        <v>0.269944</v>
-      </c>
-      <c r="P46" s="24" t="n">
-        <v>0.269481</v>
-      </c>
-      <c r="Q46" s="24" t="n">
-        <v>0.269017</v>
-      </c>
-      <c r="R46" s="25">
-        <f>IFERROR(subQ!R37/subQ!R36,"")</f>
-        <v/>
-      </c>
-      <c r="S46" s="24" t="n">
+      <c r="E48" s="21">
+        <f>IFERROR(subQ!E39/subQ!E38,"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="21">
+        <f>IFERROR(subQ!F39/subQ!F38,"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="21">
+        <f>IFERROR(subQ!G39/subQ!G38,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="22">
+        <f>IFERROR(subQ!H39/subQ!H38,"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="21">
+        <f>IFERROR(subQ!I39/subQ!I38,"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="23">
+        <f>IFERROR(subQ!J39/subQ!J38,"")</f>
+        <v/>
+      </c>
+      <c r="K48" s="24" t="n">
         <v>0.268553</v>
       </c>
-      <c r="T46" s="24" t="n">
+      <c r="L48" s="24" t="n">
         <v>0.268553</v>
       </c>
-      <c r="U46" s="24" t="n">
-        <v>0.274583</v>
-      </c>
-      <c r="V46" s="24" t="n">
-        <v>0.274583</v>
-      </c>
-      <c r="W46" s="25">
-        <f>IFERROR(subQ!W37/subQ!W36,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="H47" s="9" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="10" t="n"/>
-      <c r="L47" s="10" t="n"/>
-      <c r="M47" s="11" t="n"/>
-      <c r="N47" s="10" t="n"/>
-      <c r="O47" s="10" t="n"/>
-      <c r="P47" s="10" t="n"/>
-      <c r="Q47" s="10" t="n"/>
-      <c r="R47" s="11" t="n"/>
-      <c r="S47" s="10" t="n"/>
-      <c r="T47" s="10" t="n"/>
-      <c r="U47" s="10" t="n"/>
-      <c r="V47" s="10" t="n"/>
-      <c r="W47" s="11" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="H48" s="9" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="10" t="n"/>
-      <c r="L48" s="10" t="n"/>
-      <c r="M48" s="11" t="n"/>
-      <c r="N48" s="10" t="n"/>
-      <c r="O48" s="10" t="n"/>
-      <c r="P48" s="10" t="n"/>
-      <c r="Q48" s="10" t="n"/>
-      <c r="R48" s="11" t="n"/>
-      <c r="S48" s="10" t="n"/>
-      <c r="T48" s="10" t="n"/>
-      <c r="U48" s="10" t="n"/>
-      <c r="V48" s="10" t="n"/>
-      <c r="W48" s="11" t="n"/>
+      <c r="M48" s="25">
+        <f>IFERROR(subQ!M39/subQ!M38,"")</f>
+        <v/>
+      </c>
+      <c r="N48" s="24" t="n">
+        <v>0.268553</v>
+      </c>
+      <c r="O48" s="24" t="n">
+        <v>0.268553</v>
+      </c>
+      <c r="P48" s="24" t="n">
+        <v>0.268553</v>
+      </c>
+      <c r="Q48" s="24" t="n">
+        <v>0.268553</v>
+      </c>
+      <c r="R48" s="25">
+        <f>IFERROR(subQ!R39/subQ!R38,"")</f>
+        <v/>
+      </c>
+      <c r="S48" s="24" t="n">
+        <v>0.268553</v>
+      </c>
+      <c r="T48" s="24" t="n">
+        <v>0.268553</v>
+      </c>
+      <c r="U48" s="24" t="n">
+        <v>0.268553</v>
+      </c>
+      <c r="V48" s="24" t="n">
+        <v>0.268553</v>
+      </c>
+      <c r="W48" s="25">
+        <f>IFERROR(subQ!W39/subQ!W38,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>sc:종가</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D49" s="32" t="n">
-        <v>45050</v>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>원 — aikstockdata(금융위 T+1)</t>
-        </is>
-      </c>
       <c r="H49" s="9" t="n"/>
       <c r="J49" s="5" t="n"/>
       <c r="K49" s="10" t="n"/>
@@ -8058,24 +8418,9 @@
       <c r="W49" s="11" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>sc:기준일</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D50" s="33" t="inlineStr">
-        <is>
-          <t>20260929</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>종가 기준일</t>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
         </is>
       </c>
       <c r="H50" s="9" t="n"/>
@@ -8097,20 +8442,20 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:종가</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="n">
-        <v>0.09</v>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="n">
+        <v>45050</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>자기자본비용(가정)</t>
+          <t>원 — aikstockdata(금융위 T+1)</t>
         </is>
       </c>
       <c r="H51" s="9" t="n"/>
@@ -8132,20 +8477,22 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PER_lo</t>
-        </is>
-      </c>
-      <c r="D52" s="29" t="n">
-        <v>10</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D52" s="33" t="inlineStr">
+        <is>
+          <t>20260929</t>
+        </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 2개 &lt; 4)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="H52" s="9" t="n"/>
@@ -8167,20 +8514,20 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PER_mid</t>
-        </is>
-      </c>
-      <c r="D53" s="29" t="n">
-        <v>15</v>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="n">
+        <v>0.09</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>자기자본비용(가정)</t>
         </is>
       </c>
       <c r="H53" s="9" t="n"/>
@@ -8202,20 +8549,20 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PER_hi</t>
+          <t>PER_lo</t>
         </is>
       </c>
       <c r="D54" s="29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 2개 &lt; 4)</t>
         </is>
       </c>
       <c r="H54" s="9" t="n"/>
@@ -8237,20 +8584,20 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D55" s="24" t="n">
-        <v>0.5</v>
+          <t>PER_mid</t>
+        </is>
+      </c>
+      <c r="D55" s="29" t="n">
+        <v>15</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="H55" s="9" t="n"/>
@@ -8272,20 +8619,20 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>세율</t>
-        </is>
-      </c>
-      <c r="D56" s="24" t="n">
-        <v>0.2276</v>
+          <t>PER_hi</t>
+        </is>
+      </c>
+      <c r="D56" s="29" t="n">
+        <v>20</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>법인세율 가정(참고 — 추정 수식은 드라이버 행 참조)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="H56" s="9" t="n"/>
@@ -8307,20 +8654,20 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>판관비율</t>
+          <t>EPS_Y1가중</t>
         </is>
       </c>
       <c r="D57" s="24" t="n">
-        <v>0.0244</v>
+        <v>0.5</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>판관비율 가정(참고)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="H57" s="9" t="n"/>
@@ -8342,20 +8689,20 @@
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>배당성향</t>
+          <t>세율</t>
         </is>
       </c>
       <c r="D58" s="24" t="n">
-        <v>0.0506</v>
+        <v>0.2276</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>배당성향 가정(참고)</t>
+          <t>법인세율 가정(참고 — 추정 수식은 드라이버 행 참조)</t>
         </is>
       </c>
       <c r="H58" s="9" t="n"/>
@@ -8377,20 +8724,20 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D59" s="29" t="n">
-        <v>-2.29</v>
+          <t>판관비율</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="n">
+        <v>0.0244</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식)</t>
+          <t>판관비율 가정(참고)</t>
         </is>
       </c>
       <c r="H59" s="9" t="n"/>
@@ -8409,6 +8756,76 @@
       <c r="V59" s="10" t="n"/>
       <c r="W59" s="11" t="n"/>
     </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>sc:배당성향</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>배당성향 가정(참고)</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="11" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="11" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="11" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>sc:외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식)</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="11" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="11" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="11" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -8421,7 +8838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W86"/>
+  <dimension ref="A1:W95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8569,7 +8986,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -11278,14 +11695,25 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>(비지배주주지분)당기순이익</t>
-        </is>
+          <t>이자수익</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>2114.83</v>
+      </c>
+      <c r="F71" s="18" t="n">
+        <v>1882.76</v>
+      </c>
+      <c r="G71" s="18" t="n">
+        <v>1433</v>
       </c>
       <c r="H71" s="9" t="n"/>
       <c r="I71" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="5" t="n"/>
+        <v>2174.68</v>
+      </c>
+      <c r="J71" s="19" t="n">
+        <v>2907.16</v>
+      </c>
       <c r="K71" s="10" t="n"/>
       <c r="L71" s="10" t="n"/>
       <c r="M71" s="11" t="n"/>
@@ -11306,24 +11734,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
-        <v>42623.28</v>
+        <v>2942.13</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>-1016.39</v>
+        <v>1631.27</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>-13065.17</v>
+        <v>165</v>
       </c>
       <c r="H72" s="9" t="n"/>
       <c r="I72" s="18" t="n">
-        <v>118064.13</v>
+        <v>6.35</v>
       </c>
       <c r="J72" s="19" t="n">
-        <v>169860.18</v>
+        <v>5.8</v>
       </c>
       <c r="K72" s="10" t="n"/>
       <c r="L72" s="10" t="n"/>
@@ -11345,24 +11773,24 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="E73" s="18" t="n">
-        <v>2258.48</v>
+        <v>2614.11</v>
       </c>
       <c r="F73" s="18" t="n">
-        <v>1866.48</v>
+        <v>1129.45</v>
       </c>
       <c r="G73" s="18" t="n">
-        <v>1454.4</v>
+        <v>22.81</v>
       </c>
       <c r="H73" s="9" t="n"/>
       <c r="I73" s="18" t="n">
-        <v>1669.98</v>
+        <v>563.91</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>1721.35</v>
+        <v>130.68</v>
       </c>
       <c r="K73" s="10" t="n"/>
       <c r="L73" s="10" t="n"/>
@@ -11384,24 +11812,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>외환차손</t>
         </is>
       </c>
       <c r="E74" s="18" t="n">
-        <v>-4172.35</v>
+        <v>437.01</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>-2978.26</v>
+        <v>1404.05</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>-202.05</v>
+        <v>980.11</v>
       </c>
       <c r="H74" s="9" t="n"/>
       <c r="I74" s="18" t="n">
-        <v>-6.35</v>
+        <v>1.48</v>
       </c>
       <c r="J74" s="19" t="n">
-        <v>-5.8</v>
+        <v>15.45</v>
       </c>
       <c r="K74" s="10" t="n"/>
       <c r="L74" s="10" t="n"/>
@@ -11423,24 +11851,24 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>외화환산이익</t>
         </is>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-3007.12</v>
+        <v>752.37</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-2288.96</v>
+        <v>-1763.38</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-503.47</v>
+        <v>-23.2</v>
       </c>
       <c r="H75" s="9" t="n"/>
       <c r="I75" s="18" t="n">
-        <v>-7574.23</v>
+        <v>7913.26</v>
       </c>
       <c r="J75" s="19" t="n">
-        <v>-15296.51</v>
+        <v>3102.6</v>
       </c>
       <c r="K75" s="10" t="n"/>
       <c r="L75" s="10" t="n"/>
@@ -11462,25 +11890,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>외화환산손실</t>
         </is>
       </c>
       <c r="E76" s="18" t="n">
-        <v>5984.42</v>
+        <v>11317.13</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>-273488.49</v>
+        <v>-6383.08</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-47383.78</v>
+        <v>-2074.13</v>
       </c>
       <c r="H76" s="9" t="n"/>
-      <c r="I76" s="18" t="n">
-        <v>-24852.15</v>
-      </c>
-      <c r="J76" s="19" t="n">
-        <v>-111821.84</v>
-      </c>
+      <c r="J76" s="5" t="n"/>
       <c r="K76" s="10" t="n"/>
       <c r="L76" s="10" t="n"/>
       <c r="M76" s="11" t="n"/>
@@ -11501,24 +11924,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
+          <t>파생상품이익</t>
         </is>
       </c>
       <c r="E77" s="18" t="n">
-        <v>0</v>
+        <v>71361.41</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>11.18</v>
+        <v>-34967.9</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>138.43</v>
+        <v>-17898.82</v>
       </c>
       <c r="H77" s="9" t="n"/>
       <c r="I77" s="18" t="n">
-        <v>120</v>
+        <v>17.12</v>
       </c>
       <c r="J77" s="19" t="n">
-        <v>6.94</v>
+        <v>34.32</v>
       </c>
       <c r="K77" s="10" t="n"/>
       <c r="L77" s="10" t="n"/>
@@ -11540,24 +11963,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>파생상품손실</t>
         </is>
       </c>
       <c r="E78" s="18" t="n">
-        <v>2791.63</v>
+        <v>-4816.63</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>3523.49</v>
+        <v>265.45</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>1897.06</v>
+        <v>7760.15</v>
       </c>
       <c r="H78" s="9" t="n"/>
       <c r="I78" s="18" t="n">
-        <v>2097.87</v>
+        <v>55428.32</v>
       </c>
       <c r="J78" s="19" t="n">
-        <v>6409.19</v>
+        <v>33094.33</v>
       </c>
       <c r="K78" s="10" t="n"/>
       <c r="L78" s="10" t="n"/>
@@ -11579,24 +12002,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>이자손익</t>
         </is>
       </c>
       <c r="E79" s="18" t="n">
-        <v>2791.63</v>
+        <v>-827.3</v>
       </c>
       <c r="F79" s="18" t="n">
-        <v>3530.99</v>
+        <v>251.49</v>
       </c>
       <c r="G79" s="18" t="n">
-        <v>2072.06</v>
+        <v>1268</v>
       </c>
       <c r="H79" s="9" t="n"/>
       <c r="I79" s="18" t="n">
-        <v>2102.03</v>
+        <v>2168.33</v>
       </c>
       <c r="J79" s="19" t="n">
-        <v>7231.59</v>
+        <v>2901.36</v>
       </c>
       <c r="K79" s="10" t="n"/>
       <c r="L79" s="10" t="n"/>
@@ -11618,25 +12041,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" s="18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G80" s="18" t="n">
-        <v>175</v>
+          <t>(비지배주주지분)당기순이익</t>
+        </is>
       </c>
       <c r="H80" s="9" t="n"/>
       <c r="I80" s="18" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="J80" s="19" t="n">
-        <v>822.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J80" s="5" t="n"/>
       <c r="K80" s="10" t="n"/>
       <c r="L80" s="10" t="n"/>
       <c r="M80" s="11" t="n"/>
@@ -11657,24 +12069,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E81" s="18" t="n">
-        <v>-35478.63</v>
+        <v>42623.28</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>188321.79</v>
+        <v>-1016.39</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>-23696.36</v>
+        <v>-13065.17</v>
       </c>
       <c r="H81" s="9" t="n"/>
       <c r="I81" s="18" t="n">
-        <v>-24948.67</v>
+        <v>118064.13</v>
       </c>
       <c r="J81" s="19" t="n">
-        <v>-24769.83</v>
+        <v>169860.18</v>
       </c>
       <c r="K81" s="10" t="n"/>
       <c r="L81" s="10" t="n"/>
@@ -11696,23 +12108,25 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E82" s="18" t="n">
-        <v>126468.73</v>
+        <v>2258.48</v>
       </c>
       <c r="F82" s="18" t="n">
-        <v>69339.03</v>
+        <v>1866.48</v>
       </c>
       <c r="G82" s="18" t="n">
-        <v>20859.87</v>
+        <v>1454.4</v>
       </c>
       <c r="H82" s="9" t="n"/>
       <c r="I82" s="18" t="n">
-        <v>1037.52</v>
-      </c>
-      <c r="J82" s="5" t="n"/>
+        <v>1669.98</v>
+      </c>
+      <c r="J82" s="19" t="n">
+        <v>1721.35</v>
+      </c>
       <c r="K82" s="10" t="n"/>
       <c r="L82" s="10" t="n"/>
       <c r="M82" s="11" t="n"/>
@@ -11733,24 +12147,24 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>161905.38</v>
+        <v>-4172.35</v>
       </c>
       <c r="F83" s="18" t="n">
-        <v>234849.35</v>
+        <v>-2978.26</v>
       </c>
       <c r="G83" s="18" t="n">
-        <v>44512.19</v>
+        <v>-202.05</v>
       </c>
       <c r="H83" s="9" t="n"/>
       <c r="I83" s="18" t="n">
-        <v>58.26</v>
+        <v>-6.35</v>
       </c>
       <c r="J83" s="19" t="n">
-        <v>0</v>
+        <v>-5.8</v>
       </c>
       <c r="K83" s="10" t="n"/>
       <c r="L83" s="10" t="n"/>
@@ -11772,24 +12186,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>41.98</v>
+        <v>-3007.12</v>
       </c>
       <c r="F84" s="18" t="n">
-        <v>82.08</v>
+        <v>-2288.96</v>
       </c>
       <c r="G84" s="18" t="n">
-        <v>44.04</v>
+        <v>-503.47</v>
       </c>
       <c r="H84" s="9" t="n"/>
       <c r="I84" s="18" t="n">
-        <v>44.91</v>
+        <v>-7574.23</v>
       </c>
       <c r="J84" s="19" t="n">
-        <v>42.05</v>
+        <v>-15296.51</v>
       </c>
       <c r="K84" s="10" t="n"/>
       <c r="L84" s="10" t="n"/>
@@ -11811,24 +12225,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>652.24</v>
+        <v>5984.42</v>
       </c>
       <c r="F85" s="18" t="n">
-        <v>-79484.48</v>
+        <v>-273488.49</v>
       </c>
       <c r="G85" s="18" t="n">
-        <v>-81621.38</v>
+        <v>-47383.78</v>
       </c>
       <c r="H85" s="9" t="n"/>
       <c r="I85" s="18" t="n">
-        <v>74829.36</v>
+        <v>-24852.15</v>
       </c>
       <c r="J85" s="19" t="n">
-        <v>35753.27</v>
+        <v>-111821.84</v>
       </c>
       <c r="K85" s="10" t="n"/>
       <c r="L85" s="10" t="n"/>
@@ -11850,24 +12264,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>652.25</v>
+        <v>0</v>
       </c>
       <c r="F86" s="18" t="n">
-        <v>-79484.48</v>
+        <v>11.18</v>
       </c>
       <c r="G86" s="18" t="n">
-        <v>-81621.38</v>
+        <v>138.43</v>
       </c>
       <c r="H86" s="9" t="n"/>
       <c r="I86" s="18" t="n">
-        <v>290133.13</v>
+        <v>120</v>
       </c>
       <c r="J86" s="19" t="n">
-        <v>35753.28</v>
+        <v>6.94</v>
       </c>
       <c r="K86" s="10" t="n"/>
       <c r="L86" s="10" t="n"/>
@@ -11882,6 +12296,355 @@
       <c r="U86" s="10" t="n"/>
       <c r="V86" s="10" t="n"/>
       <c r="W86" s="11" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>2791.63</v>
+      </c>
+      <c r="F87" s="18" t="n">
+        <v>3523.49</v>
+      </c>
+      <c r="G87" s="18" t="n">
+        <v>1897.06</v>
+      </c>
+      <c r="H87" s="9" t="n"/>
+      <c r="I87" s="18" t="n">
+        <v>2097.87</v>
+      </c>
+      <c r="J87" s="19" t="n">
+        <v>6409.19</v>
+      </c>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="10" t="n"/>
+      <c r="M87" s="11" t="n"/>
+      <c r="N87" s="10" t="n"/>
+      <c r="O87" s="10" t="n"/>
+      <c r="P87" s="10" t="n"/>
+      <c r="Q87" s="10" t="n"/>
+      <c r="R87" s="11" t="n"/>
+      <c r="S87" s="10" t="n"/>
+      <c r="T87" s="10" t="n"/>
+      <c r="U87" s="10" t="n"/>
+      <c r="V87" s="10" t="n"/>
+      <c r="W87" s="11" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="n">
+        <v>2791.63</v>
+      </c>
+      <c r="F88" s="18" t="n">
+        <v>3530.99</v>
+      </c>
+      <c r="G88" s="18" t="n">
+        <v>2072.06</v>
+      </c>
+      <c r="H88" s="9" t="n"/>
+      <c r="I88" s="18" t="n">
+        <v>2102.03</v>
+      </c>
+      <c r="J88" s="19" t="n">
+        <v>7231.59</v>
+      </c>
+      <c r="K88" s="10" t="n"/>
+      <c r="L88" s="10" t="n"/>
+      <c r="M88" s="11" t="n"/>
+      <c r="N88" s="10" t="n"/>
+      <c r="O88" s="10" t="n"/>
+      <c r="P88" s="10" t="n"/>
+      <c r="Q88" s="10" t="n"/>
+      <c r="R88" s="11" t="n"/>
+      <c r="S88" s="10" t="n"/>
+      <c r="T88" s="10" t="n"/>
+      <c r="U88" s="10" t="n"/>
+      <c r="V88" s="10" t="n"/>
+      <c r="W88" s="11" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G89" s="18" t="n">
+        <v>175</v>
+      </c>
+      <c r="H89" s="9" t="n"/>
+      <c r="I89" s="18" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="J89" s="19" t="n">
+        <v>822.4</v>
+      </c>
+      <c r="K89" s="10" t="n"/>
+      <c r="L89" s="10" t="n"/>
+      <c r="M89" s="11" t="n"/>
+      <c r="N89" s="10" t="n"/>
+      <c r="O89" s="10" t="n"/>
+      <c r="P89" s="10" t="n"/>
+      <c r="Q89" s="10" t="n"/>
+      <c r="R89" s="11" t="n"/>
+      <c r="S89" s="10" t="n"/>
+      <c r="T89" s="10" t="n"/>
+      <c r="U89" s="10" t="n"/>
+      <c r="V89" s="10" t="n"/>
+      <c r="W89" s="11" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>-35478.63</v>
+      </c>
+      <c r="F90" s="18" t="n">
+        <v>188321.79</v>
+      </c>
+      <c r="G90" s="18" t="n">
+        <v>-23696.36</v>
+      </c>
+      <c r="H90" s="9" t="n"/>
+      <c r="I90" s="18" t="n">
+        <v>-24948.67</v>
+      </c>
+      <c r="J90" s="19" t="n">
+        <v>-24769.83</v>
+      </c>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="11" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="11" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="11" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>126468.73</v>
+      </c>
+      <c r="F91" s="18" t="n">
+        <v>69339.03</v>
+      </c>
+      <c r="G91" s="18" t="n">
+        <v>20859.87</v>
+      </c>
+      <c r="H91" s="9" t="n"/>
+      <c r="I91" s="18" t="n">
+        <v>1037.52</v>
+      </c>
+      <c r="J91" s="5" t="n"/>
+      <c r="K91" s="10" t="n"/>
+      <c r="L91" s="10" t="n"/>
+      <c r="M91" s="11" t="n"/>
+      <c r="N91" s="10" t="n"/>
+      <c r="O91" s="10" t="n"/>
+      <c r="P91" s="10" t="n"/>
+      <c r="Q91" s="10" t="n"/>
+      <c r="R91" s="11" t="n"/>
+      <c r="S91" s="10" t="n"/>
+      <c r="T91" s="10" t="n"/>
+      <c r="U91" s="10" t="n"/>
+      <c r="V91" s="10" t="n"/>
+      <c r="W91" s="11" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>161905.38</v>
+      </c>
+      <c r="F92" s="18" t="n">
+        <v>234849.35</v>
+      </c>
+      <c r="G92" s="18" t="n">
+        <v>44512.19</v>
+      </c>
+      <c r="H92" s="9" t="n"/>
+      <c r="I92" s="18" t="n">
+        <v>58.26</v>
+      </c>
+      <c r="J92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="10" t="n"/>
+      <c r="L92" s="10" t="n"/>
+      <c r="M92" s="11" t="n"/>
+      <c r="N92" s="10" t="n"/>
+      <c r="O92" s="10" t="n"/>
+      <c r="P92" s="10" t="n"/>
+      <c r="Q92" s="10" t="n"/>
+      <c r="R92" s="11" t="n"/>
+      <c r="S92" s="10" t="n"/>
+      <c r="T92" s="10" t="n"/>
+      <c r="U92" s="10" t="n"/>
+      <c r="V92" s="10" t="n"/>
+      <c r="W92" s="11" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="F93" s="18" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="G93" s="18" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="H93" s="9" t="n"/>
+      <c r="I93" s="18" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="J93" s="19" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="K93" s="10" t="n"/>
+      <c r="L93" s="10" t="n"/>
+      <c r="M93" s="11" t="n"/>
+      <c r="N93" s="10" t="n"/>
+      <c r="O93" s="10" t="n"/>
+      <c r="P93" s="10" t="n"/>
+      <c r="Q93" s="10" t="n"/>
+      <c r="R93" s="11" t="n"/>
+      <c r="S93" s="10" t="n"/>
+      <c r="T93" s="10" t="n"/>
+      <c r="U93" s="10" t="n"/>
+      <c r="V93" s="10" t="n"/>
+      <c r="W93" s="11" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>652.24</v>
+      </c>
+      <c r="F94" s="18" t="n">
+        <v>-79484.48</v>
+      </c>
+      <c r="G94" s="18" t="n">
+        <v>-81621.38</v>
+      </c>
+      <c r="H94" s="9" t="n"/>
+      <c r="I94" s="18" t="n">
+        <v>74829.36</v>
+      </c>
+      <c r="J94" s="19" t="n">
+        <v>35753.27</v>
+      </c>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="10" t="n"/>
+      <c r="M94" s="11" t="n"/>
+      <c r="N94" s="10" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="10" t="n"/>
+      <c r="R94" s="11" t="n"/>
+      <c r="S94" s="10" t="n"/>
+      <c r="T94" s="10" t="n"/>
+      <c r="U94" s="10" t="n"/>
+      <c r="V94" s="10" t="n"/>
+      <c r="W94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>652.25</v>
+      </c>
+      <c r="F95" s="18" t="n">
+        <v>-79484.48</v>
+      </c>
+      <c r="G95" s="18" t="n">
+        <v>-81621.38</v>
+      </c>
+      <c r="H95" s="9" t="n"/>
+      <c r="I95" s="18" t="n">
+        <v>290133.13</v>
+      </c>
+      <c r="J95" s="19" t="n">
+        <v>35753.28</v>
+      </c>
+      <c r="K95" s="10" t="n"/>
+      <c r="L95" s="10" t="n"/>
+      <c r="M95" s="11" t="n"/>
+      <c r="N95" s="10" t="n"/>
+      <c r="O95" s="10" t="n"/>
+      <c r="P95" s="10" t="n"/>
+      <c r="Q95" s="10" t="n"/>
+      <c r="R95" s="11" t="n"/>
+      <c r="S95" s="10" t="n"/>
+      <c r="T95" s="10" t="n"/>
+      <c r="U95" s="10" t="n"/>
+      <c r="V95" s="10" t="n"/>
+      <c r="W95" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12042,7 +12805,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15293,7 +16056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W42"/>
+  <dimension ref="A1:W44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17981,10 +18744,10 @@
         <v>9.57</v>
       </c>
       <c r="K32" s="20" t="n">
-        <v>5.67</v>
+        <v>5.85</v>
       </c>
       <c r="L32" s="20" t="n">
-        <v>5.83</v>
+        <v>6.18</v>
       </c>
       <c r="M32" s="35">
         <f>SUM(I32:L32)</f>
@@ -18212,7 +18975,7 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>OP조선</t>
+          <t>매출조선신규</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -18227,21 +18990,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OP 조선·해양(선박)</t>
+          <t>매출 조선·해양(선박) 신규수주(forecast_panel base — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E35" s="18" t="n"/>
       <c r="F35" s="18" t="n"/>
       <c r="G35" s="18" t="n"/>
       <c r="H35" s="34" t="n"/>
-      <c r="I35" s="18" t="n"/>
-      <c r="J35" s="19" t="n"/>
+      <c r="I35" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="K35" s="20">
-        <f>IFERROR(K34*변수!K44,"")</f>
+        <f>IFERROR(K5*변수!K44,"")</f>
         <v/>
       </c>
       <c r="L35" s="20">
-        <f>IFERROR(L34*변수!L44,"")</f>
+        <f>IFERROR(L5*변수!L44,"")</f>
         <v/>
       </c>
       <c r="M35" s="35">
@@ -18249,19 +19016,19 @@
         <v/>
       </c>
       <c r="N35" s="20">
-        <f>IFERROR(N34*변수!N44,"")</f>
+        <f>IFERROR(N5*변수!N44,"")</f>
         <v/>
       </c>
       <c r="O35" s="20">
-        <f>IFERROR(O34*변수!O44,"")</f>
+        <f>IFERROR(O5*변수!O44,"")</f>
         <v/>
       </c>
       <c r="P35" s="20">
-        <f>IFERROR(P34*변수!P44,"")</f>
+        <f>IFERROR(P5*변수!P44,"")</f>
         <v/>
       </c>
       <c r="Q35" s="20">
-        <f>IFERROR(Q34*변수!Q44,"")</f>
+        <f>IFERROR(Q5*변수!Q44,"")</f>
         <v/>
       </c>
       <c r="R35" s="35">
@@ -18269,19 +19036,19 @@
         <v/>
       </c>
       <c r="S35" s="20">
-        <f>IFERROR(S34*변수!S44,"")</f>
+        <f>IFERROR(S5*변수!S44,"")</f>
         <v/>
       </c>
       <c r="T35" s="20">
-        <f>IFERROR(T34*변수!T44,"")</f>
+        <f>IFERROR(T5*변수!T44,"")</f>
         <v/>
       </c>
       <c r="U35" s="20">
-        <f>IFERROR(U34*변수!U44,"")</f>
+        <f>IFERROR(U5*변수!U44,"")</f>
         <v/>
       </c>
       <c r="V35" s="20">
-        <f>IFERROR(V34*변수!V44,"")</f>
+        <f>IFERROR(V5*변수!V44,"")</f>
         <v/>
       </c>
       <c r="W35" s="35">
@@ -18292,7 +19059,7 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>매출기타</t>
+          <t>OP조선</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -18307,29 +19074,21 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>매출 기타 부문(총매출 − 조선)</t>
+          <t>OP 조선·해양(선박)</t>
         </is>
       </c>
       <c r="E36" s="18" t="n"/>
-      <c r="F36" s="18" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="G36" s="18" t="n">
-        <v>22.56</v>
-      </c>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
       <c r="H36" s="34" t="n"/>
-      <c r="I36" s="18" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="J36" s="19" t="n">
-        <v>30.33</v>
-      </c>
+      <c r="I36" s="18" t="n"/>
+      <c r="J36" s="19" t="n"/>
       <c r="K36" s="20">
-        <f>IFERROR(K5*변수!K45,"")</f>
+        <f>IFERROR(K34*변수!K45,"")</f>
         <v/>
       </c>
       <c r="L36" s="20">
-        <f>IFERROR(L5*변수!L45,"")</f>
+        <f>IFERROR(L34*변수!L45,"")</f>
         <v/>
       </c>
       <c r="M36" s="35">
@@ -18337,19 +19096,19 @@
         <v/>
       </c>
       <c r="N36" s="20">
-        <f>IFERROR(N5*변수!N45,"")</f>
+        <f>IFERROR(N34*변수!N45,"")</f>
         <v/>
       </c>
       <c r="O36" s="20">
-        <f>IFERROR(O5*변수!O45,"")</f>
+        <f>IFERROR(O34*변수!O45,"")</f>
         <v/>
       </c>
       <c r="P36" s="20">
-        <f>IFERROR(P5*변수!P45,"")</f>
+        <f>IFERROR(P34*변수!P45,"")</f>
         <v/>
       </c>
       <c r="Q36" s="20">
-        <f>IFERROR(Q5*변수!Q45,"")</f>
+        <f>IFERROR(Q34*변수!Q45,"")</f>
         <v/>
       </c>
       <c r="R36" s="35">
@@ -18357,19 +19116,19 @@
         <v/>
       </c>
       <c r="S36" s="20">
-        <f>IFERROR(S5*변수!S45,"")</f>
+        <f>IFERROR(S34*변수!S45,"")</f>
         <v/>
       </c>
       <c r="T36" s="20">
-        <f>IFERROR(T5*변수!T45,"")</f>
+        <f>IFERROR(T34*변수!T45,"")</f>
         <v/>
       </c>
       <c r="U36" s="20">
-        <f>IFERROR(U5*변수!U45,"")</f>
+        <f>IFERROR(U34*변수!U45,"")</f>
         <v/>
       </c>
       <c r="V36" s="20">
-        <f>IFERROR(V5*변수!V45,"")</f>
+        <f>IFERROR(V34*변수!V45,"")</f>
         <v/>
       </c>
       <c r="W36" s="35">
@@ -18380,7 +19139,7 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>OP기타</t>
+          <t>OP조선신규</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -18395,21 +19154,24 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OP 기타 부문(총매출 − 조선)</t>
+          <t>OP 조선·해양(선박) 신규수주(매출조선신규 × OPM — OP조선에 포함)</t>
         </is>
       </c>
       <c r="E37" s="18" t="n"/>
       <c r="F37" s="18" t="n"/>
       <c r="G37" s="18" t="n"/>
       <c r="H37" s="34" t="n"/>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="19" t="n"/>
-      <c r="K37" s="20">
-        <f>IFERROR(K36*변수!K46,"")</f>
-        <v/>
+      <c r="I37" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="L37" s="20">
-        <f>IFERROR(L36*변수!L46,"")</f>
+        <f>IFERROR(L35*변수!L46,"")</f>
         <v/>
       </c>
       <c r="M37" s="35">
@@ -18417,19 +19179,19 @@
         <v/>
       </c>
       <c r="N37" s="20">
-        <f>IFERROR(N36*변수!N46,"")</f>
+        <f>IFERROR(N35*변수!N46,"")</f>
         <v/>
       </c>
       <c r="O37" s="20">
-        <f>IFERROR(O36*변수!O46,"")</f>
+        <f>IFERROR(O35*변수!O46,"")</f>
         <v/>
       </c>
       <c r="P37" s="20">
-        <f>IFERROR(P36*변수!P46,"")</f>
+        <f>IFERROR(P35*변수!P46,"")</f>
         <v/>
       </c>
       <c r="Q37" s="20">
-        <f>IFERROR(Q36*변수!Q46,"")</f>
+        <f>IFERROR(Q35*변수!Q46,"")</f>
         <v/>
       </c>
       <c r="R37" s="35">
@@ -18437,19 +19199,19 @@
         <v/>
       </c>
       <c r="S37" s="20">
-        <f>IFERROR(S36*변수!S46,"")</f>
+        <f>IFERROR(S35*변수!S46,"")</f>
         <v/>
       </c>
       <c r="T37" s="20">
-        <f>IFERROR(T36*변수!T46,"")</f>
+        <f>IFERROR(T35*변수!T46,"")</f>
         <v/>
       </c>
       <c r="U37" s="20">
-        <f>IFERROR(U36*변수!U46,"")</f>
+        <f>IFERROR(U35*변수!U46,"")</f>
         <v/>
       </c>
       <c r="V37" s="20">
-        <f>IFERROR(V36*변수!V46,"")</f>
+        <f>IFERROR(V35*변수!V46,"")</f>
         <v/>
       </c>
       <c r="W37" s="35">
@@ -18458,217 +19220,199 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>비율(참고)</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="10" t="n"/>
-      <c r="L38" s="10" t="n"/>
-      <c r="M38" s="11" t="n"/>
-      <c r="N38" s="10" t="n"/>
-      <c r="O38" s="10" t="n"/>
-      <c r="P38" s="10" t="n"/>
-      <c r="Q38" s="10" t="n"/>
-      <c r="R38" s="11" t="n"/>
-      <c r="S38" s="10" t="n"/>
-      <c r="T38" s="10" t="n"/>
-      <c r="U38" s="10" t="n"/>
-      <c r="V38" s="10" t="n"/>
-      <c r="W38" s="11" t="n"/>
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>매출기타</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>매출 기타 부문(총매출 − 조선)</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="G38" s="18" t="n">
+        <v>22.56</v>
+      </c>
+      <c r="H38" s="34" t="n"/>
+      <c r="I38" s="18" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="J38" s="19" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="K38" s="20">
+        <f>IFERROR(K5*변수!K47,"")</f>
+        <v/>
+      </c>
+      <c r="L38" s="20">
+        <f>IFERROR(L5*변수!L47,"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="35">
+        <f>SUM(I38:L38)</f>
+        <v/>
+      </c>
+      <c r="N38" s="20">
+        <f>IFERROR(N5*변수!N47,"")</f>
+        <v/>
+      </c>
+      <c r="O38" s="20">
+        <f>IFERROR(O5*변수!O47,"")</f>
+        <v/>
+      </c>
+      <c r="P38" s="20">
+        <f>IFERROR(P5*변수!P47,"")</f>
+        <v/>
+      </c>
+      <c r="Q38" s="20">
+        <f>IFERROR(Q5*변수!Q47,"")</f>
+        <v/>
+      </c>
+      <c r="R38" s="35">
+        <f>SUM(N38:Q38)</f>
+        <v/>
+      </c>
+      <c r="S38" s="20">
+        <f>IFERROR(S5*변수!S47,"")</f>
+        <v/>
+      </c>
+      <c r="T38" s="20">
+        <f>IFERROR(T5*변수!T47,"")</f>
+        <v/>
+      </c>
+      <c r="U38" s="20">
+        <f>IFERROR(U5*변수!U47,"")</f>
+        <v/>
+      </c>
+      <c r="V38" s="20">
+        <f>IFERROR(V5*변수!V47,"")</f>
+        <v/>
+      </c>
+      <c r="W38" s="35">
+        <f>SUM(S38:V38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>OP기타</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>억원</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>영업이익 / 매출액</t>
-        </is>
-      </c>
-      <c r="E39" s="21">
-        <f>IFERROR(E9/E5,"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="21">
-        <f>IFERROR(F9/F5,"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="21">
-        <f>IFERROR(G9/G5,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="22">
-        <f>IFERROR(H9/H5,"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="21">
-        <f>IFERROR(I9/I5,"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="23">
-        <f>IFERROR(J9/J5,"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="31">
-        <f>IFERROR(K9/K5,"")</f>
-        <v/>
-      </c>
-      <c r="L39" s="31">
-        <f>IFERROR(L9/L5,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="25">
-        <f>IFERROR(M9/M5,"")</f>
-        <v/>
-      </c>
-      <c r="N39" s="31">
-        <f>IFERROR(N9/N5,"")</f>
-        <v/>
-      </c>
-      <c r="O39" s="31">
-        <f>IFERROR(O9/O5,"")</f>
-        <v/>
-      </c>
-      <c r="P39" s="31">
-        <f>IFERROR(P9/P5,"")</f>
-        <v/>
-      </c>
-      <c r="Q39" s="31">
-        <f>IFERROR(Q9/Q5,"")</f>
-        <v/>
-      </c>
-      <c r="R39" s="25">
-        <f>IFERROR(R9/R5,"")</f>
-        <v/>
-      </c>
-      <c r="S39" s="31">
-        <f>IFERROR(S9/S5,"")</f>
-        <v/>
-      </c>
-      <c r="T39" s="31">
-        <f>IFERROR(T9/T5,"")</f>
-        <v/>
-      </c>
-      <c r="U39" s="31">
-        <f>IFERROR(U9/U5,"")</f>
-        <v/>
-      </c>
-      <c r="V39" s="31">
-        <f>IFERROR(V9/V5,"")</f>
-        <v/>
-      </c>
-      <c r="W39" s="25">
-        <f>IFERROR(W9/W5,"")</f>
+          <t>OP 기타 부문(총매출 − 조선)</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="34" t="n"/>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="19" t="n"/>
+      <c r="K39" s="20">
+        <f>IFERROR(K38*변수!K48,"")</f>
+        <v/>
+      </c>
+      <c r="L39" s="20">
+        <f>IFERROR(L38*변수!L48,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="35">
+        <f>SUM(I39:L39)</f>
+        <v/>
+      </c>
+      <c r="N39" s="20">
+        <f>IFERROR(N38*변수!N48,"")</f>
+        <v/>
+      </c>
+      <c r="O39" s="20">
+        <f>IFERROR(O38*변수!O48,"")</f>
+        <v/>
+      </c>
+      <c r="P39" s="20">
+        <f>IFERROR(P38*변수!P48,"")</f>
+        <v/>
+      </c>
+      <c r="Q39" s="20">
+        <f>IFERROR(Q38*변수!Q48,"")</f>
+        <v/>
+      </c>
+      <c r="R39" s="35">
+        <f>SUM(N39:Q39)</f>
+        <v/>
+      </c>
+      <c r="S39" s="20">
+        <f>IFERROR(S38*변수!S48,"")</f>
+        <v/>
+      </c>
+      <c r="T39" s="20">
+        <f>IFERROR(T38*변수!T48,"")</f>
+        <v/>
+      </c>
+      <c r="U39" s="20">
+        <f>IFERROR(U38*변수!U48,"")</f>
+        <v/>
+      </c>
+      <c r="V39" s="20">
+        <f>IFERROR(V38*변수!V48,"")</f>
+        <v/>
+      </c>
+      <c r="W39" s="35">
+        <f>SUM(S39:V39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>NPM</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>지배주주순이익 / 매출액</t>
-        </is>
-      </c>
-      <c r="E40" s="21">
-        <f>IFERROR(E17/E5,"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="21">
-        <f>IFERROR(F17/F5,"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="21">
-        <f>IFERROR(G17/G5,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="22">
-        <f>IFERROR(H17/H5,"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="21">
-        <f>IFERROR(I17/I5,"")</f>
-        <v/>
-      </c>
-      <c r="J40" s="23">
-        <f>IFERROR(J17/J5,"")</f>
-        <v/>
-      </c>
-      <c r="K40" s="31">
-        <f>IFERROR(K17/K5,"")</f>
-        <v/>
-      </c>
-      <c r="L40" s="31">
-        <f>IFERROR(L17/L5,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="25">
-        <f>IFERROR(M17/M5,"")</f>
-        <v/>
-      </c>
-      <c r="N40" s="31">
-        <f>IFERROR(N17/N5,"")</f>
-        <v/>
-      </c>
-      <c r="O40" s="31">
-        <f>IFERROR(O17/O5,"")</f>
-        <v/>
-      </c>
-      <c r="P40" s="31">
-        <f>IFERROR(P17/P5,"")</f>
-        <v/>
-      </c>
-      <c r="Q40" s="31">
-        <f>IFERROR(Q17/Q5,"")</f>
-        <v/>
-      </c>
-      <c r="R40" s="25">
-        <f>IFERROR(R17/R5,"")</f>
-        <v/>
-      </c>
-      <c r="S40" s="31">
-        <f>IFERROR(S17/S5,"")</f>
-        <v/>
-      </c>
-      <c r="T40" s="31">
-        <f>IFERROR(T17/T5,"")</f>
-        <v/>
-      </c>
-      <c r="U40" s="31">
-        <f>IFERROR(U17/U5,"")</f>
-        <v/>
-      </c>
-      <c r="V40" s="31">
-        <f>IFERROR(V17/V5,"")</f>
-        <v/>
-      </c>
-      <c r="W40" s="25">
-        <f>IFERROR(W17/W5,"")</f>
-        <v/>
-      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>비율(참고)</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="10" t="n"/>
+      <c r="M40" s="11" t="n"/>
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="10" t="n"/>
+      <c r="Q40" s="10" t="n"/>
+      <c r="R40" s="11" t="n"/>
+      <c r="S40" s="10" t="n"/>
+      <c r="T40" s="10" t="n"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="11" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>매출원가율</t>
+          <t>OPM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -18678,175 +19422,361 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>매출원가 / 매출액</t>
+          <t>영업이익 / 매출액</t>
         </is>
       </c>
       <c r="E41" s="21">
-        <f>IFERROR(E6/E5,"")</f>
+        <f>IFERROR(E9/E5,"")</f>
         <v/>
       </c>
       <c r="F41" s="21">
-        <f>IFERROR(F6/F5,"")</f>
+        <f>IFERROR(F9/F5,"")</f>
         <v/>
       </c>
       <c r="G41" s="21">
-        <f>IFERROR(G6/G5,"")</f>
+        <f>IFERROR(G9/G5,"")</f>
         <v/>
       </c>
       <c r="H41" s="22">
-        <f>IFERROR(H6/H5,"")</f>
+        <f>IFERROR(H9/H5,"")</f>
         <v/>
       </c>
       <c r="I41" s="21">
-        <f>IFERROR(I6/I5,"")</f>
+        <f>IFERROR(I9/I5,"")</f>
         <v/>
       </c>
       <c r="J41" s="23">
-        <f>IFERROR(J6/J5,"")</f>
+        <f>IFERROR(J9/J5,"")</f>
         <v/>
       </c>
       <c r="K41" s="31">
-        <f>IFERROR(K6/K5,"")</f>
+        <f>IFERROR(K9/K5,"")</f>
         <v/>
       </c>
       <c r="L41" s="31">
-        <f>IFERROR(L6/L5,"")</f>
+        <f>IFERROR(L9/L5,"")</f>
         <v/>
       </c>
       <c r="M41" s="25">
-        <f>IFERROR(M6/M5,"")</f>
+        <f>IFERROR(M9/M5,"")</f>
         <v/>
       </c>
       <c r="N41" s="31">
-        <f>IFERROR(N6/N5,"")</f>
+        <f>IFERROR(N9/N5,"")</f>
         <v/>
       </c>
       <c r="O41" s="31">
-        <f>IFERROR(O6/O5,"")</f>
+        <f>IFERROR(O9/O5,"")</f>
         <v/>
       </c>
       <c r="P41" s="31">
-        <f>IFERROR(P6/P5,"")</f>
+        <f>IFERROR(P9/P5,"")</f>
         <v/>
       </c>
       <c r="Q41" s="31">
-        <f>IFERROR(Q6/Q5,"")</f>
+        <f>IFERROR(Q9/Q5,"")</f>
         <v/>
       </c>
       <c r="R41" s="25">
-        <f>IFERROR(R6/R5,"")</f>
+        <f>IFERROR(R9/R5,"")</f>
         <v/>
       </c>
       <c r="S41" s="31">
-        <f>IFERROR(S6/S5,"")</f>
+        <f>IFERROR(S9/S5,"")</f>
         <v/>
       </c>
       <c r="T41" s="31">
-        <f>IFERROR(T6/T5,"")</f>
+        <f>IFERROR(T9/T5,"")</f>
         <v/>
       </c>
       <c r="U41" s="31">
-        <f>IFERROR(U6/U5,"")</f>
+        <f>IFERROR(U9/U5,"")</f>
         <v/>
       </c>
       <c r="V41" s="31">
-        <f>IFERROR(V6/V5,"")</f>
+        <f>IFERROR(V9/V5,"")</f>
         <v/>
       </c>
       <c r="W41" s="25">
-        <f>IFERROR(W6/W5,"")</f>
+        <f>IFERROR(W9/W5,"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>지배주주순이익 / 매출액</t>
+        </is>
+      </c>
+      <c r="E42" s="21">
+        <f>IFERROR(E17/E5,"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="21">
+        <f>IFERROR(F17/F5,"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="21">
+        <f>IFERROR(G17/G5,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="22">
+        <f>IFERROR(H17/H5,"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="21">
+        <f>IFERROR(I17/I5,"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="23">
+        <f>IFERROR(J17/J5,"")</f>
+        <v/>
+      </c>
+      <c r="K42" s="31">
+        <f>IFERROR(K17/K5,"")</f>
+        <v/>
+      </c>
+      <c r="L42" s="31">
+        <f>IFERROR(L17/L5,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="25">
+        <f>IFERROR(M17/M5,"")</f>
+        <v/>
+      </c>
+      <c r="N42" s="31">
+        <f>IFERROR(N17/N5,"")</f>
+        <v/>
+      </c>
+      <c r="O42" s="31">
+        <f>IFERROR(O17/O5,"")</f>
+        <v/>
+      </c>
+      <c r="P42" s="31">
+        <f>IFERROR(P17/P5,"")</f>
+        <v/>
+      </c>
+      <c r="Q42" s="31">
+        <f>IFERROR(Q17/Q5,"")</f>
+        <v/>
+      </c>
+      <c r="R42" s="25">
+        <f>IFERROR(R17/R5,"")</f>
+        <v/>
+      </c>
+      <c r="S42" s="31">
+        <f>IFERROR(S17/S5,"")</f>
+        <v/>
+      </c>
+      <c r="T42" s="31">
+        <f>IFERROR(T17/T5,"")</f>
+        <v/>
+      </c>
+      <c r="U42" s="31">
+        <f>IFERROR(U17/U5,"")</f>
+        <v/>
+      </c>
+      <c r="V42" s="31">
+        <f>IFERROR(V17/V5,"")</f>
+        <v/>
+      </c>
+      <c r="W42" s="25">
+        <f>IFERROR(W17/W5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>매출원가율</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>매출원가 / 매출액</t>
+        </is>
+      </c>
+      <c r="E43" s="21">
+        <f>IFERROR(E6/E5,"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="21">
+        <f>IFERROR(F6/F5,"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="21">
+        <f>IFERROR(G6/G5,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="22">
+        <f>IFERROR(H6/H5,"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="21">
+        <f>IFERROR(I6/I5,"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="23">
+        <f>IFERROR(J6/J5,"")</f>
+        <v/>
+      </c>
+      <c r="K43" s="31">
+        <f>IFERROR(K6/K5,"")</f>
+        <v/>
+      </c>
+      <c r="L43" s="31">
+        <f>IFERROR(L6/L5,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="25">
+        <f>IFERROR(M6/M5,"")</f>
+        <v/>
+      </c>
+      <c r="N43" s="31">
+        <f>IFERROR(N6/N5,"")</f>
+        <v/>
+      </c>
+      <c r="O43" s="31">
+        <f>IFERROR(O6/O5,"")</f>
+        <v/>
+      </c>
+      <c r="P43" s="31">
+        <f>IFERROR(P6/P5,"")</f>
+        <v/>
+      </c>
+      <c r="Q43" s="31">
+        <f>IFERROR(Q6/Q5,"")</f>
+        <v/>
+      </c>
+      <c r="R43" s="25">
+        <f>IFERROR(R6/R5,"")</f>
+        <v/>
+      </c>
+      <c r="S43" s="31">
+        <f>IFERROR(S6/S5,"")</f>
+        <v/>
+      </c>
+      <c r="T43" s="31">
+        <f>IFERROR(T6/T5,"")</f>
+        <v/>
+      </c>
+      <c r="U43" s="31">
+        <f>IFERROR(U6/U5,"")</f>
+        <v/>
+      </c>
+      <c r="V43" s="31">
+        <f>IFERROR(V6/V5,"")</f>
+        <v/>
+      </c>
+      <c r="W43" s="25">
+        <f>IFERROR(W6/W5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
           <t>판관비율</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>판관비 / 매출액</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E44" s="21">
         <f>IFERROR(E8/E5,"")</f>
         <v/>
       </c>
-      <c r="F42" s="21">
+      <c r="F44" s="21">
         <f>IFERROR(F8/F5,"")</f>
         <v/>
       </c>
-      <c r="G42" s="21">
+      <c r="G44" s="21">
         <f>IFERROR(G8/G5,"")</f>
         <v/>
       </c>
-      <c r="H42" s="22">
+      <c r="H44" s="22">
         <f>IFERROR(H8/H5,"")</f>
         <v/>
       </c>
-      <c r="I42" s="21">
+      <c r="I44" s="21">
         <f>IFERROR(I8/I5,"")</f>
         <v/>
       </c>
-      <c r="J42" s="23">
+      <c r="J44" s="23">
         <f>IFERROR(J8/J5,"")</f>
         <v/>
       </c>
-      <c r="K42" s="31">
+      <c r="K44" s="31">
         <f>IFERROR(K8/K5,"")</f>
         <v/>
       </c>
-      <c r="L42" s="31">
+      <c r="L44" s="31">
         <f>IFERROR(L8/L5,"")</f>
         <v/>
       </c>
-      <c r="M42" s="25">
+      <c r="M44" s="25">
         <f>IFERROR(M8/M5,"")</f>
         <v/>
       </c>
-      <c r="N42" s="31">
+      <c r="N44" s="31">
         <f>IFERROR(N8/N5,"")</f>
         <v/>
       </c>
-      <c r="O42" s="31">
+      <c r="O44" s="31">
         <f>IFERROR(O8/O5,"")</f>
         <v/>
       </c>
-      <c r="P42" s="31">
+      <c r="P44" s="31">
         <f>IFERROR(P8/P5,"")</f>
         <v/>
       </c>
-      <c r="Q42" s="31">
+      <c r="Q44" s="31">
         <f>IFERROR(Q8/Q5,"")</f>
         <v/>
       </c>
-      <c r="R42" s="25">
+      <c r="R44" s="25">
         <f>IFERROR(R8/R5,"")</f>
         <v/>
       </c>
-      <c r="S42" s="31">
+      <c r="S44" s="31">
         <f>IFERROR(S8/S5,"")</f>
         <v/>
       </c>
-      <c r="T42" s="31">
+      <c r="T44" s="31">
         <f>IFERROR(T8/T5,"")</f>
         <v/>
       </c>
-      <c r="U42" s="31">
+      <c r="U44" s="31">
         <f>IFERROR(U8/U5,"")</f>
         <v/>
       </c>
-      <c r="V42" s="31">
+      <c r="V44" s="31">
         <f>IFERROR(V8/V5,"")</f>
         <v/>
       </c>
-      <c r="W42" s="25">
+      <c r="W44" s="25">
         <f>IFERROR(W8/W5,"")</f>
         <v/>
       </c>
@@ -18863,7 +19793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA39"/>
+  <dimension ref="A1:AA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19226,61 +20156,61 @@
         <v>198.344</v>
       </c>
       <c r="I5" s="26" t="n">
-        <v>223.627</v>
+        <v>193.633</v>
       </c>
       <c r="J5" s="26" t="n">
-        <v>227.123</v>
+        <v>197.13</v>
       </c>
       <c r="K5" s="26" t="n">
-        <v>222.186</v>
+        <v>192.844</v>
       </c>
       <c r="L5" s="26" t="n">
-        <v>224.655</v>
+        <v>194.987</v>
       </c>
       <c r="M5" s="26" t="n">
-        <v>214.448</v>
+        <v>186.238</v>
       </c>
       <c r="N5" s="26" t="n">
-        <v>186.157</v>
+        <v>161.928</v>
       </c>
       <c r="O5" s="26" t="n">
-        <v>170.353</v>
+        <v>148.327</v>
       </c>
       <c r="P5" s="26" t="n">
-        <v>170.353</v>
+        <v>148.327</v>
       </c>
       <c r="Q5" s="26" t="n">
-        <v>151.098</v>
+        <v>131.803</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>117.587</v>
+        <v>103.008</v>
       </c>
       <c r="S5" s="26" t="n">
-        <v>72.38</v>
+        <v>64.12</v>
       </c>
       <c r="T5" s="26" t="n">
-        <v>60.141</v>
+        <v>53.625</v>
       </c>
       <c r="U5" s="26" t="n">
-        <v>36.193</v>
+        <v>33.068</v>
       </c>
       <c r="V5" s="26" t="n">
-        <v>14.683</v>
+        <v>14.585</v>
       </c>
       <c r="W5" s="26" t="n">
         <v>103.057</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>795.405</v>
+        <v>735.418</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>847.446</v>
+        <v>735.997</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>609.391</v>
+        <v>531.465</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>183.397</v>
+        <v>165.398</v>
       </c>
     </row>
     <row r="6">
@@ -19307,61 +20237,61 @@
         <v>177.447</v>
       </c>
       <c r="I6" s="26" t="n">
-        <v>202.5</v>
+        <v>175.479</v>
       </c>
       <c r="J6" s="26" t="n">
-        <v>205.996</v>
+        <v>178.976</v>
       </c>
       <c r="K6" s="26" t="n">
-        <v>201.518</v>
+        <v>175.085</v>
       </c>
       <c r="L6" s="26" t="n">
-        <v>203.757</v>
+        <v>177.031</v>
       </c>
       <c r="M6" s="26" t="n">
-        <v>193.321</v>
+        <v>168.084</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>165.03</v>
+        <v>143.775</v>
       </c>
       <c r="O6" s="26" t="n">
-        <v>149.455</v>
+        <v>130.37</v>
       </c>
       <c r="P6" s="26" t="n">
-        <v>149.455</v>
+        <v>130.37</v>
       </c>
       <c r="Q6" s="26" t="n">
-        <v>151.098</v>
+        <v>131.803</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>117.587</v>
+        <v>103.008</v>
       </c>
       <c r="S6" s="26" t="n">
-        <v>72.38</v>
+        <v>64.12</v>
       </c>
       <c r="T6" s="26" t="n">
-        <v>60.141</v>
+        <v>53.625</v>
       </c>
       <c r="U6" s="26" t="n">
-        <v>36.193</v>
+        <v>33.068</v>
       </c>
       <c r="V6" s="26" t="n">
-        <v>14.683</v>
+        <v>14.585</v>
       </c>
       <c r="W6" s="26" t="n">
         <v>84.91500000000001</v>
       </c>
       <c r="X6" s="26" t="n">
-        <v>711.587</v>
+        <v>657.546</v>
       </c>
       <c r="Y6" s="26" t="n">
-        <v>763.626</v>
+        <v>663.975</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>567.595</v>
+        <v>495.551</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>183.397</v>
+        <v>165.398</v>
       </c>
     </row>
     <row r="7">
@@ -19385,664 +20315,659 @@
         <v>20.897</v>
       </c>
       <c r="I7" s="26" t="n">
-        <v>21.127</v>
+        <v>18.154</v>
       </c>
       <c r="J7" s="26" t="n">
-        <v>21.127</v>
+        <v>18.154</v>
       </c>
       <c r="K7" s="26" t="n">
-        <v>20.668</v>
+        <v>17.759</v>
       </c>
       <c r="L7" s="26" t="n">
-        <v>20.897</v>
+        <v>17.957</v>
       </c>
       <c r="M7" s="26" t="n">
-        <v>21.127</v>
+        <v>18.154</v>
       </c>
       <c r="N7" s="26" t="n">
-        <v>21.127</v>
+        <v>18.154</v>
       </c>
       <c r="O7" s="26" t="n">
-        <v>20.897</v>
+        <v>17.957</v>
       </c>
       <c r="P7" s="26" t="n">
-        <v>20.897</v>
+        <v>17.957</v>
       </c>
       <c r="W7" s="26" t="n">
         <v>18.142</v>
       </c>
       <c r="X7" s="26" t="n">
-        <v>83.819</v>
+        <v>77.873</v>
       </c>
       <c r="Y7" s="26" t="n">
-        <v>83.819</v>
+        <v>72.024</v>
       </c>
       <c r="Z7" s="26" t="n">
-        <v>41.794</v>
+        <v>35.914</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>cohort:③중마진</t>
+          <t>cohort:⑤초호황</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>코호트 ③중마진</t>
+          <t>코호트 ⑤초호황</t>
         </is>
       </c>
       <c r="E8" s="26" t="n">
         <v>6.893</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>78.02200000000001</v>
+        <v>96.164</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>125.644</v>
+        <v>146.311</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>177.447</v>
+        <v>198.344</v>
       </c>
       <c r="I8" s="26" t="n">
-        <v>202.5</v>
+        <v>193.633</v>
       </c>
       <c r="J8" s="26" t="n">
-        <v>205.996</v>
+        <v>197.13</v>
       </c>
       <c r="K8" s="26" t="n">
-        <v>201.518</v>
+        <v>192.844</v>
       </c>
       <c r="L8" s="26" t="n">
-        <v>203.757</v>
+        <v>194.987</v>
       </c>
       <c r="M8" s="26" t="n">
-        <v>193.321</v>
+        <v>186.238</v>
       </c>
       <c r="N8" s="26" t="n">
-        <v>165.03</v>
+        <v>161.928</v>
       </c>
       <c r="O8" s="26" t="n">
-        <v>149.455</v>
+        <v>148.327</v>
       </c>
       <c r="P8" s="26" t="n">
-        <v>149.455</v>
+        <v>148.327</v>
       </c>
       <c r="Q8" s="26" t="n">
-        <v>151.098</v>
+        <v>131.803</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>117.587</v>
+        <v>103.008</v>
       </c>
       <c r="S8" s="26" t="n">
-        <v>72.38</v>
+        <v>64.12</v>
       </c>
       <c r="T8" s="26" t="n">
-        <v>60.141</v>
+        <v>53.625</v>
       </c>
       <c r="U8" s="26" t="n">
-        <v>36.193</v>
+        <v>33.068</v>
       </c>
       <c r="V8" s="26" t="n">
-        <v>14.683</v>
+        <v>14.585</v>
       </c>
       <c r="W8" s="26" t="n">
-        <v>84.91500000000001</v>
+        <v>103.057</v>
       </c>
       <c r="X8" s="26" t="n">
-        <v>711.587</v>
+        <v>735.418</v>
       </c>
       <c r="Y8" s="26" t="n">
-        <v>763.626</v>
+        <v>735.997</v>
       </c>
       <c r="Z8" s="26" t="n">
-        <v>567.595</v>
+        <v>531.465</v>
       </c>
       <c r="AA8" s="26" t="n">
-        <v>183.397</v>
+        <v>165.398</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>cohort:②BEP</t>
+          <t>hedge_ratio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>코호트 ②BEP</t>
-        </is>
-      </c>
-      <c r="F9" s="26" t="n">
-        <v>18.142</v>
-      </c>
-      <c r="G9" s="26" t="n">
-        <v>20.668</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>20.897</v>
-      </c>
-      <c r="I9" s="26" t="n">
-        <v>21.127</v>
-      </c>
-      <c r="J9" s="26" t="n">
-        <v>21.127</v>
-      </c>
-      <c r="K9" s="26" t="n">
-        <v>20.668</v>
-      </c>
-      <c r="L9" s="26" t="n">
-        <v>20.897</v>
-      </c>
-      <c r="M9" s="26" t="n">
-        <v>21.127</v>
-      </c>
-      <c r="N9" s="26" t="n">
-        <v>21.127</v>
-      </c>
-      <c r="O9" s="26" t="n">
-        <v>20.897</v>
-      </c>
-      <c r="P9" s="26" t="n">
-        <v>20.897</v>
-      </c>
-      <c r="W9" s="26" t="n">
-        <v>18.142</v>
-      </c>
-      <c r="X9" s="26" t="n">
-        <v>83.819</v>
-      </c>
-      <c r="Y9" s="26" t="n">
-        <v>83.819</v>
-      </c>
-      <c r="Z9" s="26" t="n">
-        <v>41.794</v>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U9" s="21" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V9" s="21" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>hedge_ratio</t>
+          <t>hedge_rate</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="S10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="T10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="U10" s="21" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="V10" s="21" t="n">
-        <v>0.7</v>
+          <t>헤지환율</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>1386.95</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>1402</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>1423.95</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>1436.87</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>1439.57</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>1439.22</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>1439.22</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>1439.22</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>1442.28</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>1450.59</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>1451.94</v>
+      </c>
+      <c r="P10" s="13" t="n">
+        <v>1451.94</v>
+      </c>
+      <c r="Q10" s="13" t="n">
+        <v>1452.32</v>
+      </c>
+      <c r="R10" s="13" t="n">
+        <v>1467.26</v>
+      </c>
+      <c r="S10" s="13" t="n">
+        <v>1459.38</v>
+      </c>
+      <c r="T10" s="13" t="n">
+        <v>1457.97</v>
+      </c>
+      <c r="U10" s="13" t="n">
+        <v>1448.6</v>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>1421.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>hedge_rate</t>
+          <t>spot_assumed</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>헤지환율</t>
+          <t>건조시점 환율(가정)</t>
         </is>
       </c>
       <c r="E11" s="13" t="n">
         <v>1386.95</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>1402</v>
+        <v>1449.19</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1423.95</v>
+        <v>1466.12</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>1436.87</v>
+        <v>1501.75</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>1439.73</v>
+        <v>1419.72</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>1439.42</v>
+        <v>1353.36</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>1439.42</v>
+        <v>1353.36</v>
       </c>
       <c r="L11" s="13" t="n">
-        <v>1439.42</v>
+        <v>1353.36</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>1442.52</v>
+        <v>1353.36</v>
       </c>
       <c r="N11" s="13" t="n">
-        <v>1450.97</v>
+        <v>1353.36</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1452.37</v>
+        <v>1353.36</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>1452.37</v>
+        <v>1353.36</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>1452.82</v>
+        <v>1353.36</v>
       </c>
       <c r="R11" s="13" t="n">
-        <v>1468.19</v>
+        <v>1353.36</v>
       </c>
       <c r="S11" s="13" t="n">
-        <v>1460.6</v>
+        <v>1353.36</v>
       </c>
       <c r="T11" s="13" t="n">
-        <v>1459.41</v>
+        <v>1353.36</v>
       </c>
       <c r="U11" s="13" t="n">
-        <v>1450.43</v>
+        <v>1353.36</v>
       </c>
       <c r="V11" s="13" t="n">
-        <v>1421.92</v>
+        <v>1353.36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>spot_assumed</t>
+          <t>applied_rate</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>건조시점 환율(가정)</t>
+          <t>적용환율</t>
         </is>
       </c>
       <c r="E12" s="13" t="n">
         <v>1386.95</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1449.19</v>
+        <v>1416.15</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1466.12</v>
+        <v>1436.6</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>1501.75</v>
+        <v>1456.34</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>1419.72</v>
+        <v>1433.62</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1413.46</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1413.46</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1413.46</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1415.6</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1421.42</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1422.37</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1422.37</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1422.63</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1433.09</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1427.57</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1426.58</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1420.03</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>1353.36</v>
+        <v>1401.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>applied_rate</t>
+          <t>hedged_krw_m</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>적용환율</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>1386.95</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>1416.15</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>1436.6</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>1456.34</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>1433.73</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>1413.6</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>1413.6</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <v>1413.6</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>1415.77</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>1421.68</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <v>1422.67</v>
-      </c>
-      <c r="P13" s="13" t="n">
-        <v>1422.67</v>
-      </c>
-      <c r="Q13" s="13" t="n">
-        <v>1422.98</v>
-      </c>
-      <c r="R13" s="13" t="n">
-        <v>1433.74</v>
-      </c>
-      <c r="S13" s="13" t="n">
-        <v>1428.43</v>
-      </c>
-      <c r="T13" s="13" t="n">
-        <v>1427.59</v>
-      </c>
-      <c r="U13" s="13" t="n">
-        <v>1421.31</v>
-      </c>
-      <c r="V13" s="13" t="n">
-        <v>1401.35</v>
+          <t>헤지적용 원화매출(백만원)</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>9559.6</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>136182.6</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>210190.8</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>288856.2</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>277596.3</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>278636</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>272578.7</v>
+      </c>
+      <c r="L13" s="18" t="n">
+        <v>275607.3</v>
+      </c>
+      <c r="M13" s="18" t="n">
+        <v>263639.1</v>
+      </c>
+      <c r="N13" s="18" t="n">
+        <v>230168.1</v>
+      </c>
+      <c r="O13" s="18" t="n">
+        <v>210975.5</v>
+      </c>
+      <c r="P13" s="18" t="n">
+        <v>210975.5</v>
+      </c>
+      <c r="Q13" s="18" t="n">
+        <v>187507.3</v>
+      </c>
+      <c r="R13" s="18" t="n">
+        <v>147619.4</v>
+      </c>
+      <c r="S13" s="18" t="n">
+        <v>91535.7</v>
+      </c>
+      <c r="T13" s="18" t="n">
+        <v>76500.2</v>
+      </c>
+      <c r="U13" s="18" t="n">
+        <v>46957</v>
+      </c>
+      <c r="V13" s="18" t="n">
+        <v>20435.5</v>
+      </c>
+      <c r="W13" s="18" t="n">
+        <v>145742.2</v>
+      </c>
+      <c r="X13" s="18" t="n">
+        <v>1055279.3</v>
+      </c>
+      <c r="Y13" s="18" t="n">
+        <v>1041993.2</v>
+      </c>
+      <c r="Z13" s="18" t="n">
+        <v>757077.7</v>
+      </c>
+      <c r="AA13" s="18" t="n">
+        <v>235428.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>hedged_krw_m</t>
+          <t>target_opm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>헤지적용 원화매출(백만원)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>9559.6</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>136182.6</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>210190.8</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>288856.2</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>320619.5</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>321062.1</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>314082.5</v>
-      </c>
-      <c r="L14" s="18" t="n">
-        <v>317572.3</v>
-      </c>
-      <c r="M14" s="18" t="n">
-        <v>303609.2</v>
-      </c>
-      <c r="N14" s="18" t="n">
-        <v>264656.6</v>
-      </c>
-      <c r="O14" s="18" t="n">
-        <v>242355.7</v>
-      </c>
-      <c r="P14" s="18" t="n">
-        <v>242355.7</v>
-      </c>
-      <c r="Q14" s="18" t="n">
-        <v>215009.2</v>
-      </c>
-      <c r="R14" s="18" t="n">
-        <v>168588.8</v>
-      </c>
-      <c r="S14" s="18" t="n">
-        <v>103390</v>
-      </c>
-      <c r="T14" s="18" t="n">
-        <v>85857.2</v>
-      </c>
-      <c r="U14" s="18" t="n">
-        <v>51440.9</v>
-      </c>
-      <c r="V14" s="18" t="n">
-        <v>20575.9</v>
-      </c>
-      <c r="W14" s="18" t="n">
-        <v>145742.2</v>
-      </c>
-      <c r="X14" s="18" t="n">
-        <v>1140728.6</v>
-      </c>
-      <c r="Y14" s="18" t="n">
-        <v>1199920.6</v>
-      </c>
-      <c r="Z14" s="18" t="n">
-        <v>868309.4</v>
-      </c>
-      <c r="AA14" s="18" t="n">
-        <v>261264</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>target_opm</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
           <t>타겟 OPM(코호트)</t>
         </is>
       </c>
-      <c r="E15" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>0.0406</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>0.0429</v>
-      </c>
-      <c r="H15" s="21" t="n">
-        <v>0.0447</v>
-      </c>
-      <c r="I15" s="21" t="n">
-        <v>0.0453</v>
-      </c>
-      <c r="J15" s="21" t="n">
-        <v>0.0453</v>
-      </c>
-      <c r="K15" s="21" t="n">
-        <v>0.0453</v>
-      </c>
-      <c r="L15" s="21" t="n">
-        <v>0.0453</v>
-      </c>
-      <c r="M15" s="21" t="n">
-        <v>0.0451</v>
-      </c>
-      <c r="N15" s="21" t="n">
-        <v>0.0443</v>
-      </c>
-      <c r="O15" s="21" t="n">
-        <v>0.0439</v>
-      </c>
-      <c r="P15" s="21" t="n">
-        <v>0.0439</v>
-      </c>
-      <c r="Q15" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="R15" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="S15" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="T15" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="U15" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="V15" s="21" t="n">
-        <v>0.05</v>
+      <c r="E14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="O14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="R14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="S14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="U14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="V14" s="21" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>계약 원장(contracts.json 기반)</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>계약 원장(contracts.json 기반)</t>
+          <t>rcp</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>ships</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>amt_krw_m</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>amt_usd_m</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>fx_at_sign</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>signed</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr">
+        <is>
+          <t>cohort</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr">
+        <is>
+          <t>curve</t>
+        </is>
+      </c>
+      <c r="L17" s="1" t="inlineStr">
+        <is>
+          <t>estimated_series</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>rcp</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>ships</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>amt_krw_m</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
-        <is>
-          <t>amt_usd_m</t>
-        </is>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>fx_at_sign</t>
-        </is>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>signed</t>
-        </is>
-      </c>
-      <c r="H18" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>cohort</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>curve</t>
-        </is>
-      </c>
-      <c r="L18" s="1" t="inlineStr">
-        <is>
-          <t>estimated_series</t>
-        </is>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20250922800050</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VLCC</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>475300</v>
+      </c>
+      <c r="E18" t="n">
+        <v>342.694</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1386.95</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2028-09-30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>⑤초호황</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20250922800050</t>
+          <t>20250922800051</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -20051,13 +20976,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>475300</v>
+        <v>239500</v>
       </c>
       <c r="E19" t="n">
-        <v>342.694</v>
+        <v>172.681</v>
       </c>
       <c r="F19" t="n">
         <v>1386.95</v>
@@ -20074,12 +20999,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2028-09-30</t>
+          <t>2027-09-30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -20094,7 +21019,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20250922800051</t>
+          <t>20250930800053</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -20103,35 +21028,35 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>239500</v>
+        <v>122300</v>
       </c>
       <c r="E20" t="n">
-        <v>172.681</v>
+        <v>88.179</v>
       </c>
       <c r="F20" t="n">
         <v>1386.95</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2027-09-30</t>
+          <t>2027-06-30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -20146,7 +21071,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20250930800053</t>
+          <t>20251001800065</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -20158,32 +21083,32 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>122300</v>
+        <v>119200</v>
       </c>
       <c r="E21" t="n">
-        <v>88.179</v>
+        <v>85.944</v>
       </c>
       <c r="F21" t="n">
         <v>1386.95</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2027-06-30</t>
+          <t>2027-10-31</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -20198,44 +21123,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20251001800065</t>
+          <t>20251015800073</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VLCC</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>119200</v>
+        <v>329800</v>
       </c>
       <c r="E22" t="n">
-        <v>85.944</v>
+        <v>227.575</v>
       </c>
       <c r="F22" t="n">
-        <v>1386.95</v>
+        <v>1449.19</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2027-10-31</t>
+          <t>2028-06-30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -20244,50 +21169,50 @@
         </is>
       </c>
       <c r="L22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20251015800073</t>
+          <t>20251118800028</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>VLCC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>329800</v>
+        <v>127400</v>
       </c>
       <c r="E23" t="n">
-        <v>227.575</v>
+        <v>87.911</v>
       </c>
       <c r="F23" t="n">
         <v>1449.19</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2028-06-30</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>②BEP</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -20296,13 +21221,13 @@
         </is>
       </c>
       <c r="L23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20251118800028</t>
+          <t>20260114800029</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -20311,35 +21236,35 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>127400</v>
+        <v>251800</v>
       </c>
       <c r="E24" t="n">
-        <v>87.911</v>
+        <v>171.746</v>
       </c>
       <c r="F24" t="n">
-        <v>1449.19</v>
+        <v>1466.12</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2028-11-30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -20348,13 +21273,13 @@
         </is>
       </c>
       <c r="L24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260114800029</t>
+          <t>20260115800029</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -20366,32 +21291,32 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>251800</v>
+        <v>253900</v>
       </c>
       <c r="E25" t="n">
-        <v>171.746</v>
+        <v>173.178</v>
       </c>
       <c r="F25" t="n">
         <v>1466.12</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2028-11-30</t>
+          <t>2029-04-30</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -20400,13 +21325,13 @@
         </is>
       </c>
       <c r="L25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260115800029</t>
+          <t>20260129800084</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -20418,32 +21343,32 @@
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>253900</v>
+        <v>254100</v>
       </c>
       <c r="E26" t="n">
-        <v>173.178</v>
+        <v>173.315</v>
       </c>
       <c r="F26" t="n">
         <v>1466.12</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2029-04-30</t>
+          <t>2029-05-31</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -20458,7 +21383,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260129800084</t>
+          <t>20260209800078</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -20470,32 +21395,32 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>254100</v>
+        <v>259700</v>
       </c>
       <c r="E27" t="n">
-        <v>173.315</v>
+        <v>177.134</v>
       </c>
       <c r="F27" t="n">
         <v>1466.12</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2029-05-31</t>
+          <t>2028-12-31</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -20510,7 +21435,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260209800078</t>
+          <t>20260317800064</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -20519,35 +21444,35 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>259700</v>
+        <v>133300</v>
       </c>
       <c r="E28" t="n">
-        <v>177.134</v>
+        <v>90.92</v>
       </c>
       <c r="F28" t="n">
         <v>1466.12</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2028-12-31</t>
+          <t>2029-10-10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -20562,7 +21487,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260317800064</t>
+          <t>20260323800069</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -20574,32 +21499,32 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>133300</v>
+        <v>133800</v>
       </c>
       <c r="E29" t="n">
-        <v>90.92</v>
+        <v>91.261</v>
       </c>
       <c r="F29" t="n">
         <v>1466.12</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2029-10-10</t>
+          <t>2029-06-30</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -20614,7 +21539,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260323800069</t>
+          <t>20260331800063</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -20623,35 +21548,35 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>133800</v>
+        <v>276000</v>
       </c>
       <c r="E30" t="n">
-        <v>91.261</v>
+        <v>188.252</v>
       </c>
       <c r="F30" t="n">
         <v>1466.12</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2029-06-30</t>
+          <t>2029-09-30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -20666,7 +21591,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260331800063</t>
+          <t>20260416800003</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -20675,35 +21600,35 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>276000</v>
+        <v>132900</v>
       </c>
       <c r="E31" t="n">
-        <v>188.252</v>
+        <v>88.497</v>
       </c>
       <c r="F31" t="n">
-        <v>1466.12</v>
+        <v>1501.75</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
+          <t>2029-07-31</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -20718,7 +21643,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260416800003</t>
+          <t>20260601800013</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -20727,35 +21652,35 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>132900</v>
+        <v>282800</v>
       </c>
       <c r="E32" t="n">
-        <v>88.497</v>
+        <v>188.314</v>
       </c>
       <c r="F32" t="n">
         <v>1501.75</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2029-07-31</t>
+          <t>2028-12-31</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -20770,7 +21695,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260601800013</t>
+          <t>20260727800063</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -20782,32 +21707,32 @@
         <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>282800</v>
+        <v>271300</v>
       </c>
       <c r="E33" t="n">
-        <v>188.314</v>
+        <v>191.094</v>
       </c>
       <c r="F33" t="n">
-        <v>1501.75</v>
+        <v>1419.72</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2028-12-31</t>
+          <t>2029-12-31</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>③중마진</t>
+          <t>⑤초호황</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -20816,91 +21741,39 @@
         </is>
       </c>
       <c r="L33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>20260727800063</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>VLCC</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" t="n">
-        <v>271300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>191.094</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1419.72</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>③중마진</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>linear_progress</t>
-        </is>
-      </c>
-      <c r="L34" t="b">
-        <v>0</v>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
+          <t>⚠ 헤지비율 0.7 은 가정(통화선도 공시 없음 → 레퍼런스 SLS 시트의 HEDGE 70% 가정. hedge_rate 는 계약별 수주시점 환율로 대체)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>⚠ 헤지비율 0.7 은 가정(통화선도 공시 없음 → 레퍼런스 SLS 시트의 HEDGE 70% 가정. hedge_rate 는 계약별 수주시점 환율로 대체)</t>
+          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 9%, ③중마진 91%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트는 원장 내부 상대 등급(신조선가 지수 없음): 2025~ 수주 물량(백만$) 판정 ②BEP 9%, ③중마진 91% — 최다 ③중마진. 레퍼런스 HD현대미포 SLS 는 2025~ 물량을 100% ⑤초호황으로 두어 방향이 다르다(2021 이후 절대 호황 수준 미반영). 타겟 OPM 은 회사 calibrated_shift 로 실측 OPM 에 맞추고, 외부 지수 도입은 사용자 결정</t>
+          <t>⚠ 원장 잔여(27541억) &gt; 공시 해양 기말잔고(23665억), 커버리지 1.16 — 선형 진행 가정이 실제 진행보다 느리거나 공시 잔고 범위(환율·취소·범위)가 다르다. origin 이후 해양 매출(origin 전 수주분)을 1/coverage = 0.8593 배로 줄였다(backlog_cap, 원값 *_raw 보존). 모델은 배율 1 을 상한으로 볼 것 — 추가 배율 금지</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>⚠ 원장 잔여(27541억) &gt; 공시 해양 기말잔고(23665억), 커버리지 1.16 — 선형 진행 가정이 실제 진행보다 느리거나 공시 잔고 범위(환율·취소·범위)가 다르다. 모델은 배율 1 을 상한으로 볼 것</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>⚠ 원장 신규 19783억 vs 수주표 신규증감 13010억(2026Q2 연초 누계) — 비율 1.52: 두 공시의 계약 인식 기준(발효·선수금·환율·범위)이 다르다. backlog_coverage 해석 시 참고(reconcile_summary.ledger_vs_reported_new)</t>
         </is>
@@ -20917,7 +21790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21030,7 +21903,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D49</f>
+        <f>변수!D51</f>
         <v/>
       </c>
       <c r="I2" s="38" t="n"/>
@@ -23332,12 +24205,12 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>OP조선</t>
+          <t>매출조선신규</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OP 조선·해양(선박)</t>
+          <t>매출 조선·해양(선박) 신규수주(forecast_panel base — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E35" s="18">
@@ -23404,12 +24277,12 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>매출기타</t>
+          <t>OP조선</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>매출 기타 부문(총매출 − 조선)</t>
+          <t>OP 조선·해양(선박)</t>
         </is>
       </c>
       <c r="E36" s="18">
@@ -23476,12 +24349,12 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>OP기타</t>
+          <t>OP조선신규</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OP 기타 부문(총매출 − 조선)</t>
+          <t>OP 조선·해양(선박) 신규수주(매출조선신규 × OPM — OP조선에 포함)</t>
         </is>
       </c>
       <c r="E37" s="18">
@@ -23548,71 +24421,71 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>매출기타</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="E38" s="21">
+          <t>매출 기타 부문(총매출 − 조선)</t>
+        </is>
+      </c>
+      <c r="E38" s="18">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F38" s="21">
+      <c r="F38" s="18">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G38" s="21">
+      <c r="G38" s="18">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H38" s="21">
+      <c r="H38" s="18">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I38" s="42">
+      <c r="I38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N38" s="31">
+      <c r="N38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O38" s="31">
+      <c r="O38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(P$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(Q$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(R$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="S38" s="31">
+      <c r="S38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(S$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -23620,71 +24493,71 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>OP기타</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NPM</t>
-        </is>
-      </c>
-      <c r="E39" s="21">
+          <t>OP 기타 부문(총매출 − 조선)</t>
+        </is>
+      </c>
+      <c r="E39" s="18">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F39" s="21">
+      <c r="F39" s="18">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G39" s="21">
+      <c r="G39" s="18">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H39" s="21">
+      <c r="H39" s="18">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I39" s="42">
+      <c r="I39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="M39" s="31">
+      <c r="M39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="N39" s="31">
+      <c r="N39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="O39" s="31">
+      <c r="O39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="P39" s="31">
+      <c r="P39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(P$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(Q$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="R39" s="31">
+      <c r="R39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(R$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="S39" s="31">
+      <c r="S39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(S$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -23692,167 +24565,311 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
+          <t>OPM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
-        </is>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="E40" s="21">
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="21">
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="21">
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="21">
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
+        <v/>
       </c>
       <c r="I40" s="42">
-        <f>IFERROR(I5/E5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="J40" s="31">
-        <f>IFERROR(J5/F5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="K40" s="31">
-        <f>IFERROR(K5/G5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="L40" s="31">
-        <f>IFERROR(L5/H5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="M40" s="31">
-        <f>IFERROR(M5/I5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="N40" s="31">
-        <f>IFERROR(N5/J5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="O40" s="31">
-        <f>IFERROR(O5/K5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="P40" s="31">
-        <f>IFERROR(P5/L5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(P$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="Q40" s="31">
-        <f>IFERROR(Q5/M5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(Q$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="R40" s="31">
-        <f>IFERROR(R5/N5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(R$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="S40" s="31">
-        <f>IFERROR(S5/O5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(S$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
+          <t>NPM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
-        </is>
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="E41" s="21">
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="21">
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="21">
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="21">
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
+        <v/>
       </c>
       <c r="I41" s="42">
-        <f>IFERROR(I9/E9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="J41" s="31">
-        <f>IFERROR(J9/F9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="K41" s="31">
-        <f>IFERROR(K9/G9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="L41" s="31">
-        <f>IFERROR(L9/H9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="M41" s="31">
-        <f>IFERROR(M9/I9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(M$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="N41" s="31">
-        <f>IFERROR(N9/J9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(N$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="O41" s="31">
-        <f>IFERROR(O9/K9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(O$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="P41" s="31">
-        <f>IFERROR(P9/L9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(P$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="Q41" s="31">
-        <f>IFERROR(Q9/M9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(Q$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="R41" s="31">
-        <f>IFERROR(R9/N9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(R$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="S41" s="31">
-        <f>IFERROR(S9/O9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(S$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
+          <t>매출액 YoY</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>매출액 YoY</t>
+        </is>
+      </c>
+      <c r="I42" s="42">
+        <f>IFERROR(I5/E5-1,"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="31">
+        <f>IFERROR(J5/F5-1,"")</f>
+        <v/>
+      </c>
+      <c r="K42" s="31">
+        <f>IFERROR(K5/G5-1,"")</f>
+        <v/>
+      </c>
+      <c r="L42" s="31">
+        <f>IFERROR(L5/H5-1,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="31">
+        <f>IFERROR(M5/I5-1,"")</f>
+        <v/>
+      </c>
+      <c r="N42" s="31">
+        <f>IFERROR(N5/J5-1,"")</f>
+        <v/>
+      </c>
+      <c r="O42" s="31">
+        <f>IFERROR(O5/K5-1,"")</f>
+        <v/>
+      </c>
+      <c r="P42" s="31">
+        <f>IFERROR(P5/L5-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q42" s="31">
+        <f>IFERROR(Q5/M5-1,"")</f>
+        <v/>
+      </c>
+      <c r="R42" s="31">
+        <f>IFERROR(R5/N5-1,"")</f>
+        <v/>
+      </c>
+      <c r="S42" s="31">
+        <f>IFERROR(S5/O5-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="I43" s="42">
+        <f>IFERROR(I9/E9-1,"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="31">
+        <f>IFERROR(J9/F9-1,"")</f>
+        <v/>
+      </c>
+      <c r="K43" s="31">
+        <f>IFERROR(K9/G9-1,"")</f>
+        <v/>
+      </c>
+      <c r="L43" s="31">
+        <f>IFERROR(L9/H9-1,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="31">
+        <f>IFERROR(M9/I9-1,"")</f>
+        <v/>
+      </c>
+      <c r="N43" s="31">
+        <f>IFERROR(N9/J9-1,"")</f>
+        <v/>
+      </c>
+      <c r="O43" s="31">
+        <f>IFERROR(O9/K9-1,"")</f>
+        <v/>
+      </c>
+      <c r="P43" s="31">
+        <f>IFERROR(P9/L9-1,"")</f>
+        <v/>
+      </c>
+      <c r="Q43" s="31">
+        <f>IFERROR(Q9/M9-1,"")</f>
+        <v/>
+      </c>
+      <c r="R43" s="31">
+        <f>IFERROR(R9/N9-1,"")</f>
+        <v/>
+      </c>
+      <c r="S43" s="31">
+        <f>IFERROR(S9/O9-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
           <t>지배주주순이익 YoY</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>지배주주순이익 YoY</t>
         </is>
       </c>
-      <c r="I42" s="42">
+      <c r="I44" s="42">
         <f>IFERROR(I17/E17-1,"")</f>
         <v/>
       </c>
-      <c r="J42" s="31">
+      <c r="J44" s="31">
         <f>IFERROR(J17/F17-1,"")</f>
         <v/>
       </c>
-      <c r="K42" s="31">
+      <c r="K44" s="31">
         <f>IFERROR(K17/G17-1,"")</f>
         <v/>
       </c>
-      <c r="L42" s="31">
+      <c r="L44" s="31">
         <f>IFERROR(L17/H17-1,"")</f>
         <v/>
       </c>
-      <c r="M42" s="31">
+      <c r="M44" s="31">
         <f>IFERROR(M17/I17-1,"")</f>
         <v/>
       </c>
-      <c r="N42" s="31">
+      <c r="N44" s="31">
         <f>IFERROR(N17/J17-1,"")</f>
         <v/>
       </c>
-      <c r="O42" s="31">
+      <c r="O44" s="31">
         <f>IFERROR(O17/K17-1,"")</f>
         <v/>
       </c>
-      <c r="P42" s="31">
+      <c r="P44" s="31">
         <f>IFERROR(P17/L17-1,"")</f>
         <v/>
       </c>
-      <c r="Q42" s="31">
+      <c r="Q44" s="31">
         <f>IFERROR(Q17/M17-1,"")</f>
         <v/>
       </c>
-      <c r="R42" s="31">
+      <c r="R44" s="31">
         <f>IFERROR(R17/N17-1,"")</f>
         <v/>
       </c>
-      <c r="S42" s="31">
+      <c r="S44" s="31">
         <f>IFERROR(S17/O17-1,"")</f>
         <v/>
       </c>
@@ -23868,7 +24885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23907,7 +24924,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D49</f>
+        <f>변수!D51</f>
         <v/>
       </c>
       <c r="E2" s="38" t="n"/>
@@ -24801,12 +25818,12 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>OP조선</t>
+          <t>매출조선신규</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OP 조선·해양(선박)</t>
+          <t>매출 조선·해양(선박) 신규수주(forecast_panel base — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E35" s="41">
@@ -24829,12 +25846,12 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>매출기타</t>
+          <t>OP조선</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>매출 기타 부문(총매출 − 조선)</t>
+          <t>OP 조선·해양(선박)</t>
         </is>
       </c>
       <c r="E36" s="41">
@@ -24857,12 +25874,12 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>OP기타</t>
+          <t>OP조선신규</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OP 기타 부문(총매출 − 조선)</t>
+          <t>OP 조선·해양(선박) 신규수주(매출조선신규 × OPM — OP조선에 포함)</t>
         </is>
       </c>
       <c r="E37" s="41">
@@ -24885,27 +25902,27 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>OPM</t>
+          <t>매출기타</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="E38" s="42">
+          <t>매출 기타 부문(총매출 − 조선)</t>
+        </is>
+      </c>
+      <c r="E38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="20">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -24913,27 +25930,27 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>NPM</t>
+          <t>OP기타</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NPM</t>
-        </is>
-      </c>
-      <c r="E39" s="42">
+          <t>OP 기타 부문(총매출 − 조선)</t>
+        </is>
+      </c>
+      <c r="E39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="20">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -24941,74 +25958,130 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
+          <t>OPM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>매출액 YoY</t>
-        </is>
-      </c>
-      <c r="E40" s="38" t="n"/>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="E40" s="42">
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
       <c r="F40" s="31">
-        <f>IFERROR(F5/E5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="G40" s="31">
-        <f>IFERROR(G5/F5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="H40" s="31">
-        <f>IFERROR(H5/G5-1,"")</f>
+        <f>IFERROR(VLOOKUP($A40,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
+          <t>NPM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>영업이익 YoY</t>
-        </is>
-      </c>
-      <c r="E41" s="38" t="n"/>
+          <t>NPM</t>
+        </is>
+      </c>
+      <c r="E41" s="42">
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(E$1,SUBQH,0),0),"")</f>
+        <v/>
+      </c>
       <c r="F41" s="31">
-        <f>IFERROR(F9/E9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(F$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="G41" s="31">
-        <f>IFERROR(G9/F9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(G$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
       <c r="H41" s="31">
-        <f>IFERROR(H9/G9-1,"")</f>
+        <f>IFERROR(VLOOKUP($A41,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>지배주주순이익 YoY</t>
+          <t>매출액 YoY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>지배주주순이익 YoY</t>
+          <t>매출액 YoY</t>
         </is>
       </c>
       <c r="E42" s="38" t="n"/>
       <c r="F42" s="31">
+        <f>IFERROR(F5/E5-1,"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="31">
+        <f>IFERROR(G5/F5-1,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="31">
+        <f>IFERROR(H5/G5-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>영업이익 YoY</t>
+        </is>
+      </c>
+      <c r="E43" s="38" t="n"/>
+      <c r="F43" s="31">
+        <f>IFERROR(F9/E9-1,"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="31">
+        <f>IFERROR(G9/F9-1,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="31">
+        <f>IFERROR(H9/G9-1,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>지배주주순이익 YoY</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>지배주주순이익 YoY</t>
+        </is>
+      </c>
+      <c r="E44" s="38" t="n"/>
+      <c r="F44" s="31">
         <f>IFERROR(F17/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="31">
+      <c r="G44" s="31">
         <f>IFERROR(G17/F17-1,"")</f>
         <v/>
       </c>
-      <c r="H42" s="31">
+      <c r="H44" s="31">
         <f>IFERROR(H17/G17-1,"")</f>
         <v/>
       </c>
@@ -25037,7 +26110,7 @@
         </is>
       </c>
       <c r="C1" s="18">
-        <f>변수!D49</f>
+        <f>변수!D51</f>
         <v/>
       </c>
     </row>
@@ -25048,7 +26121,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D50</f>
+        <f>변수!D52</f>
         <v/>
       </c>
     </row>
@@ -25225,7 +26298,7 @@
         </is>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(E7*변수!D55+F7*(1-변수!D55),"")</f>
+        <f>IFERROR(E7*변수!D57+F7*(1-변수!D57),"")</f>
         <v/>
       </c>
     </row>
@@ -25236,7 +26309,7 @@
         </is>
       </c>
       <c r="D15" s="26">
-        <f>변수!D52</f>
+        <f>변수!D54</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -25260,7 +26333,7 @@
         </is>
       </c>
       <c r="D16" s="26">
-        <f>변수!D53</f>
+        <f>변수!D55</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -25284,7 +26357,7 @@
         </is>
       </c>
       <c r="D17" s="26">
-        <f>변수!D54</f>
+        <f>변수!D56</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -25348,7 +26421,7 @@
         </is>
       </c>
       <c r="D23" s="21">
-        <f>변수!D51</f>
+        <f>변수!D53</f>
         <v/>
       </c>
     </row>
@@ -25403,7 +26476,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7270.6</v>
+        <v>6870.4</v>
       </c>
     </row>
     <row r="30">
@@ -25423,7 +26496,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.2</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="32">
@@ -25443,7 +26516,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.231</v>
+        <v>0.2183</v>
       </c>
     </row>
     <row r="34">
@@ -25453,7 +26526,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="35">
@@ -25463,7 +26536,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>80900</v>
+        <v>76500</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$W$1</definedName>
@@ -1468,55 +1468,55 @@
     <comment ref="L39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2591억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2589억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="N39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2532억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 191억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2529억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 191억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2560억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2557억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="P39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2438억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2436억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="Q39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2104억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2102억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="S39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1914억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 1912억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="T39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1914억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 1912억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="U39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1677억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 1676억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="V39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1279억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 1278억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
@@ -2143,49 +2143,49 @@
     </comment>
     <comment ref="N11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6965억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6964억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7587억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7586억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="P11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8193억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8192억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8959억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8957억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9758억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9756억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10624억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10621억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11501억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11498억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12523억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12520억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2203,49 +2203,49 @@
     </comment>
     <comment ref="N12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6965억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 6964억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7587억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7586억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8193억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8192억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Q12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8959억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8957억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="S12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9758억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9756억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10624억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10621억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 11501억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 11498억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 12523억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 12520억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3570,55 +3570,55 @@
     </comment>
     <comment ref="L38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2591억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2589억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="N38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2532억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 191억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2529억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 191억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="O38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2560억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2557억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="P38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2438억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2436억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="Q38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2104억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2102억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="S38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1914억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 1912억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="T38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1914억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 1912억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="U38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1677억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 1676억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="V38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1279억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 1278억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -4521,7 +4521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 14,599억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −1,899억(2026 345억 · 2027 776억 · 2028 778억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 345억 vs 82억 · 2027 776억 vs 3,561억 · 2028 778억 vs 10,956억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 14,599억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −1,897억(2026 345억 · 2027 775억 · 2028 777억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 345억 vs 82억 · 2027 775억 vs 3,561억 · 2028 777억 vs 10,956억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6528.9</v>
+        <v>6525.6</v>
       </c>
     </row>
     <row r="30">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.05</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="32">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="33">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2074</v>
+        <v>0.2073</v>
       </c>
     </row>
     <row r="34">
@@ -6236,7 +6236,7 @@
         <v>4.48</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>-0</v>
@@ -6637,35 +6637,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -6702,35 +6702,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -6767,35 +6767,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -6832,35 +6832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -6897,35 +6897,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -6962,35 +6962,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -7027,35 +7027,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -7092,35 +7092,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -7174,7 +7174,7 @@
         <v>45700</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>46050</v>
+        <v>47900</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -7216,7 +7216,7 @@
         <v>57500</v>
       </c>
       <c r="L16" s="20" t="n">
-        <v>46450</v>
+        <v>48350</v>
       </c>
       <c r="M16" s="11" t="n"/>
       <c r="N16" s="10" t="n"/>
@@ -7300,7 +7300,7 @@
         <v>48174.2</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>46000</v>
+        <v>46633.3</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="K29" s="29" t="n">
-        <v>-0.008137459999999999</v>
+        <v>-0.007163479</v>
       </c>
       <c r="L29" s="29" t="n">
-        <v>0.010129005</v>
+        <v>0.007849182999999999</v>
       </c>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="29" t="n">
-        <v>-0.005700235</v>
+        <v>0.005120062</v>
       </c>
       <c r="O29" s="29" t="n">
-        <v>95.228949575</v>
+        <v>95.22007296699999</v>
       </c>
       <c r="P29" s="29" t="n">
-        <v>-0.002780883</v>
+        <v>-0.000424953</v>
       </c>
       <c r="Q29" s="29" t="n">
-        <v>0.006917301</v>
+        <v>-0.00083998</v>
       </c>
       <c r="R29" s="30" t="n"/>
       <c r="S29" s="29" t="n">
-        <v>-0.003310268</v>
+        <v>-0.004027772</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>95.22123567600001</v>
+        <v>95.226824377</v>
       </c>
       <c r="U29" s="29" t="n">
-        <v>0.011231891</v>
+        <v>0.003984354</v>
       </c>
       <c r="V29" s="29" t="n">
-        <v>-0.005568738</v>
+        <v>0.003115029</v>
       </c>
       <c r="W29" s="30" t="n"/>
     </row>
@@ -8140,36 +8140,36 @@
         <v/>
       </c>
       <c r="K30" s="29" t="n">
-        <v>-0.008137459999999999</v>
+        <v>-0.007163479</v>
       </c>
       <c r="L30" s="29" t="n">
-        <v>0.010129005</v>
+        <v>0.007849182999999999</v>
       </c>
       <c r="M30" s="30" t="n"/>
       <c r="N30" s="29" t="n">
-        <v>-0.005700235</v>
+        <v>0.005120062</v>
       </c>
       <c r="O30" s="29" t="n">
-        <v>95.228949575</v>
+        <v>95.22007296699999</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>-0.002780883</v>
+        <v>-0.000424953</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>0.006917301</v>
+        <v>-0.00083998</v>
       </c>
       <c r="R30" s="30" t="n"/>
       <c r="S30" s="29" t="n">
-        <v>-0.003310268</v>
+        <v>-0.004027772</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>95.22123567600001</v>
+        <v>95.226824377</v>
       </c>
       <c r="U30" s="29" t="n">
-        <v>0.011231891</v>
+        <v>0.003984354</v>
       </c>
       <c r="V30" s="29" t="n">
-        <v>-0.005568738</v>
+        <v>0.003115029</v>
       </c>
       <c r="W30" s="30" t="n"/>
     </row>
@@ -8307,33 +8307,33 @@
         <v>0.09948617899999999</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.091854699</v>
+        <v>0.091802965</v>
       </c>
       <c r="M33" s="25" t="n"/>
       <c r="N33" s="31" t="n">
-        <v>0.08938517</v>
+        <v>0.089319047</v>
       </c>
       <c r="O33" s="31" t="n">
-        <v>0.079863138</v>
+        <v>0.0798085</v>
       </c>
       <c r="P33" s="31" t="n">
-        <v>0.093493727</v>
+        <v>0.09345119</v>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0.089134273</v>
+        <v>0.089107231</v>
       </c>
       <c r="R33" s="25" t="n"/>
       <c r="S33" s="31" t="n">
-        <v>0.088774564</v>
+        <v>0.08875638399999999</v>
       </c>
       <c r="T33" s="31" t="n">
-        <v>0.08255090599999999</v>
+        <v>0.082535812</v>
       </c>
       <c r="U33" s="31" t="n">
-        <v>0.08884611000000001</v>
+        <v>0.088839895</v>
       </c>
       <c r="V33" s="31" t="n">
-        <v>0.081836134</v>
+        <v>0.08183734500000001</v>
       </c>
       <c r="W33" s="25" t="n"/>
     </row>
@@ -8658,33 +8658,33 @@
         <v>-0.01884</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>-0.021439</v>
+        <v>-0.023471</v>
       </c>
       <c r="M39" s="30" t="n"/>
       <c r="N39" s="29" t="n">
-        <v>-0.004805</v>
+        <v>-0.003609</v>
       </c>
       <c r="O39" s="29" t="n">
-        <v>0.017702</v>
+        <v>0.014559</v>
       </c>
       <c r="P39" s="29" t="n">
-        <v>-0.000947</v>
+        <v>0.001095</v>
       </c>
       <c r="Q39" s="29" t="n">
-        <v>-0.022122</v>
+        <v>-0.023643</v>
       </c>
       <c r="R39" s="30" t="n"/>
       <c r="S39" s="29" t="n">
-        <v>0.013543</v>
+        <v>0.008491</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>-0.00865</v>
+        <v>-0.01369</v>
       </c>
       <c r="U39" s="29" t="n">
-        <v>-0.027101</v>
+        <v>-0.027239</v>
       </c>
       <c r="V39" s="29" t="n">
-        <v>-0.025431</v>
+        <v>-0.027027</v>
       </c>
       <c r="W39" s="30" t="n"/>
     </row>
@@ -8815,39 +8815,39 @@
         <v>0.268401796</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>0.268401815</v>
+        <v>0.268402353</v>
       </c>
       <c r="M41" s="25">
         <f>IFERROR(subQ!M40/subQ!M38,"")</f>
         <v/>
       </c>
       <c r="N41" s="31" t="n">
-        <v>0.268404232</v>
+        <v>0.268404237</v>
       </c>
       <c r="O41" s="31" t="n">
-        <v>0.268403348</v>
+        <v>0.268402743</v>
       </c>
       <c r="P41" s="31" t="n">
-        <v>0.268403678</v>
+        <v>0.268402495</v>
       </c>
       <c r="Q41" s="31" t="n">
-        <v>0.268403991</v>
+        <v>0.268401975</v>
       </c>
       <c r="R41" s="25">
         <f>IFERROR(subQ!R40/subQ!R38,"")</f>
         <v/>
       </c>
       <c r="S41" s="31" t="n">
-        <v>0.268403532</v>
+        <v>0.268402779</v>
       </c>
       <c r="T41" s="31" t="n">
-        <v>0.268402364</v>
+        <v>0.268403942</v>
       </c>
       <c r="U41" s="31" t="n">
-        <v>0.2684037</v>
+        <v>0.268403266</v>
       </c>
       <c r="V41" s="31" t="n">
-        <v>0.268403698</v>
+        <v>0.268403411</v>
       </c>
       <c r="W41" s="25">
         <f>IFERROR(subQ!W40/subQ!W38,"")</f>
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>46050</v>
+        <v>47900</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2275954425437201</v>
+        <v>0.2275948758243246</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02443692359016904</v>
+        <v>0.02443673101699949</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02207088769035088</v>
+        <v>0.02207137908432722</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21838,43 +21838,43 @@
         <v>1418.75</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
     </row>
     <row r="13">
@@ -21904,43 +21904,43 @@
         <v>1433.29</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1413.84</v>
+        <v>1412.76</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1411.89</v>
+        <v>1410.6</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1411.89</v>
+        <v>1410.6</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1414.03</v>
+        <v>1412.74</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>1419.83</v>
+        <v>1418.54</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1420.78</v>
+        <v>1419.49</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>1420.78</v>
+        <v>1419.49</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>1421.04</v>
+        <v>1419.75</v>
       </c>
       <c r="R13" s="13" t="n">
-        <v>1431.47</v>
+        <v>1430.18</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>1425.9</v>
+        <v>1424.61</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>1424.88</v>
+        <v>1423.59</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>1418.21</v>
+        <v>1416.92</v>
       </c>
       <c r="V13" s="13" t="n">
-        <v>1398.97</v>
+        <v>1397.68</v>
       </c>
     </row>
     <row r="14">
@@ -21970,58 +21970,58 @@
         <v>277543</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>278723.9</v>
+        <v>278511</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>272288.6</v>
+        <v>272039.8</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>275314</v>
+        <v>275062.5</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>263359.2</v>
+        <v>263119</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>229925.3</v>
+        <v>229716.4</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>210753.4</v>
+        <v>210562</v>
       </c>
       <c r="P14" s="18" t="n">
-        <v>210753.4</v>
+        <v>210562</v>
       </c>
       <c r="Q14" s="18" t="n">
-        <v>187310.4</v>
+        <v>187140.3</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>147466.3</v>
+        <v>147333.4</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>91441.8</v>
+        <v>91359.10000000001</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>76422.3</v>
+        <v>76353.10000000001</v>
       </c>
       <c r="U14" s="18" t="n">
-        <v>46910.5</v>
+        <v>46867.9</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>20417.2</v>
+        <v>20398.4</v>
       </c>
       <c r="W14" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>1055313.9</v>
+        <v>1055101</v>
       </c>
       <c r="Y14" s="18" t="n">
-        <v>1040887.1</v>
+        <v>1039937.7</v>
       </c>
       <c r="Z14" s="18" t="n">
-        <v>756283.5</v>
+        <v>755597.7</v>
       </c>
       <c r="AA14" s="18" t="n">
-        <v>235191.8</v>
+        <v>234978.5</v>
       </c>
     </row>
     <row r="15">
@@ -22051,58 +22051,58 @@
         <v>277543</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>278723.9</v>
+        <v>278511</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>272288.6</v>
+        <v>272039.8</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>275314</v>
+        <v>275062.5</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>263359.2</v>
+        <v>263119</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>229925.3</v>
+        <v>229716.4</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>210753.4</v>
+        <v>210562</v>
       </c>
       <c r="P15" s="18" t="n">
-        <v>210753.4</v>
+        <v>210562</v>
       </c>
       <c r="Q15" s="18" t="n">
-        <v>187310.4</v>
+        <v>187140.3</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>147466.3</v>
+        <v>147333.4</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>91441.8</v>
+        <v>91359.10000000001</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>76422.3</v>
+        <v>76353.10000000001</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>46910.5</v>
+        <v>46867.9</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>20417.2</v>
+        <v>20398.4</v>
       </c>
       <c r="W15" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>1055313.9</v>
+        <v>1055101</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>1040887.1</v>
+        <v>1039937.7</v>
       </c>
       <c r="Z15" s="18" t="n">
-        <v>756283.5</v>
+        <v>755597.7</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>235191.8</v>
+        <v>234978.5</v>
       </c>
     </row>
     <row r="16">
@@ -22132,43 +22132,43 @@
         <v>262650.7</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>259135.9</v>
+        <v>258938.1</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>253153.2</v>
+        <v>252922.1</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>255966</v>
+        <v>255732.3</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>243798.6</v>
+        <v>243576.4</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>210364.6</v>
+        <v>210173.8</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>191405.3</v>
+        <v>191231.8</v>
       </c>
       <c r="P16" s="18" t="n">
-        <v>191405.3</v>
+        <v>191231.8</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>167749.7</v>
+        <v>167597.7</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>127905.7</v>
+        <v>127790.8</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>72306.39999999999</v>
+        <v>72241.3</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>57074.3</v>
+        <v>57023</v>
       </c>
       <c r="U16" s="18" t="n">
-        <v>27349.9</v>
+        <v>27325.3</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>856.5</v>
+        <v>855.8</v>
       </c>
     </row>
     <row r="17">
@@ -22198,43 +22198,43 @@
         <v>14892.4</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>19587.9</v>
+        <v>19572.8</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>19135.4</v>
+        <v>19117.7</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>19348</v>
+        <v>19330.2</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>19560.6</v>
+        <v>19542.6</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>19560.6</v>
+        <v>19542.6</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>19348</v>
+        <v>19330.2</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>19348</v>
+        <v>19330.2</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>19560.6</v>
+        <v>19542.6</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>19560.6</v>
+        <v>19542.6</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>19135.4</v>
+        <v>19117.7</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>19348</v>
+        <v>19330.2</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>19560.6</v>
+        <v>19542.6</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>19560.6</v>
+        <v>19542.6</v>
       </c>
     </row>
     <row r="18">
@@ -22375,55 +22375,55 @@
         <v/>
       </c>
       <c r="J23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1354.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1351.18)</f>
         <v/>
       </c>
       <c r="K23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="L23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="M23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="N23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="O23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="Q23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="R23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="S23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="T23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="U23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="V23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
     </row>
@@ -27963,7 +27963,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="46" t="n">

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -1468,55 +1468,55 @@
     <comment ref="L39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2589억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2588억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="N39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2529억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 191억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2526억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 191억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2557억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2554억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="P39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2436억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2433억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="Q39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2102억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2099억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="S39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1912억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 1910억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="T39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1912억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 1910억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="U39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1676억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 1674억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="V39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1278억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 1277억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
@@ -2155,37 +2155,37 @@
     </comment>
     <comment ref="P11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8192억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8190억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8957억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8955억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9756억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9753억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10621억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10619억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11498억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11495억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12520억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12516억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2215,37 +2215,37 @@
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8192억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8190억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Q12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8957억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8955억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="S12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9756억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9753억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10621억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10619억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 11498억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 11495억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 12520억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 12516억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3570,55 +3570,55 @@
     </comment>
     <comment ref="L38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2589억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2588억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="N38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2529억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 191억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2526억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 191억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="O38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2557억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2554억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="P38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2436억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2433억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="Q38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2102억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2099억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="S38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1912억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 1910억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="T38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1912억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 1910억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="U38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1676억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 1674억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="V38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1278억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 1277억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -4521,7 +4521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 적용 × 0.8593 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 16건 중 포함 15건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 3.0 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 적용 × 0.8593 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 16건 중 포함 15건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.9 백만원</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 14,599억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −1,897억(2026 345억 · 2027 775억 · 2028 777억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 345억 vs 82억 · 2027 775억 vs 3,561억 · 2028 777억 vs 10,956억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 14,599억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −1,896억(2026 345억 · 2027 774억 · 2028 777억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 345억 vs 82억 · 2027 774억 vs 3,561억 · 2028 777억 vs 10,956억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6525.6</v>
+        <v>6521.8</v>
       </c>
     </row>
     <row r="30">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.34</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="32">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="33">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2073</v>
+        <v>0.2072</v>
       </c>
     </row>
     <row r="34">
@@ -6236,7 +6236,7 @@
         <v>4.48</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>-0</v>
@@ -6637,35 +6637,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -6702,35 +6702,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -6767,35 +6767,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -6832,35 +6832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -6897,35 +6897,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -6962,35 +6962,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -7027,35 +7027,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -7092,35 +7092,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -7174,7 +7174,7 @@
         <v>45700</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>47900</v>
+        <v>47050</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -7300,7 +7300,7 @@
         <v>48174.2</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>46633.3</v>
+        <v>46762.5</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="K29" s="29" t="n">
-        <v>-0.007163479</v>
+        <v>-0.007005623</v>
       </c>
       <c r="L29" s="29" t="n">
-        <v>0.007849182999999999</v>
+        <v>0.012428706</v>
       </c>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="29" t="n">
-        <v>0.005120062</v>
+        <v>0.004914489</v>
       </c>
       <c r="O29" s="29" t="n">
-        <v>95.22007296699999</v>
+        <v>95.219683617</v>
       </c>
       <c r="P29" s="29" t="n">
-        <v>-0.000424953</v>
+        <v>-0.002418262</v>
       </c>
       <c r="Q29" s="29" t="n">
-        <v>-0.00083998</v>
+        <v>0.009775051</v>
       </c>
       <c r="R29" s="30" t="n"/>
       <c r="S29" s="29" t="n">
-        <v>-0.004027772</v>
+        <v>0.003142138</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>95.226824377</v>
+        <v>95.224374235</v>
       </c>
       <c r="U29" s="29" t="n">
-        <v>0.003984354</v>
+        <v>0.001437757</v>
       </c>
       <c r="V29" s="29" t="n">
-        <v>0.003115029</v>
+        <v>0.011645888</v>
       </c>
       <c r="W29" s="30" t="n"/>
     </row>
@@ -8140,36 +8140,36 @@
         <v/>
       </c>
       <c r="K30" s="29" t="n">
-        <v>-0.007163479</v>
+        <v>-0.007005623</v>
       </c>
       <c r="L30" s="29" t="n">
-        <v>0.007849182999999999</v>
+        <v>0.012428706</v>
       </c>
       <c r="M30" s="30" t="n"/>
       <c r="N30" s="29" t="n">
-        <v>0.005120062</v>
+        <v>0.004914489</v>
       </c>
       <c r="O30" s="29" t="n">
-        <v>95.22007296699999</v>
+        <v>95.219683617</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>-0.000424953</v>
+        <v>-0.002418262</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>-0.00083998</v>
+        <v>0.009775051</v>
       </c>
       <c r="R30" s="30" t="n"/>
       <c r="S30" s="29" t="n">
-        <v>-0.004027772</v>
+        <v>0.003142138</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>95.226824377</v>
+        <v>95.224374235</v>
       </c>
       <c r="U30" s="29" t="n">
-        <v>0.003984354</v>
+        <v>0.001437757</v>
       </c>
       <c r="V30" s="29" t="n">
-        <v>0.003115029</v>
+        <v>0.011645888</v>
       </c>
       <c r="W30" s="30" t="n"/>
     </row>
@@ -8307,33 +8307,33 @@
         <v>0.09948617899999999</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.091802965</v>
+        <v>0.091762205</v>
       </c>
       <c r="M33" s="25" t="n"/>
       <c r="N33" s="31" t="n">
-        <v>0.089319047</v>
+        <v>0.089239098</v>
       </c>
       <c r="O33" s="31" t="n">
-        <v>0.0798085</v>
+        <v>0.079739558</v>
       </c>
       <c r="P33" s="31" t="n">
-        <v>0.09345119</v>
+        <v>0.09339913399999999</v>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0.089107231</v>
+        <v>0.089072316</v>
       </c>
       <c r="R33" s="25" t="n"/>
       <c r="S33" s="31" t="n">
-        <v>0.08875638399999999</v>
+        <v>0.08873281299999999</v>
       </c>
       <c r="T33" s="31" t="n">
-        <v>0.082535812</v>
+        <v>0.08251620799999999</v>
       </c>
       <c r="U33" s="31" t="n">
-        <v>0.088839895</v>
+        <v>0.08883209</v>
       </c>
       <c r="V33" s="31" t="n">
-        <v>0.08183734500000001</v>
+        <v>0.081837227</v>
       </c>
       <c r="W33" s="25" t="n"/>
     </row>
@@ -8658,33 +8658,33 @@
         <v>-0.01884</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>-0.023471</v>
+        <v>-0.02022</v>
       </c>
       <c r="M39" s="30" t="n"/>
       <c r="N39" s="29" t="n">
-        <v>-0.003609</v>
+        <v>0.001326</v>
       </c>
       <c r="O39" s="29" t="n">
-        <v>0.014559</v>
+        <v>0.020525</v>
       </c>
       <c r="P39" s="29" t="n">
-        <v>0.001095</v>
+        <v>-0.001784</v>
       </c>
       <c r="Q39" s="29" t="n">
-        <v>-0.023643</v>
+        <v>-0.025714</v>
       </c>
       <c r="R39" s="30" t="n"/>
       <c r="S39" s="29" t="n">
-        <v>0.008491</v>
+        <v>0.006569</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>-0.01369</v>
+        <v>-0.005599</v>
       </c>
       <c r="U39" s="29" t="n">
-        <v>-0.027239</v>
+        <v>-0.029266</v>
       </c>
       <c r="V39" s="29" t="n">
-        <v>-0.027027</v>
+        <v>-0.028259</v>
       </c>
       <c r="W39" s="30" t="n"/>
     </row>
@@ -8815,39 +8815,39 @@
         <v>0.268401796</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>0.268402353</v>
+        <v>0.268404707</v>
       </c>
       <c r="M41" s="25">
         <f>IFERROR(subQ!M40/subQ!M38,"")</f>
         <v/>
       </c>
       <c r="N41" s="31" t="n">
-        <v>0.268404237</v>
+        <v>0.268403831</v>
       </c>
       <c r="O41" s="31" t="n">
-        <v>0.268402743</v>
+        <v>0.268401773</v>
       </c>
       <c r="P41" s="31" t="n">
-        <v>0.268402495</v>
+        <v>0.268403067</v>
       </c>
       <c r="Q41" s="31" t="n">
-        <v>0.268401975</v>
+        <v>0.268404723</v>
       </c>
       <c r="R41" s="25">
         <f>IFERROR(subQ!R40/subQ!R38,"")</f>
         <v/>
       </c>
       <c r="S41" s="31" t="n">
-        <v>0.268402779</v>
+        <v>0.268403701</v>
       </c>
       <c r="T41" s="31" t="n">
-        <v>0.268403942</v>
+        <v>0.26840191</v>
       </c>
       <c r="U41" s="31" t="n">
-        <v>0.268403266</v>
+        <v>0.268404093</v>
       </c>
       <c r="V41" s="31" t="n">
-        <v>0.268403411</v>
+        <v>0.268404072</v>
       </c>
       <c r="W41" s="25">
         <f>IFERROR(subQ!W40/subQ!W38,"")</f>
@@ -9052,11 +9052,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>47900</v>
+        <v>47050</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 45,950원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 45,850원)</t>
         </is>
       </c>
       <c r="H46" s="9" t="n"/>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2275948758243246</v>
+        <v>0.2275950415235869</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02443673101699949</v>
+        <v>0.02443678969646388</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02207137908432722</v>
+        <v>0.02207163051225125</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21838,43 +21838,43 @@
         <v>1418.75</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
     </row>
     <row r="13">
@@ -21904,43 +21904,43 @@
         <v>1433.29</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1412.76</v>
+        <v>1411.83</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1410.6</v>
+        <v>1409.04</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1410.6</v>
+        <v>1409.04</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1412.74</v>
+        <v>1411.18</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>1418.54</v>
+        <v>1416.98</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1419.49</v>
+        <v>1417.93</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>1419.49</v>
+        <v>1417.93</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>1419.75</v>
+        <v>1418.19</v>
       </c>
       <c r="R13" s="13" t="n">
-        <v>1430.18</v>
+        <v>1428.62</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>1424.61</v>
+        <v>1423.05</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>1423.59</v>
+        <v>1422.03</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>1416.92</v>
+        <v>1415.36</v>
       </c>
       <c r="V13" s="13" t="n">
-        <v>1397.68</v>
+        <v>1396.12</v>
       </c>
     </row>
     <row r="14">
@@ -21970,58 +21970,58 @@
         <v>277543</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>278511</v>
+        <v>278327.6</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>272039.8</v>
+        <v>271739</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>275062.5</v>
+        <v>274758.3</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>263119</v>
+        <v>262828.4</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>229716.4</v>
+        <v>229463.7</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>210562</v>
+        <v>210330.6</v>
       </c>
       <c r="P14" s="18" t="n">
-        <v>210562</v>
+        <v>210330.6</v>
       </c>
       <c r="Q14" s="18" t="n">
-        <v>187140.3</v>
+        <v>186934.7</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>147333.4</v>
+        <v>147172.7</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>91359.10000000001</v>
+        <v>91259</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>76353.10000000001</v>
+        <v>76269.39999999999</v>
       </c>
       <c r="U14" s="18" t="n">
-        <v>46867.9</v>
+        <v>46816.3</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>20398.4</v>
+        <v>20375.6</v>
       </c>
       <c r="W14" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>1055101</v>
+        <v>1054917.6</v>
       </c>
       <c r="Y14" s="18" t="n">
-        <v>1039937.7</v>
+        <v>1038789.4</v>
       </c>
       <c r="Z14" s="18" t="n">
-        <v>755597.7</v>
+        <v>754768.6</v>
       </c>
       <c r="AA14" s="18" t="n">
-        <v>234978.5</v>
+        <v>234720.3</v>
       </c>
     </row>
     <row r="15">
@@ -22051,58 +22051,58 @@
         <v>277543</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>278511</v>
+        <v>278327.6</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>272039.8</v>
+        <v>271739</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>275062.5</v>
+        <v>274758.3</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>263119</v>
+        <v>262828.4</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>229716.4</v>
+        <v>229463.7</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>210562</v>
+        <v>210330.6</v>
       </c>
       <c r="P15" s="18" t="n">
-        <v>210562</v>
+        <v>210330.6</v>
       </c>
       <c r="Q15" s="18" t="n">
-        <v>187140.3</v>
+        <v>186934.7</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>147333.4</v>
+        <v>147172.7</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>91359.10000000001</v>
+        <v>91259</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>76353.10000000001</v>
+        <v>76269.39999999999</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>46867.9</v>
+        <v>46816.3</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>20398.4</v>
+        <v>20375.6</v>
       </c>
       <c r="W15" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>1055101</v>
+        <v>1054917.6</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>1039937.7</v>
+        <v>1038789.4</v>
       </c>
       <c r="Z15" s="18" t="n">
-        <v>755597.7</v>
+        <v>754768.6</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>234978.5</v>
+        <v>234720.3</v>
       </c>
     </row>
     <row r="16">
@@ -22132,43 +22132,43 @@
         <v>262650.7</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>258938.1</v>
+        <v>258767.8</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>252922.1</v>
+        <v>252642.6</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>255732.3</v>
+        <v>255449.7</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>243576.4</v>
+        <v>243307.7</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>210173.8</v>
+        <v>209943</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>191231.8</v>
+        <v>191022</v>
       </c>
       <c r="P16" s="18" t="n">
-        <v>191231.8</v>
+        <v>191022</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>167597.7</v>
+        <v>167414</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>127790.8</v>
+        <v>127651.9</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>72241.3</v>
+        <v>72162.60000000001</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>57023</v>
+        <v>56960.9</v>
       </c>
       <c r="U16" s="18" t="n">
-        <v>27325.3</v>
+        <v>27295.5</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>855.8</v>
+        <v>854.8</v>
       </c>
     </row>
     <row r="17">
@@ -22198,43 +22198,43 @@
         <v>14892.4</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>19572.8</v>
+        <v>19559.8</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>19117.7</v>
+        <v>19096.4</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>19330.2</v>
+        <v>19308.6</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>19542.6</v>
+        <v>19520.7</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>19542.6</v>
+        <v>19520.7</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>19330.2</v>
+        <v>19308.6</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>19330.2</v>
+        <v>19308.6</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>19542.6</v>
+        <v>19520.7</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>19542.6</v>
+        <v>19520.7</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>19117.7</v>
+        <v>19096.4</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>19330.2</v>
+        <v>19308.6</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>19542.6</v>
+        <v>19520.7</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>19542.6</v>
+        <v>19520.7</v>
       </c>
     </row>
     <row r="18">
@@ -22375,55 +22375,55 @@
         <v/>
       </c>
       <c r="J23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1351.18)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1348.08)</f>
         <v/>
       </c>
       <c r="K23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="L23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="M23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="N23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="O23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="Q23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="R23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="S23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="T23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="U23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="V23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
     </row>
@@ -27963,7 +27963,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="46" t="n">

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -2011,121 +2011,121 @@
     </comment>
     <comment ref="K9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="L9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="N9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="O9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="P9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="Q9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="S9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="T9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="U9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="V9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="K10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="L10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="N10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="O10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="P10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="Q10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="S10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="T10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="U10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="V10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +11.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 26.8%) + 회사 캘리브레이션 +16.0%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%)
 [divide]</t>
       </text>
     </comment>
@@ -4521,7 +4521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 15.00%→15.00%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 14,599억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −1,896억(2026 345억 · 2027 774억 · 2028 777억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 345억 vs 82억 · 2027 774억 vs 3,561억 · 2028 777억 vs 10,956억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(new_order_revenue, 미보정 book-value proxy, status partial; FY합 14,599억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −1,896억(2026 345억 · 2027 774억 · 2028 777억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 345억 vs 82억 · 2027 774억 vs 3,561억 · 2028 777억 vs 10,956억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21106,7 +21106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>코호트 표(가정): ①적자 −5% ②BEP 0% ③중마진 5% ④호황 10% ⑤초호황 15% — 회사별 캘리브레이션은 target_opm.basis 참조 · 코호트 모드 reference_anchor(대안 ledger_relative) · 잔고 캡 적용 × 0.8593</t>
+          <t>코호트 표(레퍼런스 실측 캘리브레이션): ①적자 −1.1% ②BEP 1% ③중마진 4.3% ④호황 5.4% ⑤초호황 10.8% — 회사별 캘리브레이션은 target_opm.basis 참조 · 코호트 모드 reference_anchor(대안 ledger_relative) · 잔고 캡 적용 × 0.8593</t>
         </is>
       </c>
     </row>
@@ -22249,58 +22249,58 @@
         </is>
       </c>
       <c r="E18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="J18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="K18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="L18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="M18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="N18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="O18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="P18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="Q18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="R18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="S18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="T18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="U18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="V18" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="20">
@@ -26346,7 +26346,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트 OPM 표 assumed 적용. 레퍼런스 미포 SLS 셀 OPM 을 2023~2027 매출가중한 유효 표는 ①-1.1% ②1% ③4.3% ④5.4% ⑤10.8%(가정 표 ①-5% ②0% ③5% ④10% ⑤15% 는 레퍼런스 2024~26 보다 +3.8~5.1%p 높다 — cohort_opm_calibration.by_year). 다음 분기 2026Q3 타겟: 가정 15.00% vs 캘리브레이션 10.80%. 바꾸려면 --opm-table reference_calibrated(오너 결정 — 하류 섹션 각주·모델 백테스트가 cohort_opm_table 을 읽는다)</t>
+          <t>⚠ 코호트 OPM 표 reference_calibrated 적용. 레퍼런스 미포 SLS 셀 OPM 을 2023~2027 매출가중한 유효 표는 ①-1.1% ②1% ③4.3% ④5.4% ⑤10.8%(이전 가정 표 ①-5% ②0% ③5% ④10% ⑤15% 는 레퍼런스 2024~26 보다 +3.8~5.1%p 높다 — cohort_opm_calibration.by_year). 다음 분기 2026Q3 타겟: 가정 15.00% vs 캘리브레이션 10.80%. 다른 표는 --opm-table assumed (하류 섹션 각주·모델 백테스트가 cohort_opm_table 을 읽는다)</t>
         </is>
       </c>
     </row>

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -1468,7 +1468,7 @@
     <comment ref="L39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2588억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2587억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="N39" authorId="0" shapeId="0">
@@ -1516,7 +1516,7 @@
     <comment ref="V39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1277억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 1276억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
@@ -2149,7 +2149,7 @@
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7586억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7585억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2173,13 +2173,13 @@
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10619억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10618억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11495억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11494억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2209,7 +2209,7 @@
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7586억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7585억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2233,13 +2233,13 @@
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10619억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10618억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 11495억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 11494억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3570,7 +3570,7 @@
     </comment>
     <comment ref="L38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2588억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2587억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -3618,7 +3618,7 @@
     </comment>
     <comment ref="V38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1277억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 1276억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -4736,7 +4736,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(new_order_revenue, 미보정 book-value proxy, status partial; FY합 14,599억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −1,896억(2026 345억 · 2027 774억 · 2028 777억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 345억 vs 82억 · 2027 774억 vs 3,561억 · 2028 777억 vs 10,956억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(new_order_revenue, 미보정 book-value proxy, status partial; FY합 14,599억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −1,895억(2026 344억 · 2027 774억 · 2028 777억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 344억 vs 82억 · 2027 774억 vs 3,561억 · 2028 777억 vs 10,956억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6521.8</v>
+        <v>6521.1</v>
       </c>
     </row>
     <row r="30">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.21</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="32">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="33">
@@ -6637,35 +6637,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -6702,35 +6702,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -6767,35 +6767,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -6832,35 +6832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -6897,35 +6897,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -6962,35 +6962,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -7027,35 +7027,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -7092,35 +7092,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -7174,7 +7174,7 @@
         <v>45700</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>47050</v>
+        <v>45250</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -7300,7 +7300,7 @@
         <v>48174.2</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>46762.5</v>
+        <v>46430</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="K29" s="29" t="n">
-        <v>-0.007005623</v>
+        <v>-0.007009003</v>
       </c>
       <c r="L29" s="29" t="n">
-        <v>0.012428706</v>
+        <v>0.007658972</v>
       </c>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="29" t="n">
-        <v>0.004914489</v>
+        <v>-0.001555105</v>
       </c>
       <c r="O29" s="29" t="n">
-        <v>95.219683617</v>
+        <v>95.230924548</v>
       </c>
       <c r="P29" s="29" t="n">
-        <v>-0.002418262</v>
+        <v>-0.001253075</v>
       </c>
       <c r="Q29" s="29" t="n">
-        <v>0.009775051</v>
+        <v>0.003096285</v>
       </c>
       <c r="R29" s="30" t="n"/>
       <c r="S29" s="29" t="n">
-        <v>0.003142138</v>
+        <v>0.004125119</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>95.224374235</v>
+        <v>95.215349914</v>
       </c>
       <c r="U29" s="29" t="n">
-        <v>0.001437757</v>
+        <v>0.002348741</v>
       </c>
       <c r="V29" s="29" t="n">
-        <v>0.011645888</v>
+        <v>0.002344106</v>
       </c>
       <c r="W29" s="30" t="n"/>
     </row>
@@ -8140,36 +8140,36 @@
         <v/>
       </c>
       <c r="K30" s="29" t="n">
-        <v>-0.007005623</v>
+        <v>-0.007009003</v>
       </c>
       <c r="L30" s="29" t="n">
-        <v>0.012428706</v>
+        <v>0.007658972</v>
       </c>
       <c r="M30" s="30" t="n"/>
       <c r="N30" s="29" t="n">
-        <v>0.004914489</v>
+        <v>-0.001555105</v>
       </c>
       <c r="O30" s="29" t="n">
-        <v>95.219683617</v>
+        <v>95.230924548</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>-0.002418262</v>
+        <v>-0.001253075</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>0.009775051</v>
+        <v>0.003096285</v>
       </c>
       <c r="R30" s="30" t="n"/>
       <c r="S30" s="29" t="n">
-        <v>0.003142138</v>
+        <v>0.004125119</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>95.224374235</v>
+        <v>95.215349914</v>
       </c>
       <c r="U30" s="29" t="n">
-        <v>0.001437757</v>
+        <v>0.002348741</v>
       </c>
       <c r="V30" s="29" t="n">
-        <v>0.011645888</v>
+        <v>0.002344106</v>
       </c>
       <c r="W30" s="30" t="n"/>
     </row>
@@ -8307,33 +8307,33 @@
         <v>0.09948617899999999</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.091762205</v>
+        <v>0.09172928299999999</v>
       </c>
       <c r="M33" s="25" t="n"/>
       <c r="N33" s="31" t="n">
-        <v>0.089239098</v>
+        <v>0.08924035299999999</v>
       </c>
       <c r="O33" s="31" t="n">
-        <v>0.079739558</v>
+        <v>0.07973923400000001</v>
       </c>
       <c r="P33" s="31" t="n">
-        <v>0.09339913399999999</v>
+        <v>0.09340065</v>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0.089072316</v>
+        <v>0.089073686</v>
       </c>
       <c r="R33" s="25" t="n"/>
       <c r="S33" s="31" t="n">
-        <v>0.08873281299999999</v>
+        <v>0.088734153</v>
       </c>
       <c r="T33" s="31" t="n">
-        <v>0.08251620799999999</v>
+        <v>0.082518306</v>
       </c>
       <c r="U33" s="31" t="n">
-        <v>0.08883209</v>
+        <v>0.088833307</v>
       </c>
       <c r="V33" s="31" t="n">
-        <v>0.081837227</v>
+        <v>0.08183905800000001</v>
       </c>
       <c r="W33" s="25" t="n"/>
     </row>
@@ -8658,33 +8658,33 @@
         <v>-0.01884</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>-0.02022</v>
+        <v>-0.017281</v>
       </c>
       <c r="M39" s="30" t="n"/>
       <c r="N39" s="29" t="n">
-        <v>0.001326</v>
+        <v>-0.0003</v>
       </c>
       <c r="O39" s="29" t="n">
-        <v>0.020525</v>
+        <v>0.019436</v>
       </c>
       <c r="P39" s="29" t="n">
-        <v>-0.001784</v>
+        <v>0.004724</v>
       </c>
       <c r="Q39" s="29" t="n">
-        <v>-0.025714</v>
+        <v>-0.025769</v>
       </c>
       <c r="R39" s="30" t="n"/>
       <c r="S39" s="29" t="n">
-        <v>0.006569</v>
+        <v>0.012882</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>-0.005599</v>
+        <v>-0.009286000000000001</v>
       </c>
       <c r="U39" s="29" t="n">
-        <v>-0.029266</v>
+        <v>-0.027455</v>
       </c>
       <c r="V39" s="29" t="n">
-        <v>-0.028259</v>
+        <v>-0.034223</v>
       </c>
       <c r="W39" s="30" t="n"/>
     </row>
@@ -8815,39 +8815,39 @@
         <v>0.268401796</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>0.268404707</v>
+        <v>0.268403379</v>
       </c>
       <c r="M41" s="25">
         <f>IFERROR(subQ!M40/subQ!M38,"")</f>
         <v/>
       </c>
       <c r="N41" s="31" t="n">
-        <v>0.268403831</v>
+        <v>0.268401508</v>
       </c>
       <c r="O41" s="31" t="n">
-        <v>0.268401773</v>
+        <v>0.268402842</v>
       </c>
       <c r="P41" s="31" t="n">
-        <v>0.268403067</v>
+        <v>0.268403278</v>
       </c>
       <c r="Q41" s="31" t="n">
-        <v>0.268404723</v>
+        <v>0.268402179</v>
       </c>
       <c r="R41" s="25">
         <f>IFERROR(subQ!R40/subQ!R38,"")</f>
         <v/>
       </c>
       <c r="S41" s="31" t="n">
-        <v>0.268403701</v>
+        <v>0.268403208</v>
       </c>
       <c r="T41" s="31" t="n">
-        <v>0.26840191</v>
+        <v>0.268402076</v>
       </c>
       <c r="U41" s="31" t="n">
-        <v>0.268404093</v>
+        <v>0.268403676</v>
       </c>
       <c r="V41" s="31" t="n">
-        <v>0.268404072</v>
+        <v>0.268403654</v>
       </c>
       <c r="W41" s="25">
         <f>IFERROR(subQ!W40/subQ!W38,"")</f>
@@ -9052,11 +9052,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>47050</v>
+        <v>45250</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 45,850원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 47,600원)</t>
         </is>
       </c>
       <c r="H46" s="9" t="n"/>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2275950415235869</v>
+        <v>0.2275937250057721</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02443678969646388</v>
+        <v>0.02443631581968368</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02207163051225125</v>
+        <v>0.02207074937579081</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -21838,43 +21838,43 @@
         <v>1418.75</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
     </row>
     <row r="13">
@@ -21904,43 +21904,43 @@
         <v>1433.29</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1411.83</v>
+        <v>1411.27</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1409.04</v>
+        <v>1409.01</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1409.04</v>
+        <v>1409.01</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1411.18</v>
+        <v>1411.15</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>1416.98</v>
+        <v>1416.96</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1417.93</v>
+        <v>1417.9</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>1417.93</v>
+        <v>1417.9</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>1418.19</v>
+        <v>1418.16</v>
       </c>
       <c r="R13" s="13" t="n">
-        <v>1428.62</v>
+        <v>1428.59</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>1423.05</v>
+        <v>1423.02</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>1422.03</v>
+        <v>1422</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>1415.36</v>
+        <v>1415.34</v>
       </c>
       <c r="V13" s="13" t="n">
-        <v>1396.12</v>
+        <v>1396.09</v>
       </c>
     </row>
     <row r="14">
@@ -21970,58 +21970,58 @@
         <v>277543</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>278327.6</v>
+        <v>278216.4</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>271739</v>
+        <v>271733.7</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>274758.3</v>
+        <v>274753</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>262828.4</v>
+        <v>262823.4</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>229463.7</v>
+        <v>229459.4</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>210330.6</v>
+        <v>210326.6</v>
       </c>
       <c r="P14" s="18" t="n">
-        <v>210330.6</v>
+        <v>210326.6</v>
       </c>
       <c r="Q14" s="18" t="n">
-        <v>186934.7</v>
+        <v>186931.1</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>147172.7</v>
+        <v>147169.9</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>91259</v>
+        <v>91257.3</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>76269.39999999999</v>
+        <v>76268</v>
       </c>
       <c r="U14" s="18" t="n">
-        <v>46816.3</v>
+        <v>46815.4</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>20375.6</v>
+        <v>20375.2</v>
       </c>
       <c r="W14" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>1054917.6</v>
+        <v>1054806.4</v>
       </c>
       <c r="Y14" s="18" t="n">
-        <v>1038789.4</v>
+        <v>1038769.5</v>
       </c>
       <c r="Z14" s="18" t="n">
-        <v>754768.6</v>
+        <v>754754.2</v>
       </c>
       <c r="AA14" s="18" t="n">
-        <v>234720.3</v>
+        <v>234715.9</v>
       </c>
     </row>
     <row r="15">
@@ -22051,58 +22051,58 @@
         <v>277543</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>278327.6</v>
+        <v>278216.4</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>271739</v>
+        <v>271733.7</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>274758.3</v>
+        <v>274753</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>262828.4</v>
+        <v>262823.4</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>229463.7</v>
+        <v>229459.4</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>210330.6</v>
+        <v>210326.6</v>
       </c>
       <c r="P15" s="18" t="n">
-        <v>210330.6</v>
+        <v>210326.6</v>
       </c>
       <c r="Q15" s="18" t="n">
-        <v>186934.7</v>
+        <v>186931.1</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>147172.7</v>
+        <v>147169.9</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>91259</v>
+        <v>91257.3</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>76269.39999999999</v>
+        <v>76268</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>46816.3</v>
+        <v>46815.4</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>20375.6</v>
+        <v>20375.2</v>
       </c>
       <c r="W15" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>1054917.6</v>
+        <v>1054806.4</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>1038789.4</v>
+        <v>1038769.5</v>
       </c>
       <c r="Z15" s="18" t="n">
-        <v>754768.6</v>
+        <v>754754.2</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>234720.3</v>
+        <v>234715.9</v>
       </c>
     </row>
     <row r="16">
@@ -22132,40 +22132,40 @@
         <v>262650.7</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>258767.8</v>
+        <v>258664.5</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>252642.6</v>
+        <v>252637.7</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>255449.7</v>
+        <v>255444.8</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>243307.7</v>
+        <v>243303</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>209943</v>
+        <v>209939</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>191022</v>
+        <v>191018.4</v>
       </c>
       <c r="P16" s="18" t="n">
-        <v>191022</v>
+        <v>191018.4</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>167414</v>
+        <v>167410.8</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>127651.9</v>
+        <v>127649.5</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>72162.60000000001</v>
+        <v>72161.3</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>56960.9</v>
+        <v>56959.8</v>
       </c>
       <c r="U16" s="18" t="n">
-        <v>27295.5</v>
+        <v>27295</v>
       </c>
       <c r="V16" s="18" t="n">
         <v>854.8</v>
@@ -22198,43 +22198,43 @@
         <v>14892.4</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>19559.8</v>
+        <v>19551.9</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>19096.4</v>
+        <v>19096</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>19308.6</v>
+        <v>19308.2</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>19520.7</v>
+        <v>19520.4</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>19520.7</v>
+        <v>19520.4</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>19308.6</v>
+        <v>19308.2</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>19308.6</v>
+        <v>19308.2</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>19520.7</v>
+        <v>19520.4</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>19520.7</v>
+        <v>19520.4</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>19096.4</v>
+        <v>19096</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>19308.6</v>
+        <v>19308.2</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>19520.7</v>
+        <v>19520.4</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>19520.7</v>
+        <v>19520.4</v>
       </c>
     </row>
     <row r="18">
@@ -22375,55 +22375,55 @@
         <v/>
       </c>
       <c r="J23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1348.08)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1346.2)</f>
         <v/>
       </c>
       <c r="K23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="L23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="M23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="N23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="O23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="Q23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="R23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="S23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="T23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="U23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="V23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
     </row>
@@ -27963,7 +27963,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="46" t="n">

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$W$1</definedName>
@@ -1462,121 +1462,121 @@
     <comment ref="K39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2627억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 149억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2775억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 149억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="L39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2587억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2782억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 196억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="N39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2526억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 191억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2717억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2554억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2748억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="P39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2433억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2628억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="Q39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2099억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2295억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="S39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1910억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2103억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="T39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1910억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 2103억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="U39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1674억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 1869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="V39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1276억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 1472억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="L40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="N40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="O40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="P40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="Q40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="S40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="T40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="U40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="V40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="K41" authorId="0" shapeId="0">
@@ -2137,55 +2137,55 @@
     </comment>
     <comment ref="L11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6379억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6410억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="N11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 6964억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7024억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7585억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="P11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8190억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8248억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8955억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8993억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9753억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9762억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10618억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10596억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11494억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11440억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12516억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12435억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2197,55 +2197,55 @@
     </comment>
     <comment ref="L12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6379억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 6410억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="N12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6964억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7024억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7585억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8190억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8248억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Q12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8955억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8993억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="S12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9753억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9762억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10618억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10596억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 11494억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 11440억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 12516억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 12435억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3564,61 +3564,61 @@
     </comment>
     <comment ref="K38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2627억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 149억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2775억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 149억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="L38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2587억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 82억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 196억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2782억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 196억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="N38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2526억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 307억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 191억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2717억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="O38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2554억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 645억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2748억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="P38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2433억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1067억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2628억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="Q38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2099억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1543억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2295억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="S38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1910억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2042억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2103억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="T38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1910억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2536억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 193억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 2103억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="U38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1674억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2993억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 1869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="V38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1276억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 1건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3385억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 195억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 1472억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -3634,61 +3634,61 @@
     </comment>
     <comment ref="K39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="L39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="N39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="O39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="P39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="Q39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="S39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="T39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="U39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="V39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
@@ -4064,152 +4064,152 @@
   <commentList>
     <comment ref="E12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="E18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
   </commentList>
@@ -4521,7 +4521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>· 신규수주 — forecast_panel base 시나리오를 매출조선신규 행에 포함(calibrated=False, status partial — 통계 흐름, 공시 계약 개별 반영 아님). 보수/낙관/기존만 은 시나리오 시트에만(합산 안 함)</t>
+          <t>· 신규수주 — forecast_panel base 시나리오를 매출조선신규 행에 포함(calibrated=False, status partial — 공시 계약은 체결 분기별로 패널 신규수주와 상계(SLS 일정 유지)). 보수/낙관/기존만 은 시나리오 시트에만(합산 안 함)</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(new_order_revenue, 미보정 book-value proxy, status partial; FY합 14,599억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −1,895억(2026 344억 · 2027 774억 · 2028 777억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 344억 vs 82억 · 2027 774억 vs 3,561억 · 2028 777억 vs 10,956억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,233억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 패널 base 신규 매출 −2,366억(2026 57억 · 2027 1,021억 · 2028 1,288억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 344억 vs 25억 · 2027 774억 vs 2,540억 · 2028 777억 vs 9,669억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6521.1</v>
+        <v>6674.2</v>
       </c>
     </row>
     <row r="30">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.94</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="32">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2072</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="34">
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="35">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>72400</v>
+        <v>74300</v>
       </c>
     </row>
     <row r="36">
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="K29" s="29" t="n">
-        <v>-0.007009003</v>
+        <v>-0.006985525</v>
       </c>
       <c r="L29" s="29" t="n">
-        <v>0.007658972</v>
+        <v>0.006413426</v>
       </c>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="29" t="n">
-        <v>-0.001555105</v>
+        <v>-0.004634707</v>
       </c>
       <c r="O29" s="29" t="n">
-        <v>95.230924548</v>
+        <v>95.221934684</v>
       </c>
       <c r="P29" s="29" t="n">
-        <v>-0.001253075</v>
+        <v>0.001340665</v>
       </c>
       <c r="Q29" s="29" t="n">
-        <v>0.003096285</v>
+        <v>0.002621655</v>
       </c>
       <c r="R29" s="30" t="n"/>
       <c r="S29" s="29" t="n">
-        <v>0.004125119</v>
+        <v>-0.00018603</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>95.215349914</v>
+        <v>95.215685287</v>
       </c>
       <c r="U29" s="29" t="n">
-        <v>0.002348741</v>
+        <v>-0.001338812</v>
       </c>
       <c r="V29" s="29" t="n">
-        <v>0.002344106</v>
+        <v>0.001151214</v>
       </c>
       <c r="W29" s="30" t="n"/>
     </row>
@@ -8140,36 +8140,36 @@
         <v/>
       </c>
       <c r="K30" s="29" t="n">
-        <v>-0.007009003</v>
+        <v>-0.006985525</v>
       </c>
       <c r="L30" s="29" t="n">
-        <v>0.007658972</v>
+        <v>0.006413426</v>
       </c>
       <c r="M30" s="30" t="n"/>
       <c r="N30" s="29" t="n">
-        <v>-0.001555105</v>
+        <v>-0.004634707</v>
       </c>
       <c r="O30" s="29" t="n">
-        <v>95.230924548</v>
+        <v>95.221934684</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>-0.001253075</v>
+        <v>0.001340665</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>0.003096285</v>
+        <v>0.002621655</v>
       </c>
       <c r="R30" s="30" t="n"/>
       <c r="S30" s="29" t="n">
-        <v>0.004125119</v>
+        <v>-0.00018603</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>95.215349914</v>
+        <v>95.215685287</v>
       </c>
       <c r="U30" s="29" t="n">
-        <v>0.002348741</v>
+        <v>-0.001338812</v>
       </c>
       <c r="V30" s="29" t="n">
-        <v>0.002344106</v>
+        <v>0.001151214</v>
       </c>
       <c r="W30" s="30" t="n"/>
     </row>
@@ -8304,36 +8304,36 @@
         <v/>
       </c>
       <c r="K33" s="31" t="n">
-        <v>0.09948617899999999</v>
+        <v>0.104807132</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.09172928299999999</v>
+        <v>0.095786971</v>
       </c>
       <c r="M33" s="25" t="n"/>
       <c r="N33" s="31" t="n">
-        <v>0.08924035299999999</v>
+        <v>0.08951534799999999</v>
       </c>
       <c r="O33" s="31" t="n">
-        <v>0.07973923400000001</v>
+        <v>0.077904479</v>
       </c>
       <c r="P33" s="31" t="n">
-        <v>0.09340065</v>
+        <v>0.090265225</v>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0.089073686</v>
+        <v>0.08555301799999999</v>
       </c>
       <c r="R33" s="25" t="n"/>
       <c r="S33" s="31" t="n">
-        <v>0.088734153</v>
+        <v>0.085338646</v>
       </c>
       <c r="T33" s="31" t="n">
-        <v>0.082518306</v>
+        <v>0.079715842</v>
       </c>
       <c r="U33" s="31" t="n">
-        <v>0.088833307</v>
+        <v>0.086976208</v>
       </c>
       <c r="V33" s="31" t="n">
-        <v>0.08183905800000001</v>
+        <v>0.08102831000000001</v>
       </c>
       <c r="W33" s="25" t="n"/>
     </row>
@@ -8655,36 +8655,36 @@
         <v/>
       </c>
       <c r="K39" s="29" t="n">
-        <v>-0.01884</v>
+        <v>148.90116</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>-0.017281</v>
+        <v>195.492719</v>
       </c>
       <c r="M39" s="30" t="n"/>
       <c r="N39" s="29" t="n">
-        <v>-0.0003</v>
+        <v>190.9497</v>
       </c>
       <c r="O39" s="29" t="n">
-        <v>0.019436</v>
+        <v>193.099436</v>
       </c>
       <c r="P39" s="29" t="n">
-        <v>0.004724</v>
+        <v>195.204724</v>
       </c>
       <c r="Q39" s="29" t="n">
-        <v>-0.025769</v>
+        <v>195.184231</v>
       </c>
       <c r="R39" s="30" t="n"/>
       <c r="S39" s="29" t="n">
-        <v>0.012882</v>
+        <v>193.092882</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>-0.009286000000000001</v>
+        <v>193.080714</v>
       </c>
       <c r="U39" s="29" t="n">
-        <v>-0.027455</v>
+        <v>195.172545</v>
       </c>
       <c r="V39" s="29" t="n">
-        <v>-0.034223</v>
+        <v>195.175777</v>
       </c>
       <c r="W39" s="30" t="n"/>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>매출조선신규 (forecast_panel base 신규수주 매출, 억원 — 가정)</t>
+          <t>매출조선신규 (forecast_panel base · 공시 상계 신규수주 매출, 억원 — 가정)</t>
         </is>
       </c>
       <c r="E40" s="26">
@@ -8732,39 +8732,39 @@
         <v>0</v>
       </c>
       <c r="L40" s="29" t="n">
-        <v>81.61</v>
+        <v>24.58</v>
       </c>
       <c r="M40" s="30">
         <f>subQ!M39</f>
         <v/>
       </c>
       <c r="N40" s="29" t="n">
-        <v>306.54</v>
+        <v>149.36</v>
       </c>
       <c r="O40" s="29" t="n">
-        <v>644.92</v>
+        <v>408.45</v>
       </c>
       <c r="P40" s="29" t="n">
-        <v>1066.89</v>
+        <v>772.01</v>
       </c>
       <c r="Q40" s="29" t="n">
-        <v>1542.57</v>
+        <v>1210.15</v>
       </c>
       <c r="R40" s="30">
         <f>subQ!R39</f>
         <v/>
       </c>
       <c r="S40" s="29" t="n">
-        <v>2042.11</v>
+        <v>1693.02</v>
       </c>
       <c r="T40" s="29" t="n">
-        <v>2535.65</v>
+        <v>2190.75</v>
       </c>
       <c r="U40" s="29" t="n">
-        <v>2993.3</v>
+        <v>2673.48</v>
       </c>
       <c r="V40" s="29" t="n">
-        <v>3385.22</v>
+        <v>3111.34</v>
       </c>
       <c r="W40" s="30">
         <f>subQ!W39</f>
@@ -8812,42 +8812,42 @@
         <v/>
       </c>
       <c r="K41" s="31" t="n">
-        <v>0.268401796</v>
+        <v>0.268401653</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>0.268403379</v>
+        <v>0.268403913</v>
       </c>
       <c r="M41" s="25">
         <f>IFERROR(subQ!M40/subQ!M38,"")</f>
         <v/>
       </c>
       <c r="N41" s="31" t="n">
-        <v>0.268401508</v>
+        <v>0.268403629</v>
       </c>
       <c r="O41" s="31" t="n">
-        <v>0.268402842</v>
+        <v>0.268404743</v>
       </c>
       <c r="P41" s="31" t="n">
-        <v>0.268403278</v>
+        <v>0.268404583</v>
       </c>
       <c r="Q41" s="31" t="n">
-        <v>0.268402179</v>
+        <v>0.268401455</v>
       </c>
       <c r="R41" s="25">
         <f>IFERROR(subQ!R40/subQ!R38,"")</f>
         <v/>
       </c>
       <c r="S41" s="31" t="n">
-        <v>0.268403208</v>
+        <v>0.268404152</v>
       </c>
       <c r="T41" s="31" t="n">
-        <v>0.268402076</v>
+        <v>0.268403501</v>
       </c>
       <c r="U41" s="31" t="n">
-        <v>0.268403676</v>
+        <v>0.268403338</v>
       </c>
       <c r="V41" s="31" t="n">
-        <v>0.268403654</v>
+        <v>0.268402632</v>
       </c>
       <c r="W41" s="25">
         <f>IFERROR(subQ!W40/subQ!W38,"")</f>
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2275937250057721</v>
+        <v>0.2275967157334122</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02443631581968368</v>
+        <v>0.02443688464360349</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02207074937579081</v>
+        <v>0.02207012462183512</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20240,7 +20240,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매출 조선·해양(선박) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(선박) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E39" s="18" t="n"/>
@@ -26474,7 +26474,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) · calibrated=False · 행(subQ)에 포함된 시나리오: base. 보수/낙관/기존만 은 합산하지 않는다. 모델 산출값 — 목표주가·추천 아님</t>
+          <t>출처: forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel) · calibrated=False · 행(subQ)에 포함된 시나리오: base. 보수/낙관/기존만 은 합산하지 않는다. 모델 산출값 — 목표주가·추천 아님</t>
         </is>
       </c>
     </row>
@@ -27258,39 +27258,39 @@
         <v>0</v>
       </c>
       <c r="F18" s="34" t="n">
-        <v>44.89</v>
+        <v>0</v>
       </c>
       <c r="G18" s="20">
         <f>SUM(E18:F18)</f>
         <v/>
       </c>
       <c r="H18" s="34" t="n">
+        <v>44.89</v>
+      </c>
+      <c r="I18" s="34" t="n">
         <v>168.62</v>
       </c>
-      <c r="I18" s="34" t="n">
+      <c r="J18" s="34" t="n">
         <v>354.76</v>
       </c>
-      <c r="J18" s="34" t="n">
+      <c r="K18" s="34" t="n">
         <v>586.88</v>
-      </c>
-      <c r="K18" s="34" t="n">
-        <v>848.54</v>
       </c>
       <c r="L18" s="20">
         <f>SUM(H18:K18)</f>
         <v/>
       </c>
       <c r="M18" s="34" t="n">
+        <v>848.54</v>
+      </c>
+      <c r="N18" s="34" t="n">
         <v>1123.33</v>
       </c>
-      <c r="N18" s="34" t="n">
+      <c r="O18" s="34" t="n">
         <v>1394.82</v>
       </c>
-      <c r="O18" s="34" t="n">
+      <c r="P18" s="34" t="n">
         <v>1646.57</v>
-      </c>
-      <c r="P18" s="34" t="n">
-        <v>1862.15</v>
       </c>
       <c r="Q18" s="20">
         <f>SUM(M18:P18)</f>
@@ -27564,39 +27564,39 @@
         <v>0</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>132.51</v>
+        <v>75.48</v>
       </c>
       <c r="G24" s="20">
         <f>SUM(E24:F24)</f>
         <v/>
       </c>
       <c r="H24" s="34" t="n">
-        <v>497.73</v>
+        <v>340.54</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>1047.15</v>
+        <v>810.6799999999999</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>1732.29</v>
+        <v>1437.41</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>2504.65</v>
+        <v>2172.23</v>
       </c>
       <c r="L24" s="20">
         <f>SUM(H24:K24)</f>
         <v/>
       </c>
       <c r="M24" s="34" t="n">
-        <v>3315.75</v>
+        <v>2966.65</v>
       </c>
       <c r="N24" s="34" t="n">
-        <v>4117.09</v>
+        <v>3772.19</v>
       </c>
       <c r="O24" s="34" t="n">
-        <v>4860.18</v>
+        <v>4540.35</v>
       </c>
       <c r="P24" s="34" t="n">
-        <v>5496.52</v>
+        <v>5222.64</v>
       </c>
       <c r="Q24" s="20">
         <f>SUM(M24:P24)</f>
@@ -30545,7 +30545,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매출 조선·해양(선박) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(선박) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E39" s="18">
@@ -32198,7 +32198,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매출 조선·해양(선박) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(선박) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E39" s="48">

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$W$1</definedName>
@@ -1474,49 +1474,49 @@
     <comment ref="N39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2717억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2720억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2748억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2750억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="P39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2628억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2631억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="Q39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2295억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2297억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="S39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2103억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2105억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="T39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2103억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2105억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="U39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1871억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="V39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1472억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1473억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
@@ -2143,49 +2143,49 @@
     </comment>
     <comment ref="N11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7024억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7023억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7653억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="P11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8248억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8249억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8993억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8995억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9762억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9764억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10596억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10598억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11440억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11443억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12435억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12439억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2203,49 +2203,49 @@
     </comment>
     <comment ref="N12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7024억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7023억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7653억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8248억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8249억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Q12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8993억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8995억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="S12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9762억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9764억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10596억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10598억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 11440억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 11443억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 12435억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 12439억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3576,49 +3576,49 @@
     </comment>
     <comment ref="N38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2717억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2720억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="O38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2748억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2750억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="P38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2628억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2631억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="Q38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2295억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2297억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="S38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2103억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2105억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="T38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2103억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2105억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="U38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1871억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="V38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1472억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1473억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4736,7 +4736,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,233억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 패널 base 신규 매출 −2,366억(2026 57억 · 2027 1,021억 · 2028 1,288억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 344억 vs 25억 · 2027 774억 vs 2,540억 · 2028 777억 vs 9,669억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,233억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 패널 base 신규 매출 −2,366억(2026 57억 · 2027 1,021억 · 2028 1,288억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 344억 vs 25억 · 2027 775억 vs 2,540억 · 2028 777억 vs 9,669억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6674.2</v>
+        <v>6676.9</v>
       </c>
     </row>
     <row r="30">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.78</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="32">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="33">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.212</v>
+        <v>0.2121</v>
       </c>
     </row>
     <row r="34">
@@ -6236,7 +6236,7 @@
         <v>4.48</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>-0</v>
@@ -6637,35 +6637,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -6702,35 +6702,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -6767,35 +6767,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -6832,35 +6832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -6897,35 +6897,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -6962,35 +6962,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -7027,35 +7027,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -7092,35 +7092,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -7174,7 +7174,7 @@
         <v>45700</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>45250</v>
+        <v>44800</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -7258,7 +7258,7 @@
         <v>42100</v>
       </c>
       <c r="L17" s="20" t="n">
-        <v>44800</v>
+        <v>44550</v>
       </c>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="10" t="n"/>
@@ -7300,7 +7300,7 @@
         <v>48174.2</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>46430</v>
+        <v>46340</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="K29" s="29" t="n">
-        <v>-0.006985525</v>
+        <v>-0.004723878</v>
       </c>
       <c r="L29" s="29" t="n">
-        <v>0.006413426</v>
+        <v>0.010373768</v>
       </c>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="29" t="n">
-        <v>-0.004634707</v>
+        <v>-0.001095476</v>
       </c>
       <c r="O29" s="29" t="n">
-        <v>95.221934684</v>
+        <v>95.22586449000001</v>
       </c>
       <c r="P29" s="29" t="n">
-        <v>0.001340665</v>
+        <v>0.007064316</v>
       </c>
       <c r="Q29" s="29" t="n">
-        <v>0.002621655</v>
+        <v>-0.000905154</v>
       </c>
       <c r="R29" s="30" t="n"/>
       <c r="S29" s="29" t="n">
-        <v>-0.00018603</v>
+        <v>0.002346298</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>95.215685287</v>
+        <v>95.230492422</v>
       </c>
       <c r="U29" s="29" t="n">
-        <v>-0.001338812</v>
+        <v>-0.000727811</v>
       </c>
       <c r="V29" s="29" t="n">
-        <v>0.001151214</v>
+        <v>0.008779009000000001</v>
       </c>
       <c r="W29" s="30" t="n"/>
     </row>
@@ -8140,36 +8140,36 @@
         <v/>
       </c>
       <c r="K30" s="29" t="n">
-        <v>-0.006985525</v>
+        <v>-0.004723878</v>
       </c>
       <c r="L30" s="29" t="n">
-        <v>0.006413426</v>
+        <v>0.010373768</v>
       </c>
       <c r="M30" s="30" t="n"/>
       <c r="N30" s="29" t="n">
-        <v>-0.004634707</v>
+        <v>-0.001095476</v>
       </c>
       <c r="O30" s="29" t="n">
-        <v>95.221934684</v>
+        <v>95.22586449000001</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>0.001340665</v>
+        <v>0.007064316</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>0.002621655</v>
+        <v>-0.000905154</v>
       </c>
       <c r="R30" s="30" t="n"/>
       <c r="S30" s="29" t="n">
-        <v>-0.00018603</v>
+        <v>0.002346298</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>95.215685287</v>
+        <v>95.230492422</v>
       </c>
       <c r="U30" s="29" t="n">
-        <v>-0.001338812</v>
+        <v>-0.000727811</v>
       </c>
       <c r="V30" s="29" t="n">
-        <v>0.001151214</v>
+        <v>0.008779009000000001</v>
       </c>
       <c r="W30" s="30" t="n"/>
     </row>
@@ -8307,33 +8307,33 @@
         <v>0.104807132</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.095786971</v>
+        <v>0.095765129</v>
       </c>
       <c r="M33" s="25" t="n"/>
       <c r="N33" s="31" t="n">
-        <v>0.08951534799999999</v>
+        <v>0.089598289</v>
       </c>
       <c r="O33" s="31" t="n">
-        <v>0.077904479</v>
+        <v>0.07797589100000001</v>
       </c>
       <c r="P33" s="31" t="n">
-        <v>0.090265225</v>
+        <v>0.090320844</v>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0.08555301799999999</v>
+        <v>0.085593769</v>
       </c>
       <c r="R33" s="25" t="n"/>
       <c r="S33" s="31" t="n">
-        <v>0.085338646</v>
+        <v>0.085366728</v>
       </c>
       <c r="T33" s="31" t="n">
-        <v>0.079715842</v>
+        <v>0.079738479</v>
       </c>
       <c r="U33" s="31" t="n">
-        <v>0.086976208</v>
+        <v>0.08698961600000001</v>
       </c>
       <c r="V33" s="31" t="n">
-        <v>0.08102831000000001</v>
+        <v>0.081032149</v>
       </c>
       <c r="W33" s="25" t="n"/>
     </row>
@@ -8658,33 +8658,33 @@
         <v>148.90116</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>195.492719</v>
+        <v>195.47546</v>
       </c>
       <c r="M39" s="30" t="n"/>
       <c r="N39" s="29" t="n">
-        <v>190.9497</v>
+        <v>191.145885</v>
       </c>
       <c r="O39" s="29" t="n">
-        <v>193.099436</v>
+        <v>193.297155</v>
       </c>
       <c r="P39" s="29" t="n">
-        <v>195.204724</v>
+        <v>195.409807</v>
       </c>
       <c r="Q39" s="29" t="n">
-        <v>195.184231</v>
+        <v>195.37715</v>
       </c>
       <c r="R39" s="30" t="n"/>
       <c r="S39" s="29" t="n">
-        <v>193.092882</v>
+        <v>193.288299</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>193.080714</v>
+        <v>193.276119</v>
       </c>
       <c r="U39" s="29" t="n">
-        <v>195.172545</v>
+        <v>195.376558</v>
       </c>
       <c r="V39" s="29" t="n">
-        <v>195.175777</v>
+        <v>195.37185</v>
       </c>
       <c r="W39" s="30" t="n"/>
     </row>
@@ -8815,39 +8815,39 @@
         <v>0.268401653</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>0.268403913</v>
+        <v>0.268404793</v>
       </c>
       <c r="M41" s="25">
         <f>IFERROR(subQ!M40/subQ!M38,"")</f>
         <v/>
       </c>
       <c r="N41" s="31" t="n">
-        <v>0.268403629</v>
+        <v>0.268403353</v>
       </c>
       <c r="O41" s="31" t="n">
-        <v>0.268404743</v>
+        <v>0.268405107</v>
       </c>
       <c r="P41" s="31" t="n">
-        <v>0.268404583</v>
+        <v>0.268402632</v>
       </c>
       <c r="Q41" s="31" t="n">
-        <v>0.268401455</v>
+        <v>0.268404304</v>
       </c>
       <c r="R41" s="25">
         <f>IFERROR(subQ!R40/subQ!R38,"")</f>
         <v/>
       </c>
       <c r="S41" s="31" t="n">
-        <v>0.268404152</v>
+        <v>0.268404411</v>
       </c>
       <c r="T41" s="31" t="n">
-        <v>0.268403501</v>
+        <v>0.26840373</v>
       </c>
       <c r="U41" s="31" t="n">
-        <v>0.268403338</v>
+        <v>0.268403936</v>
       </c>
       <c r="V41" s="31" t="n">
-        <v>0.268402632</v>
+        <v>0.268403821</v>
       </c>
       <c r="W41" s="25">
         <f>IFERROR(subQ!W40/subQ!W38,"")</f>
@@ -9052,11 +9052,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>45250</v>
+        <v>44800</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 47,600원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 46,600원)</t>
         </is>
       </c>
       <c r="H46" s="9" t="n"/>
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2275967157334122</v>
+        <v>0.227595398663842</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02443688464360349</v>
+        <v>0.02443698356731461</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02207012462183512</v>
+        <v>0.02207121794200281</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -21838,43 +21838,43 @@
         <v>1418.75</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
     </row>
     <row r="13">
@@ -21904,43 +21904,43 @@
         <v>1433.29</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1411.27</v>
+        <v>1411.13</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1409.01</v>
+        <v>1410.45</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1409.01</v>
+        <v>1410.45</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1411.15</v>
+        <v>1412.58</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>1416.96</v>
+        <v>1418.39</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1417.9</v>
+        <v>1419.33</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>1417.9</v>
+        <v>1419.33</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>1418.16</v>
+        <v>1419.59</v>
       </c>
       <c r="R13" s="13" t="n">
-        <v>1428.59</v>
+        <v>1430.02</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>1423.02</v>
+        <v>1424.45</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>1422</v>
+        <v>1423.43</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>1415.34</v>
+        <v>1416.77</v>
       </c>
       <c r="V13" s="13" t="n">
-        <v>1396.09</v>
+        <v>1397.52</v>
       </c>
     </row>
     <row r="14">
@@ -21970,58 +21970,58 @@
         <v>277543</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>278216.4</v>
+        <v>278189.2</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>271733.7</v>
+        <v>272009.7</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>274753</v>
+        <v>275032.1</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>262823.4</v>
+        <v>263089.9</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>229459.4</v>
+        <v>229691.1</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>210326.6</v>
+        <v>210538.9</v>
       </c>
       <c r="P14" s="18" t="n">
-        <v>210326.6</v>
+        <v>210538.9</v>
       </c>
       <c r="Q14" s="18" t="n">
-        <v>186931.1</v>
+        <v>187119.8</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>147169.9</v>
+        <v>147317.3</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>91257.3</v>
+        <v>91349.10000000001</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>76268</v>
+        <v>76344.7</v>
       </c>
       <c r="U14" s="18" t="n">
-        <v>46815.4</v>
+        <v>46862.7</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>20375.2</v>
+        <v>20396.1</v>
       </c>
       <c r="W14" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>1054806.4</v>
+        <v>1054779.2</v>
       </c>
       <c r="Y14" s="18" t="n">
-        <v>1038769.5</v>
+        <v>1039822.8</v>
       </c>
       <c r="Z14" s="18" t="n">
-        <v>754754.2</v>
+        <v>755514.9</v>
       </c>
       <c r="AA14" s="18" t="n">
-        <v>234715.9</v>
+        <v>234952.6</v>
       </c>
     </row>
     <row r="15">
@@ -22051,58 +22051,58 @@
         <v>277543</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>278216.4</v>
+        <v>278189.2</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>271733.7</v>
+        <v>272009.7</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>274753</v>
+        <v>275032.1</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>262823.4</v>
+        <v>263089.9</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>229459.4</v>
+        <v>229691.1</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>210326.6</v>
+        <v>210538.9</v>
       </c>
       <c r="P15" s="18" t="n">
-        <v>210326.6</v>
+        <v>210538.9</v>
       </c>
       <c r="Q15" s="18" t="n">
-        <v>186931.1</v>
+        <v>187119.8</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>147169.9</v>
+        <v>147317.3</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>91257.3</v>
+        <v>91349.10000000001</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>76268</v>
+        <v>76344.7</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>46815.4</v>
+        <v>46862.7</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>20375.2</v>
+        <v>20396.1</v>
       </c>
       <c r="W15" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>1054806.4</v>
+        <v>1054779.2</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>1038769.5</v>
+        <v>1039822.8</v>
       </c>
       <c r="Z15" s="18" t="n">
-        <v>754754.2</v>
+        <v>755514.9</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>234715.9</v>
+        <v>234952.6</v>
       </c>
     </row>
     <row r="16">
@@ -22132,43 +22132,43 @@
         <v>262650.7</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>258664.5</v>
+        <v>258639.3</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>252637.7</v>
+        <v>252894.1</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>255444.8</v>
+        <v>255704.1</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>243303</v>
+        <v>243549.5</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>209939</v>
+        <v>210150.7</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>191018.4</v>
+        <v>191210.9</v>
       </c>
       <c r="P16" s="18" t="n">
-        <v>191018.4</v>
+        <v>191210.9</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>167410.8</v>
+        <v>167579.4</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>127649.5</v>
+        <v>127776.9</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>72161.3</v>
+        <v>72233.5</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>56959.8</v>
+        <v>57016.7</v>
       </c>
       <c r="U16" s="18" t="n">
-        <v>27295</v>
+        <v>27322.3</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>854.8</v>
+        <v>855.7</v>
       </c>
     </row>
     <row r="17">
@@ -22198,43 +22198,43 @@
         <v>14892.4</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>19551.9</v>
+        <v>19550</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>19096</v>
+        <v>19115.6</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>19308.2</v>
+        <v>19328</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>19520.4</v>
+        <v>19540.4</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>19520.4</v>
+        <v>19540.4</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>19308.2</v>
+        <v>19328</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>19308.2</v>
+        <v>19328</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>19520.4</v>
+        <v>19540.4</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>19520.4</v>
+        <v>19540.4</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>19096</v>
+        <v>19115.6</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>19308.2</v>
+        <v>19328</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>19520.4</v>
+        <v>19540.4</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>19520.4</v>
+        <v>19540.4</v>
       </c>
     </row>
     <row r="18">
@@ -22375,55 +22375,55 @@
         <v/>
       </c>
       <c r="J23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1346.2)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1345.74)</f>
         <v/>
       </c>
       <c r="K23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="L23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="M23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="N23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="O23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="Q23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="R23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="S23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="T23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="U23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="V23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
     </row>

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -1468,31 +1468,31 @@
     <comment ref="L39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2782억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 196억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2782억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="N39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2720억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2719억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2750억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2749억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="P39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2631억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="Q39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2297억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2296억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="S39" authorId="0" shapeId="0">
@@ -1510,7 +1510,7 @@
     <comment ref="U39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1871억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1870억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="V39" authorId="0" shapeId="0">
@@ -2149,7 +2149,7 @@
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7653억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2161,7 +2161,7 @@
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8995억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8994억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2173,19 +2173,19 @@
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10598억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10597억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11443억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11442억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12439억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12437억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2209,7 +2209,7 @@
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7653억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2221,7 +2221,7 @@
     </comment>
     <comment ref="Q12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8995억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8994억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2233,19 +2233,19 @@
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10598억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10597억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 11443억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 11442억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 12439억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 12437억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3570,31 +3570,31 @@
     </comment>
     <comment ref="L38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2782억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 196억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2782억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="N38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2720억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2719억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="O38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2750억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2749억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="P38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2631억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="Q38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2297억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2296억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -3612,7 +3612,7 @@
     </comment>
     <comment ref="U38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1871억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1870억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4521,7 +4521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 적용 × 0.8593 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 16건 중 포함 15건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.9 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 적용 × 0.8593 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 16건 중 포함 15건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 3.0 백만원</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6676.9</v>
+        <v>6675.4</v>
       </c>
     </row>
     <row r="30">
@@ -6236,7 +6236,7 @@
         <v>4.48</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>-0</v>
@@ -6637,35 +6637,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -6702,35 +6702,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -6767,35 +6767,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -6832,35 +6832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -6897,35 +6897,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -6962,35 +6962,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -7027,35 +7027,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -7092,35 +7092,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="K29" s="29" t="n">
-        <v>-0.004723878</v>
+        <v>-0.004498833</v>
       </c>
       <c r="L29" s="29" t="n">
-        <v>0.010373768</v>
+        <v>-0.001804744</v>
       </c>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="29" t="n">
-        <v>-0.001095476</v>
+        <v>-0.000456426</v>
       </c>
       <c r="O29" s="29" t="n">
-        <v>95.22586449000001</v>
+        <v>95.225505591</v>
       </c>
       <c r="P29" s="29" t="n">
-        <v>0.007064316</v>
+        <v>0.011146861</v>
       </c>
       <c r="Q29" s="29" t="n">
-        <v>-0.000905154</v>
+        <v>-0.004629097</v>
       </c>
       <c r="R29" s="30" t="n"/>
       <c r="S29" s="29" t="n">
-        <v>0.002346298</v>
+        <v>0.003239036</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>95.230492422</v>
+        <v>95.220615184</v>
       </c>
       <c r="U29" s="29" t="n">
-        <v>-0.000727811</v>
+        <v>0.011815084</v>
       </c>
       <c r="V29" s="29" t="n">
-        <v>0.008779009000000001</v>
+        <v>-0.008562327999999999</v>
       </c>
       <c r="W29" s="30" t="n"/>
     </row>
@@ -8140,36 +8140,36 @@
         <v/>
       </c>
       <c r="K30" s="29" t="n">
-        <v>-0.004723878</v>
+        <v>-0.004498833</v>
       </c>
       <c r="L30" s="29" t="n">
-        <v>0.010373768</v>
+        <v>-0.001804744</v>
       </c>
       <c r="M30" s="30" t="n"/>
       <c r="N30" s="29" t="n">
-        <v>-0.001095476</v>
+        <v>-0.000456426</v>
       </c>
       <c r="O30" s="29" t="n">
-        <v>95.22586449000001</v>
+        <v>95.225505591</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>0.007064316</v>
+        <v>0.011146861</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>-0.000905154</v>
+        <v>-0.004629097</v>
       </c>
       <c r="R30" s="30" t="n"/>
       <c r="S30" s="29" t="n">
-        <v>0.002346298</v>
+        <v>0.003239036</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>95.230492422</v>
+        <v>95.220615184</v>
       </c>
       <c r="U30" s="29" t="n">
-        <v>-0.000727811</v>
+        <v>0.011815084</v>
       </c>
       <c r="V30" s="29" t="n">
-        <v>0.008779009000000001</v>
+        <v>-0.008562327999999999</v>
       </c>
       <c r="W30" s="30" t="n"/>
     </row>
@@ -8307,33 +8307,33 @@
         <v>0.104807132</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.095765129</v>
+        <v>0.095760448</v>
       </c>
       <c r="M33" s="25" t="n"/>
       <c r="N33" s="31" t="n">
-        <v>0.089598289</v>
+        <v>0.089564501</v>
       </c>
       <c r="O33" s="31" t="n">
-        <v>0.07797589100000001</v>
+        <v>0.07794727999999999</v>
       </c>
       <c r="P33" s="31" t="n">
-        <v>0.090320844</v>
+        <v>0.09029854599999999</v>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0.085593769</v>
+        <v>0.085578574</v>
       </c>
       <c r="R33" s="25" t="n"/>
       <c r="S33" s="31" t="n">
-        <v>0.085366728</v>
+        <v>0.08535548699999999</v>
       </c>
       <c r="T33" s="31" t="n">
-        <v>0.079738479</v>
+        <v>0.079729996</v>
       </c>
       <c r="U33" s="31" t="n">
-        <v>0.08698961600000001</v>
+        <v>0.08698384300000001</v>
       </c>
       <c r="V33" s="31" t="n">
-        <v>0.081032149</v>
+        <v>0.08103220799999999</v>
       </c>
       <c r="W33" s="25" t="n"/>
     </row>
@@ -8658,33 +8658,33 @@
         <v>148.90116</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>195.47546</v>
+        <v>195.455121</v>
       </c>
       <c r="M39" s="30" t="n"/>
       <c r="N39" s="29" t="n">
-        <v>191.145885</v>
+        <v>191.064735</v>
       </c>
       <c r="O39" s="29" t="n">
-        <v>193.297155</v>
+        <v>193.217762</v>
       </c>
       <c r="P39" s="29" t="n">
-        <v>195.409807</v>
+        <v>195.317813</v>
       </c>
       <c r="Q39" s="29" t="n">
-        <v>195.37715</v>
+        <v>195.3015</v>
       </c>
       <c r="R39" s="30" t="n"/>
       <c r="S39" s="29" t="n">
-        <v>193.288299</v>
+        <v>193.203148</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>193.276119</v>
+        <v>193.200973</v>
       </c>
       <c r="U39" s="29" t="n">
-        <v>195.376558</v>
+        <v>195.292867</v>
       </c>
       <c r="V39" s="29" t="n">
-        <v>195.37185</v>
+        <v>195.287979</v>
       </c>
       <c r="W39" s="30" t="n"/>
     </row>
@@ -8815,39 +8815,39 @@
         <v>0.268401653</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>0.268404793</v>
+        <v>0.268402634</v>
       </c>
       <c r="M41" s="25">
         <f>IFERROR(subQ!M40/subQ!M38,"")</f>
         <v/>
       </c>
       <c r="N41" s="31" t="n">
-        <v>0.268403353</v>
+        <v>0.268401951</v>
       </c>
       <c r="O41" s="31" t="n">
-        <v>0.268405107</v>
+        <v>0.268404685</v>
       </c>
       <c r="P41" s="31" t="n">
-        <v>0.268402632</v>
+        <v>0.268404962</v>
       </c>
       <c r="Q41" s="31" t="n">
-        <v>0.268404304</v>
+        <v>0.268402874</v>
       </c>
       <c r="R41" s="25">
         <f>IFERROR(subQ!R40/subQ!R38,"")</f>
         <v/>
       </c>
       <c r="S41" s="31" t="n">
-        <v>0.268404411</v>
+        <v>0.26840341</v>
       </c>
       <c r="T41" s="31" t="n">
-        <v>0.26840373</v>
+        <v>0.268402219</v>
       </c>
       <c r="U41" s="31" t="n">
-        <v>0.268403936</v>
+        <v>0.268403794</v>
       </c>
       <c r="V41" s="31" t="n">
-        <v>0.268403821</v>
+        <v>0.268402452</v>
       </c>
       <c r="W41" s="25">
         <f>IFERROR(subQ!W40/subQ!W38,"")</f>
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.227595398663842</v>
+        <v>0.2275949721551738</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02443698356731461</v>
+        <v>0.02443703447803963</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02207121794200281</v>
+        <v>0.02207111912335032</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21838,43 +21838,43 @@
         <v>1418.75</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
     </row>
     <row r="13">
@@ -21904,43 +21904,43 @@
         <v>1433.29</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1411.13</v>
+        <v>1410.95</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1410.45</v>
+        <v>1409.85</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1410.45</v>
+        <v>1409.85</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1412.58</v>
+        <v>1411.99</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>1418.39</v>
+        <v>1417.8</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1419.33</v>
+        <v>1418.74</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>1419.33</v>
+        <v>1418.74</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>1419.59</v>
+        <v>1419</v>
       </c>
       <c r="R13" s="13" t="n">
-        <v>1430.02</v>
+        <v>1429.43</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>1424.45</v>
+        <v>1423.86</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>1423.43</v>
+        <v>1422.84</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>1416.77</v>
+        <v>1416.18</v>
       </c>
       <c r="V13" s="13" t="n">
-        <v>1397.52</v>
+        <v>1396.93</v>
       </c>
     </row>
     <row r="14">
@@ -21970,58 +21970,58 @@
         <v>277543</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>278189.2</v>
+        <v>278153.7</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>272009.7</v>
+        <v>271895.7</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>275032.1</v>
+        <v>274916.8</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>263089.9</v>
+        <v>262979.8</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>229691.1</v>
+        <v>229595.4</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>210538.9</v>
+        <v>210451.2</v>
       </c>
       <c r="P14" s="18" t="n">
-        <v>210538.9</v>
+        <v>210451.2</v>
       </c>
       <c r="Q14" s="18" t="n">
-        <v>187119.8</v>
+        <v>187041.9</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>147317.3</v>
+        <v>147256.4</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>91349.10000000001</v>
+        <v>91311.2</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>76344.7</v>
+        <v>76313</v>
       </c>
       <c r="U14" s="18" t="n">
-        <v>46862.7</v>
+        <v>46843.2</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>20396.1</v>
+        <v>20387.5</v>
       </c>
       <c r="W14" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>1054779.2</v>
+        <v>1054743.7</v>
       </c>
       <c r="Y14" s="18" t="n">
-        <v>1039822.8</v>
+        <v>1039387.7</v>
       </c>
       <c r="Z14" s="18" t="n">
-        <v>755514.9</v>
+        <v>755200.7</v>
       </c>
       <c r="AA14" s="18" t="n">
-        <v>234952.6</v>
+        <v>234854.9</v>
       </c>
     </row>
     <row r="15">
@@ -22051,58 +22051,58 @@
         <v>277543</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>278189.2</v>
+        <v>278153.7</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>272009.7</v>
+        <v>271895.7</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>275032.1</v>
+        <v>274916.8</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>263089.9</v>
+        <v>262979.8</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>229691.1</v>
+        <v>229595.4</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>210538.9</v>
+        <v>210451.2</v>
       </c>
       <c r="P15" s="18" t="n">
-        <v>210538.9</v>
+        <v>210451.2</v>
       </c>
       <c r="Q15" s="18" t="n">
-        <v>187119.8</v>
+        <v>187041.9</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>147317.3</v>
+        <v>147256.4</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>91349.10000000001</v>
+        <v>91311.2</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>76344.7</v>
+        <v>76313</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>46862.7</v>
+        <v>46843.2</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>20396.1</v>
+        <v>20387.5</v>
       </c>
       <c r="W15" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>1054779.2</v>
+        <v>1054743.7</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>1039822.8</v>
+        <v>1039387.7</v>
       </c>
       <c r="Z15" s="18" t="n">
-        <v>755514.9</v>
+        <v>755200.7</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>234952.6</v>
+        <v>234854.9</v>
       </c>
     </row>
     <row r="16">
@@ -22132,43 +22132,43 @@
         <v>262650.7</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>258639.3</v>
+        <v>258606.3</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>252894.1</v>
+        <v>252788.2</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>255704.1</v>
+        <v>255597</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>243549.5</v>
+        <v>243447.7</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>210150.7</v>
+        <v>210063.3</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>191210.9</v>
+        <v>191131.4</v>
       </c>
       <c r="P16" s="18" t="n">
-        <v>191210.9</v>
+        <v>191131.4</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>167579.4</v>
+        <v>167509.7</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>127776.9</v>
+        <v>127724.3</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>72233.5</v>
+        <v>72203.60000000001</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>57016.7</v>
+        <v>56993.2</v>
       </c>
       <c r="U16" s="18" t="n">
-        <v>27322.3</v>
+        <v>27311</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>855.7</v>
+        <v>855.3</v>
       </c>
     </row>
     <row r="17">
@@ -22198,43 +22198,43 @@
         <v>14892.4</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>19550</v>
+        <v>19547.4</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>19115.6</v>
+        <v>19107.5</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>19328</v>
+        <v>19319.8</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>19540.4</v>
+        <v>19532.1</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>19540.4</v>
+        <v>19532.1</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>19328</v>
+        <v>19319.8</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>19328</v>
+        <v>19319.8</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>19540.4</v>
+        <v>19532.1</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>19540.4</v>
+        <v>19532.1</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>19115.6</v>
+        <v>19107.5</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>19328</v>
+        <v>19319.8</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>19540.4</v>
+        <v>19532.1</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>19540.4</v>
+        <v>19532.1</v>
       </c>
     </row>
     <row r="18">
@@ -22375,55 +22375,55 @@
         <v/>
       </c>
       <c r="J23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1345.74)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1345.14)</f>
         <v/>
       </c>
       <c r="K23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="L23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="M23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="N23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="O23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="Q23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="R23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="S23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="T23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="U23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="V23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
     </row>

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -4521,7 +4521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -4521,7 +4521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.71</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="32">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="33">
@@ -7174,7 +7174,7 @@
         <v>45700</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>44800</v>
+        <v>42500</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -7258,7 +7258,7 @@
         <v>42100</v>
       </c>
       <c r="L17" s="20" t="n">
-        <v>44550</v>
+        <v>41950</v>
       </c>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="10" t="n"/>
@@ -7300,7 +7300,7 @@
         <v>48174.2</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>46340</v>
+        <v>45700</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>44800</v>
+        <v>42500</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27963,7 +27963,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="46" t="n">

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -1468,55 +1468,55 @@
     <comment ref="L39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2782억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2781억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="N39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2719억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2714억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2749억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="P39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2625억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="Q39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2296억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2292억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="S39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2105억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2101억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="T39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2105억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2101억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="U39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1870억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1867억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="V39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1473억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1470억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
@@ -2149,43 +2149,43 @@
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7651억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="P11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8249억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8247억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8994억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8991억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9764억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9760억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10597억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10592억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11442억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11436억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12437억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12431억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2209,43 +2209,43 @@
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7651억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8249억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8247억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Q12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8994억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8991억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="S12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9764억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9760억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10597억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10592억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 11442억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 11436억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 12437억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 12431억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3570,55 +3570,55 @@
     </comment>
     <comment ref="L38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2782억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2781억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="N38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2719억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2714억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="O38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2749억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="P38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2625억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="Q38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2296억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2292억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="S38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2105억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2101억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="T38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2105억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2101억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="U38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1870억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1867억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="V38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1473억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1470억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4521,7 +4521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,233억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 패널 base 신규 매출 −2,366억(2026 57억 · 2027 1,021억 · 2028 1,288억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 344억 vs 25억 · 2027 775억 vs 2,540억 · 2028 777억 vs 9,669억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,233억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 패널 base 신규 매출 −2,366억(2026 57억 · 2027 1,021억 · 2028 1,288억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 344억 vs 25억 · 2027 774억 vs 2,540억 · 2028 776억 vs 9,669억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6675.4</v>
+        <v>6670.1</v>
       </c>
     </row>
     <row r="30">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.37</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="32">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="33">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2121</v>
+        <v>0.2119</v>
       </c>
     </row>
     <row r="34">
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="35">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>74300</v>
+        <v>74000</v>
       </c>
     </row>
     <row r="36">
@@ -6236,7 +6236,7 @@
         <v>4.48</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.32</v>
+        <v>0.51</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>-0</v>
@@ -6637,35 +6637,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -6702,35 +6702,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -6767,35 +6767,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -6832,35 +6832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -6897,35 +6897,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -6962,35 +6962,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -7027,35 +7027,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -7092,35 +7092,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -7174,7 +7174,7 @@
         <v>45700</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>42500</v>
+        <v>41300</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -7258,7 +7258,7 @@
         <v>42100</v>
       </c>
       <c r="L17" s="20" t="n">
-        <v>41950</v>
+        <v>39950</v>
       </c>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="10" t="n"/>
@@ -7300,7 +7300,7 @@
         <v>48174.2</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>45700</v>
+        <v>45028.6</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="K29" s="29" t="n">
-        <v>-0.004498833</v>
+        <v>-0.006750229</v>
       </c>
       <c r="L29" s="29" t="n">
-        <v>-0.001804744</v>
+        <v>-0.000896554</v>
       </c>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="29" t="n">
-        <v>-0.000456426</v>
+        <v>0.002879298</v>
       </c>
       <c r="O29" s="29" t="n">
-        <v>95.225505591</v>
+        <v>95.21885515300001</v>
       </c>
       <c r="P29" s="29" t="n">
-        <v>0.011146861</v>
+        <v>0.006295489</v>
       </c>
       <c r="Q29" s="29" t="n">
-        <v>-0.004629097</v>
+        <v>-0.010187754</v>
       </c>
       <c r="R29" s="30" t="n"/>
       <c r="S29" s="29" t="n">
-        <v>0.003239036</v>
+        <v>0.011012421</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>95.220615184</v>
+        <v>95.21463560799999</v>
       </c>
       <c r="U29" s="29" t="n">
-        <v>0.011815084</v>
+        <v>0.007172448</v>
       </c>
       <c r="V29" s="29" t="n">
-        <v>-0.008562327999999999</v>
+        <v>-0.001829683</v>
       </c>
       <c r="W29" s="30" t="n"/>
     </row>
@@ -8140,36 +8140,36 @@
         <v/>
       </c>
       <c r="K30" s="29" t="n">
-        <v>-0.004498833</v>
+        <v>-0.006750229</v>
       </c>
       <c r="L30" s="29" t="n">
-        <v>-0.001804744</v>
+        <v>-0.000896554</v>
       </c>
       <c r="M30" s="30" t="n"/>
       <c r="N30" s="29" t="n">
-        <v>-0.000456426</v>
+        <v>0.002879298</v>
       </c>
       <c r="O30" s="29" t="n">
-        <v>95.225505591</v>
+        <v>95.21885515300001</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>0.011146861</v>
+        <v>0.006295489</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>-0.004629097</v>
+        <v>-0.010187754</v>
       </c>
       <c r="R30" s="30" t="n"/>
       <c r="S30" s="29" t="n">
-        <v>0.003239036</v>
+        <v>0.011012421</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>95.220615184</v>
+        <v>95.21463560799999</v>
       </c>
       <c r="U30" s="29" t="n">
-        <v>0.011815084</v>
+        <v>0.007172448</v>
       </c>
       <c r="V30" s="29" t="n">
-        <v>-0.008562327999999999</v>
+        <v>-0.001829683</v>
       </c>
       <c r="W30" s="30" t="n"/>
     </row>
@@ -8307,33 +8307,33 @@
         <v>0.104807132</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.095760448</v>
+        <v>0.09575420799999999</v>
       </c>
       <c r="M33" s="25" t="n"/>
       <c r="N33" s="31" t="n">
-        <v>0.089564501</v>
+        <v>0.089421205</v>
       </c>
       <c r="O33" s="31" t="n">
-        <v>0.07794727999999999</v>
+        <v>0.077824668</v>
       </c>
       <c r="P33" s="31" t="n">
-        <v>0.09029854599999999</v>
+        <v>0.090202379</v>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0.085578574</v>
+        <v>0.085511952</v>
       </c>
       <c r="R33" s="25" t="n"/>
       <c r="S33" s="31" t="n">
-        <v>0.08535548699999999</v>
+        <v>0.085308737</v>
       </c>
       <c r="T33" s="31" t="n">
-        <v>0.079729996</v>
+        <v>0.07968984699999999</v>
       </c>
       <c r="U33" s="31" t="n">
-        <v>0.08698384300000001</v>
+        <v>0.08696359300000001</v>
       </c>
       <c r="V33" s="31" t="n">
-        <v>0.08103220799999999</v>
+        <v>0.08102683500000001</v>
       </c>
       <c r="W33" s="25" t="n"/>
     </row>
@@ -8658,33 +8658,33 @@
         <v>148.90116</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>195.455121</v>
+        <v>195.384769</v>
       </c>
       <c r="M39" s="30" t="n"/>
       <c r="N39" s="29" t="n">
-        <v>191.064735</v>
+        <v>190.719629</v>
       </c>
       <c r="O39" s="29" t="n">
-        <v>193.217762</v>
+        <v>192.872785</v>
       </c>
       <c r="P39" s="29" t="n">
-        <v>195.317813</v>
+        <v>194.968546</v>
       </c>
       <c r="Q39" s="29" t="n">
-        <v>195.3015</v>
+        <v>194.939692</v>
       </c>
       <c r="R39" s="30" t="n"/>
       <c r="S39" s="29" t="n">
-        <v>193.203148</v>
+        <v>192.86235</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>193.200973</v>
+        <v>192.850197</v>
       </c>
       <c r="U39" s="29" t="n">
-        <v>195.292867</v>
+        <v>194.9419</v>
       </c>
       <c r="V39" s="29" t="n">
-        <v>195.287979</v>
+        <v>194.941373</v>
       </c>
       <c r="W39" s="30" t="n"/>
     </row>
@@ -8815,39 +8815,39 @@
         <v>0.268401653</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>0.268402634</v>
+        <v>0.268403191</v>
       </c>
       <c r="M41" s="25">
         <f>IFERROR(subQ!M40/subQ!M38,"")</f>
         <v/>
       </c>
       <c r="N41" s="31" t="n">
-        <v>0.268401951</v>
+        <v>0.268403499</v>
       </c>
       <c r="O41" s="31" t="n">
-        <v>0.268404685</v>
+        <v>0.268404008</v>
       </c>
       <c r="P41" s="31" t="n">
-        <v>0.268404962</v>
+        <v>0.268404615</v>
       </c>
       <c r="Q41" s="31" t="n">
-        <v>0.268402874</v>
+        <v>0.268402236</v>
       </c>
       <c r="R41" s="25">
         <f>IFERROR(subQ!R40/subQ!R38,"")</f>
         <v/>
       </c>
       <c r="S41" s="31" t="n">
-        <v>0.26840341</v>
+        <v>0.268403711</v>
       </c>
       <c r="T41" s="31" t="n">
-        <v>0.268402219</v>
+        <v>0.26840311</v>
       </c>
       <c r="U41" s="31" t="n">
-        <v>0.268403794</v>
+        <v>0.268404036</v>
       </c>
       <c r="V41" s="31" t="n">
-        <v>0.268402452</v>
+        <v>0.268403579</v>
       </c>
       <c r="W41" s="25">
         <f>IFERROR(subQ!W40/subQ!W38,"")</f>
@@ -9052,11 +9052,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>42500</v>
+        <v>41300</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 46,600원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 45,100원)</t>
         </is>
       </c>
       <c r="H46" s="9" t="n"/>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2275949721551738</v>
+        <v>0.2275975387712606</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02443703447803963</v>
+        <v>0.0244370908127118</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02207111912335032</v>
+        <v>0.02207091298575637</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21838,43 +21838,43 @@
         <v>1418.75</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
     </row>
     <row r="13">
@@ -21904,43 +21904,43 @@
         <v>1433.29</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1410.95</v>
+        <v>1410.5</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1409.85</v>
+        <v>1407.33</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1409.85</v>
+        <v>1407.33</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1411.99</v>
+        <v>1409.47</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>1417.8</v>
+        <v>1415.28</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1418.74</v>
+        <v>1416.22</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>1418.74</v>
+        <v>1416.22</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>1419</v>
+        <v>1416.48</v>
       </c>
       <c r="R13" s="13" t="n">
-        <v>1429.43</v>
+        <v>1426.91</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>1423.86</v>
+        <v>1421.34</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>1422.84</v>
+        <v>1420.32</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>1416.18</v>
+        <v>1413.66</v>
       </c>
       <c r="V13" s="13" t="n">
-        <v>1396.93</v>
+        <v>1394.41</v>
       </c>
     </row>
     <row r="14">
@@ -21970,58 +21970,58 @@
         <v>277543</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>278153.7</v>
+        <v>278064.4</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>271895.7</v>
+        <v>271409.8</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>274916.8</v>
+        <v>274425.4</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>262979.8</v>
+        <v>262510.5</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>229595.4</v>
+        <v>229187.3</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>210451.2</v>
+        <v>210077.4</v>
       </c>
       <c r="P14" s="18" t="n">
-        <v>210451.2</v>
+        <v>210077.4</v>
       </c>
       <c r="Q14" s="18" t="n">
-        <v>187041.9</v>
+        <v>186709.7</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>147256.4</v>
+        <v>146996.8</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>91311.2</v>
+        <v>91149.60000000001</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>76313</v>
+        <v>76177.89999999999</v>
       </c>
       <c r="U14" s="18" t="n">
-        <v>46843.2</v>
+        <v>46759.8</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>20387.5</v>
+        <v>20350.7</v>
       </c>
       <c r="W14" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>1054743.7</v>
+        <v>1054654.4</v>
       </c>
       <c r="Y14" s="18" t="n">
-        <v>1039387.7</v>
+        <v>1037533</v>
       </c>
       <c r="Z14" s="18" t="n">
-        <v>755200.7</v>
+        <v>753861.3</v>
       </c>
       <c r="AA14" s="18" t="n">
-        <v>234854.9</v>
+        <v>234438</v>
       </c>
     </row>
     <row r="15">
@@ -22051,58 +22051,58 @@
         <v>277543</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>278153.7</v>
+        <v>278064.4</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>271895.7</v>
+        <v>271409.8</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>274916.8</v>
+        <v>274425.4</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>262979.8</v>
+        <v>262510.5</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>229595.4</v>
+        <v>229187.3</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>210451.2</v>
+        <v>210077.4</v>
       </c>
       <c r="P15" s="18" t="n">
-        <v>210451.2</v>
+        <v>210077.4</v>
       </c>
       <c r="Q15" s="18" t="n">
-        <v>187041.9</v>
+        <v>186709.7</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>147256.4</v>
+        <v>146996.8</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>91311.2</v>
+        <v>91149.60000000001</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>76313</v>
+        <v>76177.89999999999</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>46843.2</v>
+        <v>46759.8</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>20387.5</v>
+        <v>20350.7</v>
       </c>
       <c r="W15" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>1054743.7</v>
+        <v>1054654.4</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>1039387.7</v>
+        <v>1037533</v>
       </c>
       <c r="Z15" s="18" t="n">
-        <v>755200.7</v>
+        <v>753861.3</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>234854.9</v>
+        <v>234438</v>
       </c>
     </row>
     <row r="16">
@@ -22132,43 +22132,43 @@
         <v>262650.7</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>258606.3</v>
+        <v>258523.3</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>252788.2</v>
+        <v>252336.7</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>255597</v>
+        <v>255140.5</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>243447.7</v>
+        <v>243013.6</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>210063.3</v>
+        <v>209690.4</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>191131.4</v>
+        <v>190792.5</v>
       </c>
       <c r="P16" s="18" t="n">
-        <v>191131.4</v>
+        <v>190792.5</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>167509.7</v>
+        <v>167212.8</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>127724.3</v>
+        <v>127500</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>72203.60000000001</v>
+        <v>72076.5</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>56993.2</v>
+        <v>56893</v>
       </c>
       <c r="U16" s="18" t="n">
-        <v>27311</v>
+        <v>27263</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>855.3</v>
+        <v>853.8</v>
       </c>
     </row>
     <row r="17">
@@ -22198,43 +22198,43 @@
         <v>14892.4</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>19547.4</v>
+        <v>19541.1</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>19107.5</v>
+        <v>19073</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>19319.8</v>
+        <v>19284.9</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>19532.1</v>
+        <v>19496.9</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>19532.1</v>
+        <v>19496.9</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>19319.8</v>
+        <v>19284.9</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>19319.8</v>
+        <v>19284.9</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>19532.1</v>
+        <v>19496.9</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>19532.1</v>
+        <v>19496.9</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>19107.5</v>
+        <v>19073</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>19319.8</v>
+        <v>19284.9</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>19532.1</v>
+        <v>19496.9</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>19532.1</v>
+        <v>19496.9</v>
       </c>
     </row>
     <row r="18">
@@ -22375,55 +22375,55 @@
         <v/>
       </c>
       <c r="J23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1345.14)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1343.63)</f>
         <v/>
       </c>
       <c r="K23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="L23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="M23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="N23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="O23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="Q23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="R23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="S23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="T23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="U23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="V23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
     </row>
@@ -27963,7 +27963,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="46" t="n">

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -1474,49 +1474,49 @@
     <comment ref="N39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2714억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2719억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2749억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="P39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2625억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="Q39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2292억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2296억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="S39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2101억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2104억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="T39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2101억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2104억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="U39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1867억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1870억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="V39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1470억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1473억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
@@ -2149,43 +2149,43 @@
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7651억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="P11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8247억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8249억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8991억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8994억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9760억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9763억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10592억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10597억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11436억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11442억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12431억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12437억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2209,43 +2209,43 @@
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7651억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8247억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8249억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Q12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8991억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8994억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="S12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9760억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9763억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10592억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10597억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 11436억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 11442억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 12431억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 12437억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3576,49 +3576,49 @@
     </comment>
     <comment ref="N38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2714억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2719억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="O38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2749억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="P38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2625억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="Q38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2292억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2296억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="S38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2101억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2104억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="T38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2101억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2104억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="U38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1867억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1870억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="V38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1470억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1473억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4521,7 +4521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,233억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 패널 base 신규 매출 −2,366억(2026 57억 · 2027 1,021억 · 2028 1,288억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 344억 vs 25억 · 2027 774억 vs 2,540억 · 2028 776억 vs 9,669억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,233억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 패널 base 신규 매출 −2,366억(2026 57억 · 2027 1,021억 · 2028 1,288억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 344억 vs 25억 · 2027 775억 vs 2,540억 · 2028 777억 vs 9,669억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6670.1</v>
+        <v>6674.8</v>
       </c>
     </row>
     <row r="30">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.19</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="32">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="33">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2119</v>
+        <v>0.2121</v>
       </c>
     </row>
     <row r="34">
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="35">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>74000</v>
+        <v>74300</v>
       </c>
     </row>
     <row r="36">
@@ -6236,7 +6236,7 @@
         <v>4.48</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.51</v>
+        <v>0.32</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>-0</v>
@@ -6637,35 +6637,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -6702,35 +6702,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -6767,35 +6767,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -6832,35 +6832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -6897,35 +6897,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -6962,35 +6962,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -7027,35 +7027,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -7092,35 +7092,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -7174,7 +7174,7 @@
         <v>45700</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>41300</v>
+        <v>41900</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -7300,7 +7300,7 @@
         <v>48174.2</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>45028.6</v>
+        <v>44643.8</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="K29" s="29" t="n">
-        <v>-0.006750229</v>
+        <v>-0.005789965</v>
       </c>
       <c r="L29" s="29" t="n">
-        <v>-0.000896554</v>
+        <v>0.001223934</v>
       </c>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="29" t="n">
-        <v>0.002879298</v>
+        <v>-0.002919616</v>
       </c>
       <c r="O29" s="29" t="n">
-        <v>95.21885515300001</v>
+        <v>95.225180491</v>
       </c>
       <c r="P29" s="29" t="n">
-        <v>0.006295489</v>
+        <v>0.000648981</v>
       </c>
       <c r="Q29" s="29" t="n">
-        <v>-0.010187754</v>
+        <v>-0.005272189</v>
       </c>
       <c r="R29" s="30" t="n"/>
       <c r="S29" s="29" t="n">
-        <v>0.011012421</v>
+        <v>0.000109623</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>95.21463560799999</v>
+        <v>95.22729636</v>
       </c>
       <c r="U29" s="29" t="n">
-        <v>0.007172448</v>
+        <v>0.000554141</v>
       </c>
       <c r="V29" s="29" t="n">
-        <v>-0.001829683</v>
+        <v>-0.002287123</v>
       </c>
       <c r="W29" s="30" t="n"/>
     </row>
@@ -8140,36 +8140,36 @@
         <v/>
       </c>
       <c r="K30" s="29" t="n">
-        <v>-0.006750229</v>
+        <v>-0.005789965</v>
       </c>
       <c r="L30" s="29" t="n">
-        <v>-0.000896554</v>
+        <v>0.001223934</v>
       </c>
       <c r="M30" s="30" t="n"/>
       <c r="N30" s="29" t="n">
-        <v>0.002879298</v>
+        <v>-0.002919616</v>
       </c>
       <c r="O30" s="29" t="n">
-        <v>95.21885515300001</v>
+        <v>95.225180491</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>0.006295489</v>
+        <v>0.000648981</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>-0.010187754</v>
+        <v>-0.005272189</v>
       </c>
       <c r="R30" s="30" t="n"/>
       <c r="S30" s="29" t="n">
-        <v>0.011012421</v>
+        <v>0.000109623</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>95.21463560799999</v>
+        <v>95.22729636</v>
       </c>
       <c r="U30" s="29" t="n">
-        <v>0.007172448</v>
+        <v>0.000554141</v>
       </c>
       <c r="V30" s="29" t="n">
-        <v>-0.001829683</v>
+        <v>-0.002287123</v>
       </c>
       <c r="W30" s="30" t="n"/>
     </row>
@@ -8307,33 +8307,33 @@
         <v>0.104807132</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.09575420799999999</v>
+        <v>0.095726125</v>
       </c>
       <c r="M33" s="25" t="n"/>
       <c r="N33" s="31" t="n">
-        <v>0.089421205</v>
+        <v>0.089567306</v>
       </c>
       <c r="O33" s="31" t="n">
-        <v>0.077824668</v>
+        <v>0.077948214</v>
       </c>
       <c r="P33" s="31" t="n">
-        <v>0.090202379</v>
+        <v>0.090301064</v>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0.085511952</v>
+        <v>0.08557964999999999</v>
       </c>
       <c r="R33" s="25" t="n"/>
       <c r="S33" s="31" t="n">
-        <v>0.085308737</v>
+        <v>0.085357585</v>
       </c>
       <c r="T33" s="31" t="n">
-        <v>0.07968984699999999</v>
+        <v>0.079730858</v>
       </c>
       <c r="U33" s="31" t="n">
-        <v>0.08696359300000001</v>
+        <v>0.086985744</v>
       </c>
       <c r="V33" s="31" t="n">
-        <v>0.08102683500000001</v>
+        <v>0.081033033</v>
       </c>
       <c r="W33" s="25" t="n"/>
     </row>
@@ -8658,33 +8658,33 @@
         <v>148.90116</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>195.384769</v>
+        <v>195.376633</v>
       </c>
       <c r="M39" s="30" t="n"/>
       <c r="N39" s="29" t="n">
-        <v>190.719629</v>
+        <v>191.066234</v>
       </c>
       <c r="O39" s="29" t="n">
-        <v>192.872785</v>
+        <v>193.2195</v>
       </c>
       <c r="P39" s="29" t="n">
-        <v>194.968546</v>
+        <v>195.318483</v>
       </c>
       <c r="Q39" s="29" t="n">
-        <v>194.939692</v>
+        <v>195.299253</v>
       </c>
       <c r="R39" s="30" t="n"/>
       <c r="S39" s="29" t="n">
-        <v>192.86235</v>
+        <v>193.209287</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>192.850197</v>
+        <v>193.197112</v>
       </c>
       <c r="U39" s="29" t="n">
-        <v>194.9419</v>
+        <v>195.287005</v>
       </c>
       <c r="V39" s="29" t="n">
-        <v>194.941373</v>
+        <v>195.288662</v>
       </c>
       <c r="W39" s="30" t="n"/>
     </row>
@@ -8815,39 +8815,39 @@
         <v>0.268401653</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>0.268403191</v>
+        <v>0.268402327</v>
       </c>
       <c r="M41" s="25">
         <f>IFERROR(subQ!M40/subQ!M38,"")</f>
         <v/>
       </c>
       <c r="N41" s="31" t="n">
-        <v>0.268403499</v>
+        <v>0.268403822</v>
       </c>
       <c r="O41" s="31" t="n">
-        <v>0.268404008</v>
+        <v>0.268403218</v>
       </c>
       <c r="P41" s="31" t="n">
-        <v>0.268404615</v>
+        <v>0.2684036</v>
       </c>
       <c r="Q41" s="31" t="n">
-        <v>0.268402236</v>
+        <v>0.268401553</v>
       </c>
       <c r="R41" s="25">
         <f>IFERROR(subQ!R40/subQ!R38,"")</f>
         <v/>
       </c>
       <c r="S41" s="31" t="n">
-        <v>0.268403711</v>
+        <v>0.268404116</v>
       </c>
       <c r="T41" s="31" t="n">
-        <v>0.26840311</v>
+        <v>0.268403469</v>
       </c>
       <c r="U41" s="31" t="n">
-        <v>0.268404036</v>
+        <v>0.268402775</v>
       </c>
       <c r="V41" s="31" t="n">
-        <v>0.268403579</v>
+        <v>0.268403038</v>
       </c>
       <c r="W41" s="25">
         <f>IFERROR(subQ!W40/subQ!W38,"")</f>
@@ -9052,11 +9052,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>41300</v>
+        <v>41900</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 45,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 41,950원)</t>
         </is>
       </c>
       <c r="H46" s="9" t="n"/>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2275975387712606</v>
+        <v>0.2275952512424075</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.0244370908127118</v>
+        <v>0.02443671713340683</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02207091298575637</v>
+        <v>0.02207016273858089</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21838,43 +21838,43 @@
         <v>1418.75</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
     </row>
     <row r="13">
@@ -21904,43 +21904,43 @@
         <v>1433.29</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1410.5</v>
+        <v>1410.42</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1407.33</v>
+        <v>1409.84</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1407.33</v>
+        <v>1409.84</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1409.47</v>
+        <v>1411.98</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>1415.28</v>
+        <v>1417.79</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1416.22</v>
+        <v>1418.73</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>1416.22</v>
+        <v>1418.73</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>1416.48</v>
+        <v>1418.99</v>
       </c>
       <c r="R13" s="13" t="n">
-        <v>1426.91</v>
+        <v>1429.42</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>1421.34</v>
+        <v>1423.85</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>1420.32</v>
+        <v>1422.83</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>1413.66</v>
+        <v>1416.16</v>
       </c>
       <c r="V13" s="13" t="n">
-        <v>1394.41</v>
+        <v>1396.92</v>
       </c>
     </row>
     <row r="14">
@@ -21970,58 +21970,58 @@
         <v>277543</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>278064.4</v>
+        <v>278050.2</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>271409.8</v>
+        <v>271893.4</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>274425.4</v>
+        <v>274914.5</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>262510.5</v>
+        <v>262977.6</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>229187.3</v>
+        <v>229593.4</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>210077.4</v>
+        <v>210449.4</v>
       </c>
       <c r="P14" s="18" t="n">
-        <v>210077.4</v>
+        <v>210449.4</v>
       </c>
       <c r="Q14" s="18" t="n">
-        <v>186709.7</v>
+        <v>187040.3</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>146996.8</v>
+        <v>147255.2</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>91149.60000000001</v>
+        <v>91310.39999999999</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>76177.89999999999</v>
+        <v>76312.39999999999</v>
       </c>
       <c r="U14" s="18" t="n">
-        <v>46759.8</v>
+        <v>46842.8</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>20350.7</v>
+        <v>20387.3</v>
       </c>
       <c r="W14" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>1054654.4</v>
+        <v>1054640.2</v>
       </c>
       <c r="Y14" s="18" t="n">
-        <v>1037533</v>
+        <v>1039378.9</v>
       </c>
       <c r="Z14" s="18" t="n">
-        <v>753861.3</v>
+        <v>755194.3</v>
       </c>
       <c r="AA14" s="18" t="n">
-        <v>234438</v>
+        <v>234852.9</v>
       </c>
     </row>
     <row r="15">
@@ -22051,58 +22051,58 @@
         <v>277543</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>278064.4</v>
+        <v>278050.2</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>271409.8</v>
+        <v>271893.4</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>274425.4</v>
+        <v>274914.5</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>262510.5</v>
+        <v>262977.6</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>229187.3</v>
+        <v>229593.4</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>210077.4</v>
+        <v>210449.4</v>
       </c>
       <c r="P15" s="18" t="n">
-        <v>210077.4</v>
+        <v>210449.4</v>
       </c>
       <c r="Q15" s="18" t="n">
-        <v>186709.7</v>
+        <v>187040.3</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>146996.8</v>
+        <v>147255.2</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>91149.60000000001</v>
+        <v>91310.39999999999</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>76177.89999999999</v>
+        <v>76312.39999999999</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>46759.8</v>
+        <v>46842.8</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>20350.7</v>
+        <v>20387.3</v>
       </c>
       <c r="W15" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>1054654.4</v>
+        <v>1054640.2</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>1037533</v>
+        <v>1039378.9</v>
       </c>
       <c r="Z15" s="18" t="n">
-        <v>753861.3</v>
+        <v>755194.3</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>234438</v>
+        <v>234852.9</v>
       </c>
     </row>
     <row r="16">
@@ -22132,43 +22132,43 @@
         <v>262650.7</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>258523.3</v>
+        <v>258510.1</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>252336.7</v>
+        <v>252786.1</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>255140.5</v>
+        <v>255594.8</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>243013.6</v>
+        <v>243445.6</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>209690.4</v>
+        <v>210061.5</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>190792.5</v>
+        <v>191129.8</v>
       </c>
       <c r="P16" s="18" t="n">
-        <v>190792.5</v>
+        <v>191129.8</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>167212.8</v>
+        <v>167508.3</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>127500</v>
+        <v>127723.3</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>72076.5</v>
+        <v>72203</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>56893</v>
+        <v>56992.8</v>
       </c>
       <c r="U16" s="18" t="n">
-        <v>27263</v>
+        <v>27310.8</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>853.8</v>
+        <v>855.3</v>
       </c>
     </row>
     <row r="17">
@@ -22198,43 +22198,43 @@
         <v>14892.4</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>19541.1</v>
+        <v>19540.1</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>19073</v>
+        <v>19107.3</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>19284.9</v>
+        <v>19319.7</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>19496.9</v>
+        <v>19532</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>19496.9</v>
+        <v>19532</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>19284.9</v>
+        <v>19319.7</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>19284.9</v>
+        <v>19319.7</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>19496.9</v>
+        <v>19532</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>19496.9</v>
+        <v>19532</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>19073</v>
+        <v>19107.3</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>19284.9</v>
+        <v>19319.7</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>19496.9</v>
+        <v>19532</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>19496.9</v>
+        <v>19532</v>
       </c>
     </row>
     <row r="18">
@@ -22375,55 +22375,55 @@
         <v/>
       </c>
       <c r="J23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1343.63)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1343.39)</f>
         <v/>
       </c>
       <c r="K23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="L23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="M23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="N23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="O23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="Q23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="R23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="S23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="T23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="U23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="V23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
     </row>
@@ -27963,7 +27963,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="46" t="n">

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -1468,55 +1468,55 @@
     <comment ref="L39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2781억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2780억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="N39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2719억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2714억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2749억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="P39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2625억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="Q39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2296억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2291억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="S39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2104억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="T39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2104억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="U39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1870억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1867억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="V39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1473억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1470억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
@@ -2149,43 +2149,43 @@
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7651억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="P11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8249억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8246억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8994억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8990억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9763억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9759억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10597억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10591억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11442억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11435억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12437억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12430억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2209,43 +2209,43 @@
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7652억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7651억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8249억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8246억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Q12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8994억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8990억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="S12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9763억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9759억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10597억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10591억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 11442억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 11435억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 12437억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 12430억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3570,55 +3570,55 @@
     </comment>
     <comment ref="L38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2781억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2780억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="N38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2719억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2714억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="O38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2749억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="P38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2630억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2625억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="Q38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2296억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2291억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="S38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2104억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="T38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2104억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="U38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1870억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1867억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="V38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1473억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1470억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4521,7 +4521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4684,7 +4684,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 적용 × 0.8593 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 16건 중 포함 15건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 3.0 백만원</t>
+          <t>· 선표(SLS) — 헤지비율 70.0%(estimate) · 헤지환율 계약별 수주시점 환율 · 코호트 모드 reference_anchor · 잔고 캡 적용 × 0.8593 · subQ 매출조선 = SLS 합계/100 + 원장 밖 잔고 소진(변수 drv:매출조선, 역산) + 매출조선신규 — 계약 16건 중 포함 15건(marine_hedged_krw_m_signed_by_origin), 재구성 최대차 2.9 백만원</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,233억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 패널 base 신규 매출 −2,366억(2026 57억 · 2027 1,021억 · 2028 1,288억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 344억 vs 25억 · 2027 775억 vs 2,540억 · 2028 777억 vs 9,669억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,233억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 패널 base 신규 매출 −2,366억(2026 57억 · 2027 1,021억 · 2028 1,288억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 344억 vs 25억 · 2027 773억 vs 2,540억 · 2028 775억 vs 9,669억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6674.8</v>
+        <v>6668.9</v>
       </c>
     </row>
     <row r="30">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.28</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="32">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="33">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2121</v>
+        <v>0.2119</v>
       </c>
     </row>
     <row r="34">
@@ -5187,7 +5187,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="35">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>74300</v>
+        <v>74000</v>
       </c>
     </row>
     <row r="36">
@@ -6236,7 +6236,7 @@
         <v>4.48</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.32</v>
+        <v>0.53</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>-0</v>
@@ -6637,35 +6637,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -6702,35 +6702,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -6767,35 +6767,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -6832,35 +6832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -6897,35 +6897,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -6962,35 +6962,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -7027,35 +7027,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -7092,35 +7092,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -7174,7 +7174,7 @@
         <v>45700</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>41900</v>
+        <v>42300</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -7258,7 +7258,7 @@
         <v>42100</v>
       </c>
       <c r="L17" s="20" t="n">
-        <v>39950</v>
+        <v>36000</v>
       </c>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="10" t="n"/>
@@ -7300,7 +7300,7 @@
         <v>48174.2</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>44643.8</v>
+        <v>43540.9</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="K29" s="29" t="n">
-        <v>-0.005789965</v>
+        <v>-0.004564584</v>
       </c>
       <c r="L29" s="29" t="n">
-        <v>0.001223934</v>
+        <v>0.003521965</v>
       </c>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="29" t="n">
-        <v>-0.002919616</v>
+        <v>0.008695982999999999</v>
       </c>
       <c r="O29" s="29" t="n">
-        <v>95.225180491</v>
+        <v>95.216664959</v>
       </c>
       <c r="P29" s="29" t="n">
-        <v>0.000648981</v>
+        <v>0.011520516</v>
       </c>
       <c r="Q29" s="29" t="n">
-        <v>-0.005272189</v>
+        <v>0.007858871999999999</v>
       </c>
       <c r="R29" s="30" t="n"/>
       <c r="S29" s="29" t="n">
-        <v>0.000109623</v>
+        <v>-0.001116828</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>95.22729636</v>
+        <v>95.222439416</v>
       </c>
       <c r="U29" s="29" t="n">
-        <v>0.000554141</v>
+        <v>0.002559039</v>
       </c>
       <c r="V29" s="29" t="n">
-        <v>-0.002287123</v>
+        <v>-0.001169388</v>
       </c>
       <c r="W29" s="30" t="n"/>
     </row>
@@ -8140,36 +8140,36 @@
         <v/>
       </c>
       <c r="K30" s="29" t="n">
-        <v>-0.005789965</v>
+        <v>-0.004564584</v>
       </c>
       <c r="L30" s="29" t="n">
-        <v>0.001223934</v>
+        <v>0.003521965</v>
       </c>
       <c r="M30" s="30" t="n"/>
       <c r="N30" s="29" t="n">
-        <v>-0.002919616</v>
+        <v>0.008695982999999999</v>
       </c>
       <c r="O30" s="29" t="n">
-        <v>95.225180491</v>
+        <v>95.216664959</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>0.000648981</v>
+        <v>0.011520516</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>-0.005272189</v>
+        <v>0.007858871999999999</v>
       </c>
       <c r="R30" s="30" t="n"/>
       <c r="S30" s="29" t="n">
-        <v>0.000109623</v>
+        <v>-0.001116828</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>95.22729636</v>
+        <v>95.222439416</v>
       </c>
       <c r="U30" s="29" t="n">
-        <v>0.000554141</v>
+        <v>0.002559039</v>
       </c>
       <c r="V30" s="29" t="n">
-        <v>-0.002287123</v>
+        <v>-0.001169388</v>
       </c>
       <c r="W30" s="30" t="n"/>
     </row>
@@ -8307,33 +8307,33 @@
         <v>0.104807132</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.095726125</v>
+        <v>0.09572768500000001</v>
       </c>
       <c r="M33" s="25" t="n"/>
       <c r="N33" s="31" t="n">
-        <v>0.089567306</v>
+        <v>0.089406284</v>
       </c>
       <c r="O33" s="31" t="n">
-        <v>0.077948214</v>
+        <v>0.077811934</v>
       </c>
       <c r="P33" s="31" t="n">
-        <v>0.090301064</v>
+        <v>0.090192312</v>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0.08557964999999999</v>
+        <v>0.08550587</v>
       </c>
       <c r="R33" s="25" t="n"/>
       <c r="S33" s="31" t="n">
-        <v>0.085357585</v>
+        <v>0.08530399700000001</v>
       </c>
       <c r="T33" s="31" t="n">
-        <v>0.079730858</v>
+        <v>0.07968684199999999</v>
       </c>
       <c r="U33" s="31" t="n">
-        <v>0.086985744</v>
+        <v>0.086962833</v>
       </c>
       <c r="V33" s="31" t="n">
-        <v>0.081033033</v>
+        <v>0.08102707000000001</v>
       </c>
       <c r="W33" s="25" t="n"/>
     </row>
@@ -8658,33 +8658,33 @@
         <v>148.90116</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>195.376633</v>
+        <v>195.319911</v>
       </c>
       <c r="M39" s="30" t="n"/>
       <c r="N39" s="29" t="n">
-        <v>191.066234</v>
+        <v>190.681742</v>
       </c>
       <c r="O39" s="29" t="n">
-        <v>193.2195</v>
+        <v>192.830805</v>
       </c>
       <c r="P39" s="29" t="n">
-        <v>195.318483</v>
+        <v>194.930132</v>
       </c>
       <c r="Q39" s="29" t="n">
-        <v>195.299253</v>
+        <v>194.899086</v>
       </c>
       <c r="R39" s="30" t="n"/>
       <c r="S39" s="29" t="n">
-        <v>193.209287</v>
+        <v>192.811792</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>193.197112</v>
+        <v>192.809641</v>
       </c>
       <c r="U39" s="29" t="n">
-        <v>195.287005</v>
+        <v>194.901822</v>
       </c>
       <c r="V39" s="29" t="n">
-        <v>195.288662</v>
+        <v>194.895773</v>
       </c>
       <c r="W39" s="30" t="n"/>
     </row>
@@ -8815,39 +8815,39 @@
         <v>0.268401653</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>0.268402327</v>
+        <v>0.268403749</v>
       </c>
       <c r="M41" s="25">
         <f>IFERROR(subQ!M40/subQ!M38,"")</f>
         <v/>
       </c>
       <c r="N41" s="31" t="n">
-        <v>0.268403822</v>
+        <v>0.268404544</v>
       </c>
       <c r="O41" s="31" t="n">
-        <v>0.268403218</v>
+        <v>0.268402636</v>
       </c>
       <c r="P41" s="31" t="n">
-        <v>0.2684036</v>
+        <v>0.268403915</v>
       </c>
       <c r="Q41" s="31" t="n">
-        <v>0.268401553</v>
+        <v>0.268404759</v>
       </c>
       <c r="R41" s="25">
         <f>IFERROR(subQ!R40/subQ!R38,"")</f>
         <v/>
       </c>
       <c r="S41" s="31" t="n">
-        <v>0.268404116</v>
+        <v>0.268403917</v>
       </c>
       <c r="T41" s="31" t="n">
-        <v>0.268403469</v>
+        <v>0.268402667</v>
       </c>
       <c r="U41" s="31" t="n">
-        <v>0.268402775</v>
+        <v>0.268402864</v>
       </c>
       <c r="V41" s="31" t="n">
-        <v>0.268403038</v>
+        <v>0.268402096</v>
       </c>
       <c r="W41" s="25">
         <f>IFERROR(subQ!W40/subQ!W38,"")</f>
@@ -9052,11 +9052,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>41900</v>
+        <v>42300</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 41,950원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 39,100원)</t>
         </is>
       </c>
       <c r="H46" s="9" t="n"/>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2275952512424075</v>
+        <v>0.2275957840130833</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02443671713340683</v>
+        <v>0.02443664868022551</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02207016273858089</v>
+        <v>0.02207163090952749</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21838,43 +21838,43 @@
         <v>1418.75</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
     </row>
     <row r="13">
@@ -21904,43 +21904,43 @@
         <v>1433.29</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1410.42</v>
+        <v>1410.04</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1409.84</v>
+        <v>1407.04</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1409.84</v>
+        <v>1407.04</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1411.98</v>
+        <v>1409.17</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>1417.79</v>
+        <v>1414.98</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1418.73</v>
+        <v>1415.93</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>1418.73</v>
+        <v>1415.93</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>1418.99</v>
+        <v>1416.18</v>
       </c>
       <c r="R13" s="13" t="n">
-        <v>1429.42</v>
+        <v>1426.62</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>1423.85</v>
+        <v>1421.04</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>1422.83</v>
+        <v>1420.03</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>1416.16</v>
+        <v>1413.36</v>
       </c>
       <c r="V13" s="13" t="n">
-        <v>1396.92</v>
+        <v>1394.12</v>
       </c>
     </row>
     <row r="14">
@@ -21970,58 +21970,58 @@
         <v>277543</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>278050.2</v>
+        <v>277974.5</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>271893.4</v>
+        <v>271352.5</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>274914.5</v>
+        <v>274367.5</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>262977.6</v>
+        <v>262455.2</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>229593.4</v>
+        <v>229139.2</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>210449.4</v>
+        <v>210033.3</v>
       </c>
       <c r="P14" s="18" t="n">
-        <v>210449.4</v>
+        <v>210033.3</v>
       </c>
       <c r="Q14" s="18" t="n">
-        <v>187040.3</v>
+        <v>186670.5</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>147255.2</v>
+        <v>146966.2</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>91310.39999999999</v>
+        <v>91130.5</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>76312.39999999999</v>
+        <v>76162</v>
       </c>
       <c r="U14" s="18" t="n">
-        <v>46842.8</v>
+        <v>46750</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>20387.3</v>
+        <v>20346.3</v>
       </c>
       <c r="W14" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>1054640.2</v>
+        <v>1054564.5</v>
       </c>
       <c r="Y14" s="18" t="n">
-        <v>1039378.9</v>
+        <v>1037314.4</v>
       </c>
       <c r="Z14" s="18" t="n">
-        <v>755194.3</v>
+        <v>753703.3</v>
       </c>
       <c r="AA14" s="18" t="n">
-        <v>234852.9</v>
+        <v>234388.8</v>
       </c>
     </row>
     <row r="15">
@@ -22051,58 +22051,58 @@
         <v>277543</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>278050.2</v>
+        <v>277974.5</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>271893.4</v>
+        <v>271352.5</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>274914.5</v>
+        <v>274367.5</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>262977.6</v>
+        <v>262455.2</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>229593.4</v>
+        <v>229139.2</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>210449.4</v>
+        <v>210033.3</v>
       </c>
       <c r="P15" s="18" t="n">
-        <v>210449.4</v>
+        <v>210033.3</v>
       </c>
       <c r="Q15" s="18" t="n">
-        <v>187040.3</v>
+        <v>186670.5</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>147255.2</v>
+        <v>146966.2</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>91310.39999999999</v>
+        <v>91130.5</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>76312.39999999999</v>
+        <v>76162</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>46842.8</v>
+        <v>46750</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>20387.3</v>
+        <v>20346.3</v>
       </c>
       <c r="W15" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>1054640.2</v>
+        <v>1054564.5</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>1039378.9</v>
+        <v>1037314.4</v>
       </c>
       <c r="Z15" s="18" t="n">
-        <v>755194.3</v>
+        <v>753703.3</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>234852.9</v>
+        <v>234388.8</v>
       </c>
     </row>
     <row r="16">
@@ -22132,43 +22132,43 @@
         <v>262650.7</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>258510.1</v>
+        <v>258439.8</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>252786.1</v>
+        <v>252283.5</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>255594.8</v>
+        <v>255086.7</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>243445.6</v>
+        <v>242962.5</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>210061.5</v>
+        <v>209646.5</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>191129.8</v>
+        <v>190752.5</v>
       </c>
       <c r="P16" s="18" t="n">
-        <v>191129.8</v>
+        <v>190752.5</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>167508.3</v>
+        <v>167177.9</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>127723.3</v>
+        <v>127473.5</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>72203</v>
+        <v>72061.60000000001</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>56992.8</v>
+        <v>56881.1</v>
       </c>
       <c r="U16" s="18" t="n">
-        <v>27310.8</v>
+        <v>27257.3</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>855.3</v>
+        <v>853.6</v>
       </c>
     </row>
     <row r="17">
@@ -22198,43 +22198,43 @@
         <v>14892.4</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>19540.1</v>
+        <v>19534.7</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>19107.3</v>
+        <v>19068.9</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>19319.7</v>
+        <v>19280.8</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>19532</v>
+        <v>19492.7</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>19532</v>
+        <v>19492.7</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>19319.7</v>
+        <v>19280.8</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>19319.7</v>
+        <v>19280.8</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>19532</v>
+        <v>19492.7</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>19532</v>
+        <v>19492.7</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>19107.3</v>
+        <v>19068.9</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>19319.7</v>
+        <v>19280.8</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>19532</v>
+        <v>19492.7</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>19532</v>
+        <v>19492.7</v>
       </c>
     </row>
     <row r="18">
@@ -22375,55 +22375,55 @@
         <v/>
       </c>
       <c r="J23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1343.39)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1342.11)</f>
         <v/>
       </c>
       <c r="K23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="L23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="M23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="N23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="O23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="Q23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="R23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="S23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="T23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="U23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="V23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
     </row>
@@ -27963,7 +27963,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="46" t="n">

--- a/argus/kship/models/439260_model.xlsx
+++ b/argus/kship/models/439260_model.xlsx
@@ -1468,55 +1468,55 @@
     <comment ref="L39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2780억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2777억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="N39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2714억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2709억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 190억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="O39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2739억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 192억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="P39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2625억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2620억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="Q39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2291억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2288억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="S39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2097억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 192억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="T39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 2100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 2097억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 192억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="U39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1867억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1864억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="V39" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 1539.96; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 1470억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 1467억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="K40" authorId="0" shapeId="0">
@@ -2149,43 +2149,43 @@
     </comment>
     <comment ref="O11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7651억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 7650억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="P11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8246억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8244억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8990억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 8987억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9759억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 9755억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10591억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 10587억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11435억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 11430억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12430억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 3분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 12424억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2209,43 +2209,43 @@
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7651억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7650억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8246억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8244억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Q12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8990억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8987억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="S12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9759억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9755억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10591억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10587억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 11435억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 11430억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 12430억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 12424억 × 2.21%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3570,55 +3570,55 @@
     </comment>
     <comment ref="L38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2780억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2777억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 25억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="N38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2714억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 191억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2709억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 149억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 190억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="O38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2744억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2739억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 408억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 192억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="P38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2625억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2620억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 772억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="Q38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2291억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2288억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1210억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="S38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2097억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 1693억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 192억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="T38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 2100억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 193억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 2097억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2191억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 192억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="U38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1867억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1864억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 2673억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="V38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 1470억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 1467억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 1건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 0억(최근 4분기 '부문매출−SLS' 중위 1540억/분기, 잔여 0억) + 신규수주 매출 3111억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억)) · origin 이후 공시 수주 SLS 195억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4521,7 +4521,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,233억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 패널 base 신규 매출 −2,366억(2026 57억 · 2027 1,021억 · 2028 1,288억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 344억 vs 25억 · 2027 773억 vs 2,540억 · 2028 775억 vs 9,669억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 원장 잔여가 공시 잔고를 넘음(커버리지 &gt; 1) → 원장 밖 소진분 0 (sls warnings 참고) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 26.8% 채움에서만, 추정 구간 타겟 10.80%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 12,233억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 1건 2,713억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 3,882억 − 공시 2,713억 = 1,169억) — 패널 base 신규 매출 −2,366억(2026 57억 · 2027 1,021억 · 2028 1,288억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 1건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 2,713억 vs 패널 base 신규수주 3,882억(70%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 344억 vs 25억 · 2027 772억 vs 2,540억 · 2028 774억 vs 9,669억 / SLS 선표 잔고 캡 적용 — 원장 잔여가 공시 잔고를 넘어 R3 가 줄인 값(sls.backlog_cap_applied) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -291/-223/-457/-254(중위 -272억) → 추정 2026Q3 +32억(차 +304억, +112%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6668.9</v>
+        <v>6663</v>
       </c>
     </row>
     <row r="30">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.34</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="32">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="33">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2119</v>
+        <v>0.2117</v>
       </c>
     </row>
     <row r="34">
@@ -6236,7 +6236,7 @@
         <v>4.48</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.53</v>
+        <v>0.71</v>
       </c>
       <c r="L18" s="20" t="n">
         <v>-0</v>
@@ -6637,35 +6637,35 @@
         <v>1418.75</v>
       </c>
       <c r="L6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="M6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="N6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="O6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="R6" s="11" t="n"/>
       <c r="S6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="W6" s="11" t="n"/>
     </row>
@@ -6702,35 +6702,35 @@
         <v>1355.4</v>
       </c>
       <c r="L7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="M7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="N7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="O7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="R7" s="11" t="n"/>
       <c r="S7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="W7" s="11" t="n"/>
     </row>
@@ -6767,35 +6767,35 @@
         <v>890.41</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="M8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="N8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="R8" s="11" t="n"/>
       <c r="S8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="W8" s="11" t="n"/>
     </row>
@@ -6832,35 +6832,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="L9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="M9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="N9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="O9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="W9" s="11" t="n"/>
     </row>
@@ -6897,35 +6897,35 @@
         <v>1631.97</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="N10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="R10" s="11" t="n"/>
       <c r="S10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="W10" s="11" t="n"/>
     </row>
@@ -6962,35 +6962,35 @@
         <v>1539.06</v>
       </c>
       <c r="L11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="M11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="N11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="O11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="R11" s="11" t="n"/>
       <c r="S11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="W11" s="11" t="n"/>
     </row>
@@ -7027,35 +7027,35 @@
         <v>210.43</v>
       </c>
       <c r="L12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="M12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="N12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="R12" s="11" t="n"/>
       <c r="S12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="W12" s="11" t="n"/>
     </row>
@@ -7092,35 +7092,35 @@
         <v>202.16</v>
       </c>
       <c r="L13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="M13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="N13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="O13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="R13" s="11" t="n"/>
       <c r="S13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="W13" s="11" t="n"/>
     </row>
@@ -7174,7 +7174,7 @@
         <v>45700</v>
       </c>
       <c r="L15" s="20" t="n">
-        <v>42300</v>
+        <v>36300</v>
       </c>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="10" t="n"/>
@@ -7300,7 +7300,7 @@
         <v>48174.2</v>
       </c>
       <c r="L18" s="20" t="n">
-        <v>43540.9</v>
+        <v>41781.2</v>
       </c>
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="10" t="n"/>
@@ -8072,36 +8072,36 @@
         <v/>
       </c>
       <c r="K29" s="29" t="n">
-        <v>-0.004564584</v>
+        <v>-0.002984413</v>
       </c>
       <c r="L29" s="29" t="n">
-        <v>0.003521965</v>
+        <v>0.006568021</v>
       </c>
       <c r="M29" s="30" t="n"/>
       <c r="N29" s="29" t="n">
-        <v>0.008695982999999999</v>
+        <v>0.009323013999999999</v>
       </c>
       <c r="O29" s="29" t="n">
-        <v>95.216664959</v>
+        <v>95.21585199899999</v>
       </c>
       <c r="P29" s="29" t="n">
-        <v>0.011520516</v>
+        <v>0.005459945</v>
       </c>
       <c r="Q29" s="29" t="n">
-        <v>0.007858871999999999</v>
+        <v>0.013927137</v>
       </c>
       <c r="R29" s="30" t="n"/>
       <c r="S29" s="29" t="n">
-        <v>-0.001116828</v>
+        <v>-0.00645696</v>
       </c>
       <c r="T29" s="29" t="n">
-        <v>95.222439416</v>
+        <v>95.232031272</v>
       </c>
       <c r="U29" s="29" t="n">
-        <v>0.002559039</v>
+        <v>0.006423135</v>
       </c>
       <c r="V29" s="29" t="n">
-        <v>-0.001169388</v>
+        <v>-0.001016982</v>
       </c>
       <c r="W29" s="30" t="n"/>
     </row>
@@ -8140,36 +8140,36 @@
         <v/>
       </c>
       <c r="K30" s="29" t="n">
-        <v>-0.004564584</v>
+        <v>-0.002984413</v>
       </c>
       <c r="L30" s="29" t="n">
-        <v>0.003521965</v>
+        <v>0.006568021</v>
       </c>
       <c r="M30" s="30" t="n"/>
       <c r="N30" s="29" t="n">
-        <v>0.008695982999999999</v>
+        <v>0.009323013999999999</v>
       </c>
       <c r="O30" s="29" t="n">
-        <v>95.216664959</v>
+        <v>95.21585199899999</v>
       </c>
       <c r="P30" s="29" t="n">
-        <v>0.011520516</v>
+        <v>0.005459945</v>
       </c>
       <c r="Q30" s="29" t="n">
-        <v>0.007858871999999999</v>
+        <v>0.013927137</v>
       </c>
       <c r="R30" s="30" t="n"/>
       <c r="S30" s="29" t="n">
-        <v>-0.001116828</v>
+        <v>-0.00645696</v>
       </c>
       <c r="T30" s="29" t="n">
-        <v>95.222439416</v>
+        <v>95.232031272</v>
       </c>
       <c r="U30" s="29" t="n">
-        <v>0.002559039</v>
+        <v>0.006423135</v>
       </c>
       <c r="V30" s="29" t="n">
-        <v>-0.001169388</v>
+        <v>-0.001016982</v>
       </c>
       <c r="W30" s="30" t="n"/>
     </row>
@@ -8307,33 +8307,33 @@
         <v>0.104807132</v>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.09572768500000001</v>
+        <v>0.095660599</v>
       </c>
       <c r="M33" s="25" t="n"/>
       <c r="N33" s="31" t="n">
-        <v>0.089406284</v>
+        <v>0.08928218</v>
       </c>
       <c r="O33" s="31" t="n">
-        <v>0.077811934</v>
+        <v>0.07770268499999999</v>
       </c>
       <c r="P33" s="31" t="n">
-        <v>0.090192312</v>
+        <v>0.090109301</v>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0.08550587</v>
+        <v>0.085448126</v>
       </c>
       <c r="R33" s="25" t="n"/>
       <c r="S33" s="31" t="n">
-        <v>0.08530399700000001</v>
+        <v>0.08526481700000001</v>
       </c>
       <c r="T33" s="31" t="n">
-        <v>0.07968684199999999</v>
+        <v>0.079653115</v>
       </c>
       <c r="U33" s="31" t="n">
-        <v>0.086962833</v>
+        <v>0.086947126</v>
       </c>
       <c r="V33" s="31" t="n">
-        <v>0.08102707000000001</v>
+        <v>0.08102554300000001</v>
       </c>
       <c r="W33" s="25" t="n"/>
     </row>
@@ -8658,33 +8658,33 @@
         <v>148.90116</v>
       </c>
       <c r="L39" s="29" t="n">
-        <v>195.319911</v>
+        <v>195.128304</v>
       </c>
       <c r="M39" s="30" t="n"/>
       <c r="N39" s="29" t="n">
-        <v>190.681742</v>
+        <v>190.363521</v>
       </c>
       <c r="O39" s="29" t="n">
-        <v>192.830805</v>
+        <v>192.508237</v>
       </c>
       <c r="P39" s="29" t="n">
-        <v>194.930132</v>
+        <v>194.6033</v>
       </c>
       <c r="Q39" s="29" t="n">
-        <v>194.899086</v>
+        <v>194.584404</v>
       </c>
       <c r="R39" s="30" t="n"/>
       <c r="S39" s="29" t="n">
-        <v>192.811792</v>
+        <v>192.498387</v>
       </c>
       <c r="T39" s="29" t="n">
-        <v>192.809641</v>
+        <v>192.486256</v>
       </c>
       <c r="U39" s="29" t="n">
-        <v>194.901822</v>
+        <v>194.575763</v>
       </c>
       <c r="V39" s="29" t="n">
-        <v>194.895773</v>
+        <v>194.578864</v>
       </c>
       <c r="W39" s="30" t="n"/>
     </row>
@@ -8815,39 +8815,39 @@
         <v>0.268401653</v>
       </c>
       <c r="L41" s="31" t="n">
-        <v>0.268403749</v>
+        <v>0.268404727</v>
       </c>
       <c r="M41" s="25">
         <f>IFERROR(subQ!M40/subQ!M38,"")</f>
         <v/>
       </c>
       <c r="N41" s="31" t="n">
-        <v>0.268404544</v>
+        <v>0.268404205</v>
       </c>
       <c r="O41" s="31" t="n">
-        <v>0.268402636</v>
+        <v>0.268403412</v>
       </c>
       <c r="P41" s="31" t="n">
-        <v>0.268403915</v>
+        <v>0.268403552</v>
       </c>
       <c r="Q41" s="31" t="n">
-        <v>0.268404759</v>
+        <v>0.268403553</v>
       </c>
       <c r="R41" s="25">
         <f>IFERROR(subQ!R40/subQ!R38,"")</f>
         <v/>
       </c>
       <c r="S41" s="31" t="n">
-        <v>0.268403917</v>
+        <v>0.268401958</v>
       </c>
       <c r="T41" s="31" t="n">
-        <v>0.268402667</v>
+        <v>0.268403892</v>
       </c>
       <c r="U41" s="31" t="n">
-        <v>0.268402864</v>
+        <v>0.268403583</v>
       </c>
       <c r="V41" s="31" t="n">
-        <v>0.268402096</v>
+        <v>0.268402845</v>
       </c>
       <c r="W41" s="25">
         <f>IFERROR(subQ!W40/subQ!W38,"")</f>
@@ -9052,11 +9052,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>42300</v>
+        <v>36300</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 39,100원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 38,000원)</t>
         </is>
       </c>
       <c r="H46" s="9" t="n"/>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2275957840130833</v>
+        <v>0.2275937210756476</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02443664868022551</v>
+        <v>0.02443659469514871</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02207163090952749</v>
+        <v>0.02207159181874941</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21838,43 +21838,43 @@
         <v>1418.75</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="N12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="R12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="S12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="T12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
     </row>
     <row r="13">
@@ -21904,43 +21904,43 @@
         <v>1433.29</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>1410.04</v>
+        <v>1408.65</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>1407.04</v>
+        <v>1404.74</v>
       </c>
       <c r="L13" s="13" t="n">
-        <v>1407.04</v>
+        <v>1404.74</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1409.17</v>
+        <v>1406.88</v>
       </c>
       <c r="N13" s="13" t="n">
-        <v>1414.98</v>
+        <v>1412.69</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>1415.93</v>
+        <v>1413.63</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>1415.93</v>
+        <v>1413.63</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>1416.18</v>
+        <v>1413.89</v>
       </c>
       <c r="R13" s="13" t="n">
-        <v>1426.62</v>
+        <v>1424.32</v>
       </c>
       <c r="S13" s="13" t="n">
-        <v>1421.04</v>
+        <v>1418.75</v>
       </c>
       <c r="T13" s="13" t="n">
-        <v>1420.03</v>
+        <v>1417.73</v>
       </c>
       <c r="U13" s="13" t="n">
-        <v>1413.36</v>
+        <v>1411.06</v>
       </c>
       <c r="V13" s="13" t="n">
-        <v>1394.12</v>
+        <v>1391.82</v>
       </c>
     </row>
     <row r="14">
@@ -21970,58 +21970,58 @@
         <v>277543</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>277974.5</v>
+        <v>277701.3</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>271352.5</v>
+        <v>270909.9</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>274367.5</v>
+        <v>273920</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>262455.2</v>
+        <v>262027.7</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>229139.2</v>
+        <v>228767.6</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>210033.3</v>
+        <v>209692.9</v>
       </c>
       <c r="P14" s="18" t="n">
-        <v>210033.3</v>
+        <v>209692.9</v>
       </c>
       <c r="Q14" s="18" t="n">
-        <v>186670.5</v>
+        <v>186368</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>146966.2</v>
+        <v>146729.8</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>91130.5</v>
+        <v>90983.3</v>
       </c>
       <c r="T14" s="18" t="n">
-        <v>76162</v>
+        <v>76038.89999999999</v>
       </c>
       <c r="U14" s="18" t="n">
-        <v>46750</v>
+        <v>46674.1</v>
       </c>
       <c r="V14" s="18" t="n">
-        <v>20346.3</v>
+        <v>20312.8</v>
       </c>
       <c r="W14" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X14" s="18" t="n">
-        <v>1054564.5</v>
+        <v>1054291.3</v>
       </c>
       <c r="Y14" s="18" t="n">
-        <v>1037314.4</v>
+        <v>1035625.2</v>
       </c>
       <c r="Z14" s="18" t="n">
-        <v>753703.3</v>
+        <v>752483.6</v>
       </c>
       <c r="AA14" s="18" t="n">
-        <v>234388.8</v>
+        <v>234009.1</v>
       </c>
     </row>
     <row r="15">
@@ -22051,58 +22051,58 @@
         <v>277543</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>277974.5</v>
+        <v>277701.3</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>271352.5</v>
+        <v>270909.9</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>274367.5</v>
+        <v>273920</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>262455.2</v>
+        <v>262027.7</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>229139.2</v>
+        <v>228767.6</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>210033.3</v>
+        <v>209692.9</v>
       </c>
       <c r="P15" s="18" t="n">
-        <v>210033.3</v>
+        <v>209692.9</v>
       </c>
       <c r="Q15" s="18" t="n">
-        <v>186670.5</v>
+        <v>186368</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>146966.2</v>
+        <v>146729.8</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>91130.5</v>
+        <v>90983.3</v>
       </c>
       <c r="T15" s="18" t="n">
-        <v>76162</v>
+        <v>76038.89999999999</v>
       </c>
       <c r="U15" s="18" t="n">
-        <v>46750</v>
+        <v>46674.1</v>
       </c>
       <c r="V15" s="18" t="n">
-        <v>20346.3</v>
+        <v>20312.8</v>
       </c>
       <c r="W15" s="18" t="n">
         <v>145742.2</v>
       </c>
       <c r="X15" s="18" t="n">
-        <v>1054564.5</v>
+        <v>1054291.3</v>
       </c>
       <c r="Y15" s="18" t="n">
-        <v>1037314.4</v>
+        <v>1035625.2</v>
       </c>
       <c r="Z15" s="18" t="n">
-        <v>753703.3</v>
+        <v>752483.6</v>
       </c>
       <c r="AA15" s="18" t="n">
-        <v>234388.8</v>
+        <v>234009.1</v>
       </c>
     </row>
     <row r="16">
@@ -22132,43 +22132,43 @@
         <v>262650.7</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>258439.8</v>
+        <v>258186</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>252283.5</v>
+        <v>251872.4</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>255086.7</v>
+        <v>254670.9</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>242962.5</v>
+        <v>242567.2</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>209646.5</v>
+        <v>209307</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>190752.5</v>
+        <v>190443.8</v>
       </c>
       <c r="P16" s="18" t="n">
-        <v>190752.5</v>
+        <v>190443.8</v>
       </c>
       <c r="Q16" s="18" t="n">
-        <v>167177.9</v>
+        <v>166907.5</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>127473.5</v>
+        <v>127269.2</v>
       </c>
       <c r="S16" s="18" t="n">
-        <v>72061.60000000001</v>
+        <v>71945.8</v>
       </c>
       <c r="T16" s="18" t="n">
-        <v>56881.1</v>
+        <v>56789.8</v>
       </c>
       <c r="U16" s="18" t="n">
-        <v>27257.3</v>
+        <v>27213.5</v>
       </c>
       <c r="V16" s="18" t="n">
-        <v>853.6</v>
+        <v>852.3</v>
       </c>
     </row>
     <row r="17">
@@ -22198,43 +22198,43 @@
         <v>14892.4</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>19534.7</v>
+        <v>19515.3</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>19068.9</v>
+        <v>19037.5</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>19280.8</v>
+        <v>19249</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>19492.7</v>
+        <v>19460.6</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>19492.7</v>
+        <v>19460.6</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>19280.8</v>
+        <v>19249</v>
       </c>
       <c r="P17" s="18" t="n">
-        <v>19280.8</v>
+        <v>19249</v>
       </c>
       <c r="Q17" s="18" t="n">
-        <v>19492.7</v>
+        <v>19460.6</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>19492.7</v>
+        <v>19460.6</v>
       </c>
       <c r="S17" s="18" t="n">
-        <v>19068.9</v>
+        <v>19037.5</v>
       </c>
       <c r="T17" s="18" t="n">
-        <v>19280.8</v>
+        <v>19249</v>
       </c>
       <c r="U17" s="18" t="n">
-        <v>19492.7</v>
+        <v>19460.6</v>
       </c>
       <c r="V17" s="18" t="n">
-        <v>19492.7</v>
+        <v>19460.6</v>
       </c>
     </row>
     <row r="18">
@@ -22375,55 +22375,55 @@
         <v/>
       </c>
       <c r="J23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1342.11)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(J$1,변수H,0),0),1337.49)</f>
         <v/>
       </c>
       <c r="K23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(K$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="L23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(L$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="M23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(M$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="N23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(N$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="O23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(O$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(P$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="Q23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Q$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="R23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(R$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="S23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(S$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="T23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(T$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="U23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(U$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="V23" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(V$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
     </row>
@@ -27963,7 +27963,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="46" t="n">
